--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB1F6DA-2E10-464F-B951-F9B733965CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE231811-E3D9-413B-ACD1-B258ACCD920B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>FORECAST</t>
   </si>
@@ -206,6 +206,15 @@
   </si>
   <si>
     <t>DIF UNITS</t>
+  </si>
+  <si>
+    <t>Cremigurt Mango 150g</t>
+  </si>
+  <si>
+    <t>Cremigurt Ciruela 150g</t>
+  </si>
+  <si>
+    <t>Cremigurt Mora 150g</t>
   </si>
 </sst>
 </file>
@@ -440,39 +449,41 @@
       <sheetName val="INVENTARIO NACIONAL 06-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 07-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 10-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 11-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 12-08-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="3">
           <cell r="G3">
-            <v>117531</v>
+            <v>175964</v>
           </cell>
           <cell r="H3">
-            <v>115833</v>
+            <v>173472</v>
           </cell>
           <cell r="I3">
-            <v>23506.2</v>
+            <v>25137.714285714286</v>
           </cell>
           <cell r="J3">
-            <v>517136.4</v>
+            <v>553029.71428571432</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.18108911394511443</v>
+            <v>0.27112136241704837</v>
           </cell>
           <cell r="M3">
-            <v>-531492</v>
+            <v>-473059</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>5573</v>
+            <v>8143</v>
           </cell>
           <cell r="D4">
-            <v>1114.5999999999999</v>
+            <v>1163.2857142857142</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -495,364 +506,388 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>469</v>
+            <v>563</v>
           </cell>
           <cell r="D5">
-            <v>93.8</v>
+            <v>80.428571428571431</v>
           </cell>
           <cell r="G5">
-            <v>1698</v>
+            <v>2492</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
           </cell>
           <cell r="I5">
-            <v>46244</v>
+            <v>46246</v>
           </cell>
           <cell r="J5">
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>5</v>
+            <v>7</v>
           </cell>
           <cell r="L5">
-            <v>16</v>
+            <v>14</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>1969</v>
+            <v>3103</v>
           </cell>
           <cell r="D6">
-            <v>393.8</v>
+            <v>443.28571428571428</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>523</v>
+            <v>723</v>
           </cell>
           <cell r="D7">
-            <v>104.6</v>
+            <v>103.28571428571429</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>42</v>
+            <v>64</v>
           </cell>
           <cell r="D8">
-            <v>8.4</v>
+            <v>9.1428571428571423</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>6506</v>
+            <v>10057</v>
           </cell>
           <cell r="D9">
-            <v>1301.2</v>
+            <v>1436.7142857142858</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>617</v>
+            <v>964</v>
           </cell>
           <cell r="D10">
-            <v>123.4</v>
+            <v>137.71428571428572</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>1635</v>
+            <v>2510</v>
           </cell>
           <cell r="D11">
-            <v>327</v>
+            <v>358.57142857142856</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>3728</v>
+            <v>4766</v>
           </cell>
           <cell r="D12">
-            <v>745.6</v>
+            <v>680.85714285714289</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>2116</v>
+            <v>2728</v>
           </cell>
           <cell r="D13">
-            <v>423.2</v>
+            <v>389.71428571428572</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>15669</v>
+            <v>24069</v>
           </cell>
           <cell r="D14">
-            <v>3133.8</v>
+            <v>3438.4285714285716</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>10437</v>
+            <v>15488</v>
           </cell>
           <cell r="D15">
-            <v>2087.4</v>
+            <v>2212.5714285714284</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>10105</v>
+            <v>15459</v>
           </cell>
           <cell r="D16">
-            <v>2021</v>
+            <v>2208.4285714285716</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>11379</v>
+            <v>18063</v>
           </cell>
           <cell r="D17">
-            <v>2275.8000000000002</v>
+            <v>2580.4285714285716</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>310</v>
+            <v>319</v>
           </cell>
           <cell r="D18">
-            <v>62</v>
+            <v>45.571428571428569</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>1041</v>
+            <v>0</v>
           </cell>
           <cell r="D19">
-            <v>208.2</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>628</v>
+            <v>0</v>
           </cell>
           <cell r="D20">
-            <v>125.6</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>2422</v>
+            <v>0</v>
           </cell>
           <cell r="D21">
-            <v>484.4</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>3655</v>
+            <v>1415</v>
           </cell>
           <cell r="D22">
-            <v>731</v>
+            <v>202.14285714285714</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>0</v>
+            <v>844</v>
           </cell>
           <cell r="D23">
-            <v>0</v>
+            <v>120.57142857142857</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>402</v>
+            <v>3423</v>
           </cell>
           <cell r="D24">
-            <v>80.400000000000006</v>
+            <v>489</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>2877</v>
+            <v>5055</v>
           </cell>
           <cell r="D25">
-            <v>575.4</v>
+            <v>722.14285714285711</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>4413</v>
+            <v>0</v>
           </cell>
           <cell r="D26">
-            <v>882.6</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>2401</v>
+            <v>582</v>
           </cell>
           <cell r="D27">
-            <v>480.2</v>
+            <v>83.142857142857139</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>1658</v>
+            <v>4287</v>
           </cell>
           <cell r="D28">
-            <v>331.6</v>
+            <v>612.42857142857144</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>582</v>
+            <v>8062</v>
           </cell>
           <cell r="D29">
-            <v>116.4</v>
+            <v>1151.7142857142858</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>513</v>
+            <v>3388</v>
           </cell>
           <cell r="D30">
-            <v>102.6</v>
+            <v>484</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>2032</v>
+            <v>2546</v>
           </cell>
           <cell r="D31">
-            <v>406.4</v>
+            <v>363.71428571428572</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>3158</v>
+            <v>914</v>
           </cell>
           <cell r="D32">
-            <v>631.6</v>
+            <v>130.57142857142858</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>4100</v>
+            <v>749</v>
           </cell>
           <cell r="D33">
-            <v>820</v>
+            <v>107</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>2473</v>
+            <v>3434</v>
           </cell>
           <cell r="D34">
-            <v>494.6</v>
+            <v>490.57142857142856</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>172</v>
+            <v>4519</v>
           </cell>
           <cell r="D35">
-            <v>34.4</v>
+            <v>645.57142857142856</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>3237</v>
+            <v>5918</v>
           </cell>
           <cell r="D36">
-            <v>647.4</v>
+            <v>845.42857142857144</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>662</v>
+            <v>3812</v>
           </cell>
           <cell r="D37">
-            <v>132.4</v>
+            <v>544.57142857142856</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>1428</v>
+            <v>175</v>
           </cell>
           <cell r="D38">
-            <v>285.60000000000002</v>
+            <v>25</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>2874</v>
+            <v>4530</v>
           </cell>
           <cell r="D39">
-            <v>574.79999999999995</v>
+            <v>647.14285714285711</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>1561</v>
+            <v>709</v>
           </cell>
           <cell r="D40">
-            <v>312.2</v>
+            <v>101.28571428571429</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>1252</v>
+            <v>2181</v>
           </cell>
           <cell r="D41">
-            <v>250.4</v>
+            <v>311.57142857142856</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>205</v>
+            <v>3902</v>
           </cell>
           <cell r="D42">
-            <v>41</v>
+            <v>557.42857142857144</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>452</v>
+            <v>2251</v>
           </cell>
           <cell r="D43">
-            <v>90.4</v>
+            <v>321.57142857142856</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>331</v>
+            <v>1816</v>
           </cell>
           <cell r="D44">
-            <v>66.2</v>
+            <v>259.42857142857144</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>216</v>
+            <v>345</v>
           </cell>
           <cell r="D45">
-            <v>43.2</v>
+            <v>49.285714285714285</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>0</v>
+            <v>715</v>
           </cell>
           <cell r="D46">
-            <v>0</v>
+            <v>102.14285714285714</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>10</v>
+            <v>483</v>
           </cell>
           <cell r="D47">
-            <v>2</v>
+            <v>69</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="C48">
+            <v>387</v>
+          </cell>
+          <cell r="D48">
+            <v>55.285714285714285</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="C49">
+            <v>0</v>
+          </cell>
+          <cell r="D49">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="C50">
+            <v>11</v>
+          </cell>
+          <cell r="D50">
+            <v>1.5714285714285714</v>
           </cell>
         </row>
       </sheetData>
@@ -862,6 +897,8 @@
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1164,7 +1201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55CD20E1-8530-482E-BAF2-454F195C9DA1}">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="10"/>
@@ -1206,11 +1243,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>5573</v>
+        <v>8143</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1114.5999999999999</v>
+        <v>1163.2857142857142</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1222,11 +1259,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>469</v>
+        <v>563</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>93.8</v>
+        <v>80.428571428571431</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1238,11 +1275,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>1969</v>
+        <v>3103</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>393.8</v>
+        <v>443.28571428571428</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1254,11 +1291,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>523</v>
+        <v>723</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>104.6</v>
+        <v>103.28571428571429</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1270,11 +1307,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>8.4</v>
+        <v>9.1428571428571423</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1286,11 +1323,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>6506</v>
+        <v>10057</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1301.2</v>
+        <v>1436.7142857142858</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1302,11 +1339,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>617</v>
+        <v>964</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>123.4</v>
+        <v>137.71428571428572</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1318,11 +1355,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>1635</v>
+        <v>2510</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>327</v>
+        <v>358.57142857142856</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1334,11 +1371,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>3728</v>
+        <v>4766</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>745.6</v>
+        <v>680.85714285714289</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1350,11 +1387,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>2116</v>
+        <v>2728</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>423.2</v>
+        <v>389.71428571428572</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1366,11 +1403,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>15669</v>
+        <v>24069</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3133.8</v>
+        <v>3438.4285714285716</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1382,11 +1419,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>10437</v>
+        <v>15488</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2087.4</v>
+        <v>2212.5714285714284</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1398,11 +1435,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>10105</v>
+        <v>15459</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2021</v>
+        <v>2208.4285714285716</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1414,11 +1451,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>11379</v>
+        <v>18063</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2275.8000000000002</v>
+        <v>2580.4285714285716</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1430,475 +1467,523 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>62</v>
+        <v>45.571428571428569</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
-        <v>130700</v>
+        <v>130157</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="C17" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>1041</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!$C$19</f>
+        <v>0</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>208.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="15">
-        <v>130701</v>
+        <v>130158</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C18" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>628</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!$C$20</f>
+        <v>0</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>125.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
-        <v>130702</v>
+        <v>130159</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C19" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>2422</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!$C$21</f>
+        <v>0</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>484.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="15">
-        <v>130703</v>
+        <v>130700</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>3655</v>
+        <v>1415</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>731</v>
+        <v>202.14285714285714</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="15">
-        <v>130704</v>
+        <v>130701</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>0</v>
+        <v>844</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>0</v>
+        <v>120.57142857142857</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="15">
-        <v>130707</v>
+        <v>130702</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>402</v>
+        <v>3423</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>80.400000000000006</v>
+        <v>489</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="15">
-        <v>131150</v>
+        <v>130703</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>2877</v>
+        <v>5055</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>575.4</v>
+        <v>722.14285714285711</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
-        <v>131151</v>
+        <v>130704</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>4413</v>
+        <v>0</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>882.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="15">
-        <v>131152</v>
+        <v>130707</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>2401</v>
+        <v>582</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>480.2</v>
+        <v>83.142857142857139</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="15">
-        <v>131153</v>
+        <v>131150</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>1658</v>
+        <v>4287</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>331.6</v>
+        <v>612.42857142857144</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="15">
-        <v>131700</v>
+        <v>131151</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>582</v>
+        <v>8062</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>116.4</v>
+        <v>1151.7142857142858</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="15">
-        <v>131701</v>
+        <v>131152</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>513</v>
+        <v>3388</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>102.6</v>
+        <v>484</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="15">
-        <v>132150</v>
+        <v>131153</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>2032</v>
+        <v>2546</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>406.4</v>
+        <v>363.71428571428572</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="15">
-        <v>132151</v>
+        <v>131700</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>3158</v>
+        <v>914</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>631.6</v>
+        <v>130.57142857142858</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="15">
-        <v>132152</v>
+        <v>131701</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>4100</v>
+        <v>749</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>820</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="15">
-        <v>132153</v>
+        <v>132150</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>2473</v>
+        <v>3434</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>494.6</v>
+        <v>490.57142857142856</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="15">
-        <v>140230</v>
+        <v>132151</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>172</v>
+        <v>4519</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>34.4</v>
+        <v>645.57142857142856</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="15">
-        <v>140231</v>
+        <v>132152</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>3237</v>
+        <v>5918</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>647.4</v>
+        <v>845.42857142857144</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="15">
-        <v>140232</v>
+        <v>132153</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>662</v>
+        <v>3812</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>132.4</v>
+        <v>544.57142857142856</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="15">
-        <v>150360</v>
+        <v>140230</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>1428</v>
+        <v>175</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>285.60000000000002</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="15">
-        <v>150361</v>
+        <v>140231</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>2874</v>
+        <v>4530</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>574.79999999999995</v>
+        <v>647.14285714285711</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
-        <v>150362</v>
+        <v>140232</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>1561</v>
+        <v>709</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>312.2</v>
+        <v>101.28571428571429</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="15">
-        <v>150363</v>
+        <v>150360</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>1252</v>
+        <v>2181</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>250.4</v>
+        <v>311.57142857142856</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="15">
-        <v>151500</v>
+        <v>150361</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>205</v>
+        <v>3902</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>41</v>
+        <v>557.42857142857144</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="15">
-        <v>151501</v>
+        <v>150362</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>452</v>
+        <v>2251</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>90.4</v>
+        <v>321.57142857142856</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="15">
-        <v>151502</v>
+        <v>150363</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>331</v>
+        <v>1816</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>66.2</v>
+        <v>259.42857142857144</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="15">
-        <v>151503</v>
+        <v>151500</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>216</v>
+        <v>345</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>43.2</v>
+        <v>49.285714285714285</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="15"/>
+      <c r="A44" s="15">
+        <v>151501</v>
+      </c>
       <c r="B44" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>0</v>
+        <v>102.14285714285714</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="15"/>
+      <c r="A45" s="15">
+        <v>151502</v>
+      </c>
       <c r="B45" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>10</v>
+        <v>483</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="11"/>
+      <c r="A46" s="15">
+        <v>151503</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C46" s="13">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
+        <v>387</v>
+      </c>
+      <c r="D46" s="12">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
+        <v>55.285714285714285</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="15"/>
+      <c r="B47" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="13">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
+        <v>0</v>
+      </c>
+      <c r="D47" s="12">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="15"/>
+      <c r="B48" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" s="13">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
+        <v>11</v>
+      </c>
+      <c r="D48" s="12">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
+        <v>1.5714285714285714</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C49" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1951,19 +2036,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>117531</v>
+        <v>175964</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>115833</v>
+        <v>173472</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>23506.2</v>
+        <v>25137.714285714286</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>517136.4</v>
+        <v>553029.71428571432</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -1971,11 +2056,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.18108911394511443</v>
+        <v>0.27112136241704837</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-531492</v>
+        <v>-473059</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2011,7 +2096,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>1698</v>
+        <v>2492</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2019,7 +2104,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2027,11 +2112,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE231811-E3D9-413B-ACD1-B258ACCD920B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D038EDB4-9C6C-41FC-891D-9DDEECD7A10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -457,33 +457,33 @@
       <sheetData sheetId="1">
         <row r="3">
           <cell r="G3">
-            <v>175964</v>
+            <v>208630</v>
           </cell>
           <cell r="H3">
-            <v>173472</v>
+            <v>206619</v>
           </cell>
           <cell r="I3">
-            <v>25137.714285714286</v>
+            <v>26078.75</v>
           </cell>
           <cell r="J3">
-            <v>553029.71428571432</v>
+            <v>573732.5</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.27112136241704837</v>
+            <v>0.32145239845121049</v>
           </cell>
           <cell r="M3">
-            <v>-473059</v>
+            <v>-440393</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>8143</v>
+            <v>9706</v>
           </cell>
           <cell r="D4">
-            <v>1163.2857142857142</v>
+            <v>1213.25</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -506,188 +506,188 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>563</v>
+            <v>629</v>
           </cell>
           <cell r="D5">
-            <v>80.428571428571431</v>
+            <v>78.625</v>
           </cell>
           <cell r="G5">
-            <v>2492</v>
+            <v>2011</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
           </cell>
           <cell r="I5">
-            <v>46246</v>
+            <v>46247</v>
           </cell>
           <cell r="J5">
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>7</v>
+            <v>8</v>
           </cell>
           <cell r="L5">
-            <v>14</v>
+            <v>13</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>3103</v>
+            <v>3767</v>
           </cell>
           <cell r="D6">
-            <v>443.28571428571428</v>
+            <v>470.875</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>723</v>
+            <v>866</v>
           </cell>
           <cell r="D7">
-            <v>103.28571428571429</v>
+            <v>108.25</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>64</v>
+            <v>75</v>
           </cell>
           <cell r="D8">
-            <v>9.1428571428571423</v>
+            <v>9.375</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>10057</v>
+            <v>11647</v>
           </cell>
           <cell r="D9">
-            <v>1436.7142857142858</v>
+            <v>1455.875</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>964</v>
+            <v>1158</v>
           </cell>
           <cell r="D10">
-            <v>137.71428571428572</v>
+            <v>144.75</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>2510</v>
+            <v>2768</v>
           </cell>
           <cell r="D11">
-            <v>358.57142857142856</v>
+            <v>346</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>4766</v>
+            <v>5800</v>
           </cell>
           <cell r="D12">
-            <v>680.85714285714289</v>
+            <v>725</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>2728</v>
+            <v>3098</v>
           </cell>
           <cell r="D13">
-            <v>389.71428571428572</v>
+            <v>387.25</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>24069</v>
+            <v>28268</v>
           </cell>
           <cell r="D14">
-            <v>3438.4285714285716</v>
+            <v>3533.5</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>15488</v>
+            <v>17988</v>
           </cell>
           <cell r="D15">
-            <v>2212.5714285714284</v>
+            <v>2248.5</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>15459</v>
+            <v>17747</v>
           </cell>
           <cell r="D16">
-            <v>2208.4285714285716</v>
+            <v>2218.375</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>18063</v>
+            <v>21394</v>
           </cell>
           <cell r="D17">
-            <v>2580.4285714285716</v>
+            <v>2674.25</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>319</v>
+            <v>348</v>
           </cell>
           <cell r="D18">
-            <v>45.571428571428569</v>
+            <v>43.5</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>0</v>
+            <v>383</v>
           </cell>
           <cell r="D19">
-            <v>0</v>
+            <v>47.875</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>0</v>
+            <v>559</v>
           </cell>
           <cell r="D20">
-            <v>0</v>
+            <v>69.875</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>0</v>
+            <v>453</v>
           </cell>
           <cell r="D21">
-            <v>0</v>
+            <v>56.625</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>1415</v>
+            <v>1778</v>
           </cell>
           <cell r="D22">
-            <v>202.14285714285714</v>
+            <v>222.25</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>844</v>
+            <v>1038</v>
           </cell>
           <cell r="D23">
-            <v>120.57142857142857</v>
+            <v>129.75</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>3423</v>
+            <v>4226</v>
           </cell>
           <cell r="D24">
-            <v>489</v>
+            <v>528.25</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>5055</v>
+            <v>6369</v>
           </cell>
           <cell r="D25">
-            <v>722.14285714285711</v>
+            <v>796.125</v>
           </cell>
         </row>
         <row r="26">
@@ -703,87 +703,87 @@
             <v>582</v>
           </cell>
           <cell r="D27">
-            <v>83.142857142857139</v>
+            <v>72.75</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>4287</v>
+            <v>5249</v>
           </cell>
           <cell r="D28">
-            <v>612.42857142857144</v>
+            <v>656.125</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>8062</v>
+            <v>9188</v>
           </cell>
           <cell r="D29">
-            <v>1151.7142857142858</v>
+            <v>1148.5</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>3388</v>
+            <v>4165</v>
           </cell>
           <cell r="D30">
-            <v>484</v>
+            <v>520.625</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>2546</v>
+            <v>3048</v>
           </cell>
           <cell r="D31">
-            <v>363.71428571428572</v>
+            <v>381</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>914</v>
+            <v>1089</v>
           </cell>
           <cell r="D32">
-            <v>130.57142857142858</v>
+            <v>136.125</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>749</v>
+            <v>885</v>
           </cell>
           <cell r="D33">
-            <v>107</v>
+            <v>110.625</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>3434</v>
+            <v>4939</v>
           </cell>
           <cell r="D34">
-            <v>490.57142857142856</v>
+            <v>617.375</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>4519</v>
+            <v>5514</v>
           </cell>
           <cell r="D35">
-            <v>645.57142857142856</v>
+            <v>689.25</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>5918</v>
+            <v>7294</v>
           </cell>
           <cell r="D36">
-            <v>845.42857142857144</v>
+            <v>911.75</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>3812</v>
+            <v>4688</v>
           </cell>
           <cell r="D37">
-            <v>544.57142857142856</v>
+            <v>586</v>
           </cell>
         </row>
         <row r="38">
@@ -791,15 +791,15 @@
             <v>175</v>
           </cell>
           <cell r="D38">
-            <v>25</v>
+            <v>21.875</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>4530</v>
+            <v>4937</v>
           </cell>
           <cell r="D39">
-            <v>647.14285714285711</v>
+            <v>617.125</v>
           </cell>
         </row>
         <row r="40">
@@ -807,71 +807,71 @@
             <v>709</v>
           </cell>
           <cell r="D40">
-            <v>101.28571428571429</v>
+            <v>88.625</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>2181</v>
+            <v>2531</v>
           </cell>
           <cell r="D41">
-            <v>311.57142857142856</v>
+            <v>316.375</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>3902</v>
+            <v>4523</v>
           </cell>
           <cell r="D42">
-            <v>557.42857142857144</v>
+            <v>565.375</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>2251</v>
+            <v>2654</v>
           </cell>
           <cell r="D43">
-            <v>321.57142857142856</v>
+            <v>331.75</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>1816</v>
+            <v>2145</v>
           </cell>
           <cell r="D44">
-            <v>259.42857142857144</v>
+            <v>268.125</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>345</v>
+            <v>418</v>
           </cell>
           <cell r="D45">
-            <v>49.285714285714285</v>
+            <v>52.25</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>715</v>
+            <v>829</v>
           </cell>
           <cell r="D46">
-            <v>102.14285714285714</v>
+            <v>103.625</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>483</v>
+            <v>539</v>
           </cell>
           <cell r="D47">
-            <v>69</v>
+            <v>67.375</v>
           </cell>
         </row>
         <row r="48">
           <cell r="C48">
-            <v>387</v>
+            <v>440</v>
           </cell>
           <cell r="D48">
-            <v>55.285714285714285</v>
+            <v>55</v>
           </cell>
         </row>
         <row r="49">
@@ -884,10 +884,10 @@
         </row>
         <row r="50">
           <cell r="C50">
-            <v>11</v>
+            <v>13</v>
           </cell>
           <cell r="D50">
-            <v>1.5714285714285714</v>
+            <v>1.625</v>
           </cell>
         </row>
       </sheetData>
@@ -1243,11 +1243,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>8143</v>
+        <v>9706</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1163.2857142857142</v>
+        <v>1213.25</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>563</v>
+        <v>629</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>80.428571428571431</v>
+        <v>78.625</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1275,11 +1275,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>3103</v>
+        <v>3767</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>443.28571428571428</v>
+        <v>470.875</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1291,11 +1291,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>723</v>
+        <v>866</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>103.28571428571429</v>
+        <v>108.25</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1307,11 +1307,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>9.1428571428571423</v>
+        <v>9.375</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1323,11 +1323,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>10057</v>
+        <v>11647</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1436.7142857142858</v>
+        <v>1455.875</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1339,11 +1339,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>964</v>
+        <v>1158</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>137.71428571428572</v>
+        <v>144.75</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1355,11 +1355,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>2510</v>
+        <v>2768</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>358.57142857142856</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1371,11 +1371,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>4766</v>
+        <v>5800</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>680.85714285714289</v>
+        <v>725</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1387,11 +1387,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>2728</v>
+        <v>3098</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>389.71428571428572</v>
+        <v>387.25</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>24069</v>
+        <v>28268</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3438.4285714285716</v>
+        <v>3533.5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1419,11 +1419,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>15488</v>
+        <v>17988</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2212.5714285714284</v>
+        <v>2248.5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1435,11 +1435,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>15459</v>
+        <v>17747</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2208.4285714285716</v>
+        <v>2218.375</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1451,11 +1451,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>18063</v>
+        <v>21394</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2580.4285714285716</v>
+        <v>2674.25</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1467,11 +1467,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>319</v>
+        <v>348</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>45.571428571428569</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1483,11 +1483,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$19</f>
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>0</v>
+        <v>47.875</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1499,11 +1499,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$20</f>
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>0</v>
+        <v>69.875</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1515,11 +1515,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$21</f>
-        <v>0</v>
+        <v>453</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>0</v>
+        <v>56.625</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1531,11 +1531,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>1415</v>
+        <v>1778</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>202.14285714285714</v>
+        <v>222.25</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1547,11 +1547,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>844</v>
+        <v>1038</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>120.57142857142857</v>
+        <v>129.75</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1563,11 +1563,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>3423</v>
+        <v>4226</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>489</v>
+        <v>528.25</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1579,11 +1579,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>5055</v>
+        <v>6369</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>722.14285714285711</v>
+        <v>796.125</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>83.142857142857139</v>
+        <v>72.75</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1627,11 +1627,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>4287</v>
+        <v>5249</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>612.42857142857144</v>
+        <v>656.125</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1643,11 +1643,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>8062</v>
+        <v>9188</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>1151.7142857142858</v>
+        <v>1148.5</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1659,11 +1659,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>3388</v>
+        <v>4165</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>484</v>
+        <v>520.625</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>2546</v>
+        <v>3048</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>363.71428571428572</v>
+        <v>381</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1691,11 +1691,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>914</v>
+        <v>1089</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>130.57142857142858</v>
+        <v>136.125</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1707,11 +1707,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>749</v>
+        <v>885</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>107</v>
+        <v>110.625</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1723,11 +1723,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>3434</v>
+        <v>4939</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>490.57142857142856</v>
+        <v>617.375</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1739,11 +1739,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>4519</v>
+        <v>5514</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>645.57142857142856</v>
+        <v>689.25</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1755,11 +1755,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>5918</v>
+        <v>7294</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>845.42857142857144</v>
+        <v>911.75</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1771,11 +1771,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>3812</v>
+        <v>4688</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>544.57142857142856</v>
+        <v>586</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>25</v>
+        <v>21.875</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1803,11 +1803,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>4530</v>
+        <v>4937</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>647.14285714285711</v>
+        <v>617.125</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>101.28571428571429</v>
+        <v>88.625</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1835,11 +1835,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>2181</v>
+        <v>2531</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>311.57142857142856</v>
+        <v>316.375</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1851,11 +1851,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>3902</v>
+        <v>4523</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>557.42857142857144</v>
+        <v>565.375</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1867,11 +1867,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>2251</v>
+        <v>2654</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>321.57142857142856</v>
+        <v>331.75</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1883,11 +1883,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>1816</v>
+        <v>2145</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>259.42857142857144</v>
+        <v>268.125</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1899,11 +1899,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>345</v>
+        <v>418</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>49.285714285714285</v>
+        <v>52.25</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1915,11 +1915,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>715</v>
+        <v>829</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>102.14285714285714</v>
+        <v>103.625</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>483</v>
+        <v>539</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>69</v>
+        <v>67.375</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1947,11 +1947,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>387</v>
+        <v>440</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>55.285714285714285</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1975,11 +1975,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>1.5714285714285714</v>
+        <v>1.625</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2036,19 +2036,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>175964</v>
+        <v>208630</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>173472</v>
+        <v>206619</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>25137.714285714286</v>
+        <v>26078.75</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>553029.71428571432</v>
+        <v>573732.5</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2056,11 +2056,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.27112136241704837</v>
+        <v>0.32145239845121049</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-473059</v>
+        <v>-440393</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2096,7 +2096,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>2492</v>
+        <v>2011</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2112,11 +2112,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D038EDB4-9C6C-41FC-891D-9DDEECD7A10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39BA4D2C-5DB1-48FB-8F18-389FAE966CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -441,9 +441,6 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="VINCULO VTS BY SKU JULIO"/>
-      <sheetName val="VINCULO VTS BY SKU OPEN"/>
-      <sheetName val="DESV. VTS BY SKU"/>
       <sheetName val="INVENTARIO NACIONAL 04-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 05-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 06-08-26"/>
@@ -451,446 +448,15 @@
       <sheetName val="INVENTARIO NACIONAL 10-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 11-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 12-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 13-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
+      <sheetName val="VINCULO VTS BY SKU JULIO"/>
+      <sheetName val="VINCULO VTS BY SKU OPEN"/>
+      <sheetName val="DESV. VTS BY SKU"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="3">
-          <cell r="G3">
-            <v>208630</v>
-          </cell>
-          <cell r="H3">
-            <v>206619</v>
-          </cell>
-          <cell r="I3">
-            <v>26078.75</v>
-          </cell>
-          <cell r="J3">
-            <v>573732.5</v>
-          </cell>
-          <cell r="K3">
-            <v>649023</v>
-          </cell>
-          <cell r="L3">
-            <v>0.32145239845121049</v>
-          </cell>
-          <cell r="M3">
-            <v>-440393</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="C4">
-            <v>9706</v>
-          </cell>
-          <cell r="D4">
-            <v>1213.25</v>
-          </cell>
-          <cell r="G4" t="str">
-            <v>UNITS RETURN</v>
-          </cell>
-          <cell r="H4" t="str">
-            <v>INICIO DE VENTA</v>
-          </cell>
-          <cell r="I4" t="str">
-            <v>TRANSC. VENTA</v>
-          </cell>
-          <cell r="J4" t="str">
-            <v>FINAL DE VENTA</v>
-          </cell>
-          <cell r="K4" t="str">
-            <v>DIAS VENTA EFECT.</v>
-          </cell>
-          <cell r="L4" t="str">
-            <v>DIAS VENTA RESTA.</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="C5">
-            <v>629</v>
-          </cell>
-          <cell r="D5">
-            <v>78.625</v>
-          </cell>
-          <cell r="G5">
-            <v>2011</v>
-          </cell>
-          <cell r="H5">
-            <v>46237</v>
-          </cell>
-          <cell r="I5">
-            <v>46247</v>
-          </cell>
-          <cell r="J5">
-            <v>46265</v>
-          </cell>
-          <cell r="K5">
-            <v>8</v>
-          </cell>
-          <cell r="L5">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="C6">
-            <v>3767</v>
-          </cell>
-          <cell r="D6">
-            <v>470.875</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="C7">
-            <v>866</v>
-          </cell>
-          <cell r="D7">
-            <v>108.25</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="C8">
-            <v>75</v>
-          </cell>
-          <cell r="D8">
-            <v>9.375</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="C9">
-            <v>11647</v>
-          </cell>
-          <cell r="D9">
-            <v>1455.875</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="C10">
-            <v>1158</v>
-          </cell>
-          <cell r="D10">
-            <v>144.75</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="C11">
-            <v>2768</v>
-          </cell>
-          <cell r="D11">
-            <v>346</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="C12">
-            <v>5800</v>
-          </cell>
-          <cell r="D12">
-            <v>725</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="C13">
-            <v>3098</v>
-          </cell>
-          <cell r="D13">
-            <v>387.25</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="C14">
-            <v>28268</v>
-          </cell>
-          <cell r="D14">
-            <v>3533.5</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="C15">
-            <v>17988</v>
-          </cell>
-          <cell r="D15">
-            <v>2248.5</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="C16">
-            <v>17747</v>
-          </cell>
-          <cell r="D16">
-            <v>2218.375</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="C17">
-            <v>21394</v>
-          </cell>
-          <cell r="D17">
-            <v>2674.25</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="C18">
-            <v>348</v>
-          </cell>
-          <cell r="D18">
-            <v>43.5</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="C19">
-            <v>383</v>
-          </cell>
-          <cell r="D19">
-            <v>47.875</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="C20">
-            <v>559</v>
-          </cell>
-          <cell r="D20">
-            <v>69.875</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="C21">
-            <v>453</v>
-          </cell>
-          <cell r="D21">
-            <v>56.625</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="C22">
-            <v>1778</v>
-          </cell>
-          <cell r="D22">
-            <v>222.25</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="C23">
-            <v>1038</v>
-          </cell>
-          <cell r="D23">
-            <v>129.75</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="C24">
-            <v>4226</v>
-          </cell>
-          <cell r="D24">
-            <v>528.25</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="C25">
-            <v>6369</v>
-          </cell>
-          <cell r="D25">
-            <v>796.125</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="C26">
-            <v>0</v>
-          </cell>
-          <cell r="D26">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="C27">
-            <v>582</v>
-          </cell>
-          <cell r="D27">
-            <v>72.75</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="C28">
-            <v>5249</v>
-          </cell>
-          <cell r="D28">
-            <v>656.125</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="C29">
-            <v>9188</v>
-          </cell>
-          <cell r="D29">
-            <v>1148.5</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="C30">
-            <v>4165</v>
-          </cell>
-          <cell r="D30">
-            <v>520.625</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="C31">
-            <v>3048</v>
-          </cell>
-          <cell r="D31">
-            <v>381</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="C32">
-            <v>1089</v>
-          </cell>
-          <cell r="D32">
-            <v>136.125</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="C33">
-            <v>885</v>
-          </cell>
-          <cell r="D33">
-            <v>110.625</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="C34">
-            <v>4939</v>
-          </cell>
-          <cell r="D34">
-            <v>617.375</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="C35">
-            <v>5514</v>
-          </cell>
-          <cell r="D35">
-            <v>689.25</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="C36">
-            <v>7294</v>
-          </cell>
-          <cell r="D36">
-            <v>911.75</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="C37">
-            <v>4688</v>
-          </cell>
-          <cell r="D37">
-            <v>586</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="C38">
-            <v>175</v>
-          </cell>
-          <cell r="D38">
-            <v>21.875</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="C39">
-            <v>4937</v>
-          </cell>
-          <cell r="D39">
-            <v>617.125</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="C40">
-            <v>709</v>
-          </cell>
-          <cell r="D40">
-            <v>88.625</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="C41">
-            <v>2531</v>
-          </cell>
-          <cell r="D41">
-            <v>316.375</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="C42">
-            <v>4523</v>
-          </cell>
-          <cell r="D42">
-            <v>565.375</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="C43">
-            <v>2654</v>
-          </cell>
-          <cell r="D43">
-            <v>331.75</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="C44">
-            <v>2145</v>
-          </cell>
-          <cell r="D44">
-            <v>268.125</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="C45">
-            <v>418</v>
-          </cell>
-          <cell r="D45">
-            <v>52.25</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="C46">
-            <v>829</v>
-          </cell>
-          <cell r="D46">
-            <v>103.625</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="C47">
-            <v>539</v>
-          </cell>
-          <cell r="D47">
-            <v>67.375</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="C48">
-            <v>440</v>
-          </cell>
-          <cell r="D48">
-            <v>55</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="C49">
-            <v>0</v>
-          </cell>
-          <cell r="D49">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="C50">
-            <v>13</v>
-          </cell>
-          <cell r="D50">
-            <v>1.625</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
@@ -899,6 +465,444 @@
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
+      <sheetData sheetId="10">
+        <row r="3">
+          <cell r="G3">
+            <v>237806</v>
+          </cell>
+          <cell r="H3">
+            <v>235631</v>
+          </cell>
+          <cell r="I3">
+            <v>26422.888888888891</v>
+          </cell>
+          <cell r="J3">
+            <v>581303.55555555562</v>
+          </cell>
+          <cell r="K3">
+            <v>649023</v>
+          </cell>
+          <cell r="L3">
+            <v>0.36640612120063543</v>
+          </cell>
+          <cell r="M3">
+            <v>-411217</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="C4">
+            <v>10703</v>
+          </cell>
+          <cell r="D4">
+            <v>1189.2222222222222</v>
+          </cell>
+          <cell r="G4" t="str">
+            <v>UNITS RETURN</v>
+          </cell>
+          <cell r="H4" t="str">
+            <v>INICIO DE VENTA</v>
+          </cell>
+          <cell r="I4" t="str">
+            <v>TRANSC. VENTA</v>
+          </cell>
+          <cell r="J4" t="str">
+            <v>FINAL DE VENTA</v>
+          </cell>
+          <cell r="K4" t="str">
+            <v>DIAS VENTA EFECT.</v>
+          </cell>
+          <cell r="L4" t="str">
+            <v>DIAS VENTA RESTA.</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="C5">
+            <v>789</v>
+          </cell>
+          <cell r="D5">
+            <v>87.666666666666671</v>
+          </cell>
+          <cell r="G5">
+            <v>2175</v>
+          </cell>
+          <cell r="H5">
+            <v>46237</v>
+          </cell>
+          <cell r="I5">
+            <v>46248</v>
+          </cell>
+          <cell r="J5">
+            <v>46265</v>
+          </cell>
+          <cell r="K5">
+            <v>9</v>
+          </cell>
+          <cell r="L5">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6">
+            <v>4207</v>
+          </cell>
+          <cell r="D6">
+            <v>467.44444444444446</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7">
+            <v>967</v>
+          </cell>
+          <cell r="D7">
+            <v>107.44444444444444</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>90</v>
+          </cell>
+          <cell r="D8">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9">
+            <v>13213</v>
+          </cell>
+          <cell r="D9">
+            <v>1468.1111111111111</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>1361</v>
+          </cell>
+          <cell r="D10">
+            <v>151.22222222222223</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11">
+            <v>3094</v>
+          </cell>
+          <cell r="D11">
+            <v>343.77777777777777</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>6814</v>
+          </cell>
+          <cell r="D12">
+            <v>757.11111111111109</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>3258</v>
+          </cell>
+          <cell r="D13">
+            <v>362</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14">
+            <v>32304</v>
+          </cell>
+          <cell r="D14">
+            <v>3589.3333333333335</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="C15">
+            <v>20652</v>
+          </cell>
+          <cell r="D15">
+            <v>2294.6666666666665</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>20404</v>
+          </cell>
+          <cell r="D16">
+            <v>2267.1111111111113</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>24407</v>
+          </cell>
+          <cell r="D17">
+            <v>2711.8888888888887</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="C18">
+            <v>354</v>
+          </cell>
+          <cell r="D18">
+            <v>39.333333333333336</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="C19">
+            <v>830</v>
+          </cell>
+          <cell r="D19">
+            <v>92.222222222222229</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="C20">
+            <v>1168</v>
+          </cell>
+          <cell r="D20">
+            <v>129.77777777777777</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="C21">
+            <v>1002</v>
+          </cell>
+          <cell r="D21">
+            <v>111.33333333333333</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="C22">
+            <v>2194</v>
+          </cell>
+          <cell r="D22">
+            <v>243.77777777777777</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="C23">
+            <v>1252</v>
+          </cell>
+          <cell r="D23">
+            <v>139.11111111111111</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="C24">
+            <v>4679</v>
+          </cell>
+          <cell r="D24">
+            <v>519.88888888888891</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25">
+            <v>7208</v>
+          </cell>
+          <cell r="D25">
+            <v>800.88888888888891</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="C26">
+            <v>0</v>
+          </cell>
+          <cell r="D26">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="C27">
+            <v>582</v>
+          </cell>
+          <cell r="D27">
+            <v>64.666666666666671</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="C28">
+            <v>6157</v>
+          </cell>
+          <cell r="D28">
+            <v>684.11111111111109</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="C29">
+            <v>10752</v>
+          </cell>
+          <cell r="D29">
+            <v>1194.6666666666667</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="C30">
+            <v>4631</v>
+          </cell>
+          <cell r="D30">
+            <v>514.55555555555554</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="C31">
+            <v>3386</v>
+          </cell>
+          <cell r="D31">
+            <v>376.22222222222223</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="C32">
+            <v>1164</v>
+          </cell>
+          <cell r="D32">
+            <v>129.33333333333334</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="C33">
+            <v>1048</v>
+          </cell>
+          <cell r="D33">
+            <v>116.44444444444444</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="C34">
+            <v>5670</v>
+          </cell>
+          <cell r="D34">
+            <v>630</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="C35">
+            <v>6252</v>
+          </cell>
+          <cell r="D35">
+            <v>694.66666666666663</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="C36">
+            <v>8184</v>
+          </cell>
+          <cell r="D36">
+            <v>909.33333333333337</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="C37">
+            <v>5496</v>
+          </cell>
+          <cell r="D37">
+            <v>610.66666666666663</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="C38">
+            <v>175</v>
+          </cell>
+          <cell r="D38">
+            <v>19.444444444444443</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="C39">
+            <v>5251</v>
+          </cell>
+          <cell r="D39">
+            <v>583.44444444444446</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="C40">
+            <v>709</v>
+          </cell>
+          <cell r="D40">
+            <v>78.777777777777771</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="C41">
+            <v>2720</v>
+          </cell>
+          <cell r="D41">
+            <v>302.22222222222223</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="C42">
+            <v>4857</v>
+          </cell>
+          <cell r="D42">
+            <v>539.66666666666663</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="C43">
+            <v>2881</v>
+          </cell>
+          <cell r="D43">
+            <v>320.11111111111109</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="C44">
+            <v>2394</v>
+          </cell>
+          <cell r="D44">
+            <v>266</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="C45">
+            <v>437</v>
+          </cell>
+          <cell r="D45">
+            <v>48.555555555555557</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="C46">
+            <v>902</v>
+          </cell>
+          <cell r="D46">
+            <v>100.22222222222223</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="C47">
+            <v>546</v>
+          </cell>
+          <cell r="D47">
+            <v>60.666666666666664</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="C48">
+            <v>467</v>
+          </cell>
+          <cell r="D48">
+            <v>51.888888888888886</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="C49">
+            <v>0</v>
+          </cell>
+          <cell r="D49">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="C50">
+            <v>20</v>
+          </cell>
+          <cell r="D50">
+            <v>2.2222222222222223</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1243,11 +1247,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>9706</v>
+        <v>10703</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1213.25</v>
+        <v>1189.2222222222222</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1259,11 +1263,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>629</v>
+        <v>789</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>78.625</v>
+        <v>87.666666666666671</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1275,11 +1279,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>3767</v>
+        <v>4207</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>470.875</v>
+        <v>467.44444444444446</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1291,11 +1295,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>866</v>
+        <v>967</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>108.25</v>
+        <v>107.44444444444444</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1307,11 +1311,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>9.375</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1323,11 +1327,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>11647</v>
+        <v>13213</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1455.875</v>
+        <v>1468.1111111111111</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1339,11 +1343,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>1158</v>
+        <v>1361</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>144.75</v>
+        <v>151.22222222222223</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1355,11 +1359,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>2768</v>
+        <v>3094</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>346</v>
+        <v>343.77777777777777</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1371,11 +1375,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>5800</v>
+        <v>6814</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>725</v>
+        <v>757.11111111111109</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1387,11 +1391,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>3098</v>
+        <v>3258</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>387.25</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1403,11 +1407,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>28268</v>
+        <v>32304</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3533.5</v>
+        <v>3589.3333333333335</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1419,11 +1423,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>17988</v>
+        <v>20652</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2248.5</v>
+        <v>2294.6666666666665</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1435,11 +1439,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>17747</v>
+        <v>20404</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2218.375</v>
+        <v>2267.1111111111113</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1451,11 +1455,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>21394</v>
+        <v>24407</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2674.25</v>
+        <v>2711.8888888888887</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1467,11 +1471,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>43.5</v>
+        <v>39.333333333333336</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1483,11 +1487,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$19</f>
-        <v>383</v>
+        <v>830</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>47.875</v>
+        <v>92.222222222222229</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1499,11 +1503,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$20</f>
-        <v>559</v>
+        <v>1168</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>69.875</v>
+        <v>129.77777777777777</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1515,11 +1519,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$21</f>
-        <v>453</v>
+        <v>1002</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>56.625</v>
+        <v>111.33333333333333</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1531,11 +1535,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>1778</v>
+        <v>2194</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>222.25</v>
+        <v>243.77777777777777</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1547,11 +1551,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>1038</v>
+        <v>1252</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>129.75</v>
+        <v>139.11111111111111</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1563,11 +1567,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>4226</v>
+        <v>4679</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>528.25</v>
+        <v>519.88888888888891</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1579,11 +1583,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>6369</v>
+        <v>7208</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>796.125</v>
+        <v>800.88888888888891</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1615,7 +1619,7 @@
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>72.75</v>
+        <v>64.666666666666671</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1627,11 +1631,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>5249</v>
+        <v>6157</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>656.125</v>
+        <v>684.11111111111109</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1643,11 +1647,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>9188</v>
+        <v>10752</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>1148.5</v>
+        <v>1194.6666666666667</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1659,11 +1663,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>4165</v>
+        <v>4631</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>520.625</v>
+        <v>514.55555555555554</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1675,11 +1679,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>3048</v>
+        <v>3386</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>381</v>
+        <v>376.22222222222223</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1691,11 +1695,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1089</v>
+        <v>1164</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>136.125</v>
+        <v>129.33333333333334</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1707,11 +1711,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>885</v>
+        <v>1048</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>110.625</v>
+        <v>116.44444444444444</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1723,11 +1727,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>4939</v>
+        <v>5670</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>617.375</v>
+        <v>630</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1739,11 +1743,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>5514</v>
+        <v>6252</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>689.25</v>
+        <v>694.66666666666663</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1755,11 +1759,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>7294</v>
+        <v>8184</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>911.75</v>
+        <v>909.33333333333337</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1771,11 +1775,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>4688</v>
+        <v>5496</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>586</v>
+        <v>610.66666666666663</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1791,7 +1795,7 @@
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>21.875</v>
+        <v>19.444444444444443</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1803,11 +1807,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>4937</v>
+        <v>5251</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>617.125</v>
+        <v>583.44444444444446</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1823,7 +1827,7 @@
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>88.625</v>
+        <v>78.777777777777771</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1835,11 +1839,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>2531</v>
+        <v>2720</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>316.375</v>
+        <v>302.22222222222223</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1851,11 +1855,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>4523</v>
+        <v>4857</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>565.375</v>
+        <v>539.66666666666663</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1867,11 +1871,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>2654</v>
+        <v>2881</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>331.75</v>
+        <v>320.11111111111109</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1883,11 +1887,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>2145</v>
+        <v>2394</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>268.125</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1899,11 +1903,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>52.25</v>
+        <v>48.555555555555557</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1915,11 +1919,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>829</v>
+        <v>902</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>103.625</v>
+        <v>100.22222222222223</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1931,11 +1935,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>67.375</v>
+        <v>60.666666666666664</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1947,11 +1951,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>440</v>
+        <v>467</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>55</v>
+        <v>51.888888888888886</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1975,11 +1979,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>1.625</v>
+        <v>2.2222222222222223</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2036,19 +2040,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>208630</v>
+        <v>237806</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>206619</v>
+        <v>235631</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>26078.75</v>
+        <v>26422.888888888891</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>573732.5</v>
+        <v>581303.55555555562</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2056,11 +2060,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.32145239845121049</v>
+        <v>0.36640612120063543</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-440393</v>
+        <v>-411217</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2096,7 +2100,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>2011</v>
+        <v>2175</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2104,7 +2108,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2112,11 +2116,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39BA4D2C-5DB1-48FB-8F18-389FAE966CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268D22F9-AA54-4820-BC5C-234BB7FE00A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -450,6 +450,7 @@
       <sheetName val="INVENTARIO NACIONAL 12-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 13-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -465,36 +466,37 @@
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
-      <sheetData sheetId="10">
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11">
         <row r="3">
           <cell r="G3">
-            <v>237806</v>
+            <v>263164</v>
           </cell>
           <cell r="H3">
-            <v>235631</v>
+            <v>260939</v>
           </cell>
           <cell r="I3">
-            <v>26422.888888888891</v>
+            <v>26316.400000000001</v>
           </cell>
           <cell r="J3">
-            <v>581303.55555555562</v>
+            <v>578960.80000000005</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.36640612120063543</v>
+            <v>0.40547715566320452</v>
           </cell>
           <cell r="M3">
-            <v>-411217</v>
+            <v>-385859</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>10703</v>
+            <v>11756</v>
           </cell>
           <cell r="D4">
-            <v>1189.2222222222222</v>
+            <v>1175.5999999999999</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -517,44 +519,44 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>789</v>
+            <v>823</v>
           </cell>
           <cell r="D5">
-            <v>87.666666666666671</v>
+            <v>82.3</v>
           </cell>
           <cell r="G5">
-            <v>2175</v>
+            <v>2225</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
           </cell>
           <cell r="I5">
-            <v>46248</v>
+            <v>46251</v>
           </cell>
           <cell r="J5">
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>9</v>
+            <v>10</v>
           </cell>
           <cell r="L5">
-            <v>12</v>
+            <v>11</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>4207</v>
+            <v>4634</v>
           </cell>
           <cell r="D6">
-            <v>467.44444444444446</v>
+            <v>463.4</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>967</v>
+            <v>1004</v>
           </cell>
           <cell r="D7">
-            <v>107.44444444444444</v>
+            <v>100.4</v>
           </cell>
         </row>
         <row r="8">
@@ -562,239 +564,239 @@
             <v>90</v>
           </cell>
           <cell r="D8">
-            <v>10</v>
+            <v>9</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>13213</v>
+            <v>14437</v>
           </cell>
           <cell r="D9">
-            <v>1468.1111111111111</v>
+            <v>1443.7</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>1361</v>
+            <v>1441</v>
           </cell>
           <cell r="D10">
-            <v>151.22222222222223</v>
+            <v>144.1</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>3094</v>
+            <v>3157</v>
           </cell>
           <cell r="D11">
-            <v>343.77777777777777</v>
+            <v>315.7</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>6814</v>
+            <v>7180</v>
           </cell>
           <cell r="D12">
-            <v>757.11111111111109</v>
+            <v>718</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>3258</v>
+            <v>3422</v>
           </cell>
           <cell r="D13">
-            <v>362</v>
+            <v>342.2</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>32304</v>
+            <v>36510</v>
           </cell>
           <cell r="D14">
-            <v>3589.3333333333335</v>
+            <v>3651</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>20652</v>
+            <v>24080</v>
           </cell>
           <cell r="D15">
-            <v>2294.6666666666665</v>
+            <v>2408</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>20404</v>
+            <v>23292</v>
           </cell>
           <cell r="D16">
-            <v>2267.1111111111113</v>
+            <v>2329.1999999999998</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>24407</v>
+            <v>27946</v>
           </cell>
           <cell r="D17">
-            <v>2711.8888888888887</v>
+            <v>2794.6</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>354</v>
+            <v>355</v>
           </cell>
           <cell r="D18">
-            <v>39.333333333333336</v>
+            <v>35.5</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>830</v>
+            <v>1063</v>
           </cell>
           <cell r="D19">
-            <v>92.222222222222229</v>
+            <v>106.3</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>1168</v>
+            <v>1442</v>
           </cell>
           <cell r="D20">
-            <v>129.77777777777777</v>
+            <v>144.19999999999999</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>1002</v>
+            <v>1311</v>
           </cell>
           <cell r="D21">
-            <v>111.33333333333333</v>
+            <v>131.1</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>2194</v>
+            <v>2384</v>
           </cell>
           <cell r="D22">
-            <v>243.77777777777777</v>
+            <v>238.4</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>1252</v>
+            <v>1298</v>
           </cell>
           <cell r="D23">
-            <v>139.11111111111111</v>
+            <v>129.80000000000001</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>4679</v>
+            <v>5003</v>
           </cell>
           <cell r="D24">
-            <v>519.88888888888891</v>
+            <v>500.3</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>7208</v>
+            <v>7763</v>
           </cell>
           <cell r="D25">
-            <v>800.88888888888891</v>
+            <v>776.3</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="D26">
-            <v>0</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>582</v>
+            <v>1500</v>
           </cell>
           <cell r="D27">
-            <v>64.666666666666671</v>
+            <v>150</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>6157</v>
+            <v>6782</v>
           </cell>
           <cell r="D28">
-            <v>684.11111111111109</v>
+            <v>678.2</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>10752</v>
+            <v>11052</v>
           </cell>
           <cell r="D29">
-            <v>1194.6666666666667</v>
+            <v>1105.2</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>4631</v>
+            <v>4932</v>
           </cell>
           <cell r="D30">
-            <v>514.55555555555554</v>
+            <v>493.2</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>3386</v>
+            <v>3391</v>
           </cell>
           <cell r="D31">
-            <v>376.22222222222223</v>
+            <v>339.1</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>1164</v>
+            <v>1326</v>
           </cell>
           <cell r="D32">
-            <v>129.33333333333334</v>
+            <v>132.6</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>1048</v>
+            <v>1192</v>
           </cell>
           <cell r="D33">
-            <v>116.44444444444444</v>
+            <v>119.2</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>5670</v>
+            <v>6145</v>
           </cell>
           <cell r="D34">
-            <v>630</v>
+            <v>614.5</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>6252</v>
+            <v>6715</v>
           </cell>
           <cell r="D35">
-            <v>694.66666666666663</v>
+            <v>671.5</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>8184</v>
+            <v>8316</v>
           </cell>
           <cell r="D36">
-            <v>909.33333333333337</v>
+            <v>831.6</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>5496</v>
+            <v>5818</v>
           </cell>
           <cell r="D37">
-            <v>610.66666666666663</v>
+            <v>581.79999999999995</v>
           </cell>
         </row>
         <row r="38">
@@ -802,15 +804,15 @@
             <v>175</v>
           </cell>
           <cell r="D38">
-            <v>19.444444444444443</v>
+            <v>17.5</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>5251</v>
+            <v>5701</v>
           </cell>
           <cell r="D39">
-            <v>583.44444444444446</v>
+            <v>570.1</v>
           </cell>
         </row>
         <row r="40">
@@ -818,55 +820,55 @@
             <v>709</v>
           </cell>
           <cell r="D40">
-            <v>78.777777777777771</v>
+            <v>70.900000000000006</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>2720</v>
+            <v>3036</v>
           </cell>
           <cell r="D41">
-            <v>302.22222222222223</v>
+            <v>303.60000000000002</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>4857</v>
+            <v>5285</v>
           </cell>
           <cell r="D42">
-            <v>539.66666666666663</v>
+            <v>528.5</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>2881</v>
+            <v>3223</v>
           </cell>
           <cell r="D43">
-            <v>320.11111111111109</v>
+            <v>322.3</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>2394</v>
+            <v>2734</v>
           </cell>
           <cell r="D44">
-            <v>266</v>
+            <v>273.39999999999998</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>437</v>
+            <v>446</v>
           </cell>
           <cell r="D45">
-            <v>48.555555555555557</v>
+            <v>44.6</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>902</v>
+            <v>933</v>
           </cell>
           <cell r="D46">
-            <v>100.22222222222223</v>
+            <v>93.3</v>
           </cell>
         </row>
         <row r="47">
@@ -874,7 +876,7 @@
             <v>546</v>
           </cell>
           <cell r="D47">
-            <v>60.666666666666664</v>
+            <v>54.6</v>
           </cell>
         </row>
         <row r="48">
@@ -882,7 +884,7 @@
             <v>467</v>
           </cell>
           <cell r="D48">
-            <v>51.888888888888886</v>
+            <v>46.7</v>
           </cell>
         </row>
         <row r="49">
@@ -895,14 +897,14 @@
         </row>
         <row r="50">
           <cell r="C50">
-            <v>20</v>
+            <v>24</v>
           </cell>
           <cell r="D50">
-            <v>2.2222222222222223</v>
+            <v>2.4</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1247,11 +1249,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>10703</v>
+        <v>11756</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1189.2222222222222</v>
+        <v>1175.5999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1263,11 +1265,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>789</v>
+        <v>823</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>87.666666666666671</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,11 +1281,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>4207</v>
+        <v>4634</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>467.44444444444446</v>
+        <v>463.4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1295,11 +1297,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>967</v>
+        <v>1004</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>107.44444444444444</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1315,7 +1317,7 @@
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1327,11 +1329,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>13213</v>
+        <v>14437</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1468.1111111111111</v>
+        <v>1443.7</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1343,11 +1345,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>1361</v>
+        <v>1441</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>151.22222222222223</v>
+        <v>144.1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1359,11 +1361,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>3094</v>
+        <v>3157</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>343.77777777777777</v>
+        <v>315.7</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1375,11 +1377,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>6814</v>
+        <v>7180</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>757.11111111111109</v>
+        <v>718</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1391,11 +1393,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>3258</v>
+        <v>3422</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>362</v>
+        <v>342.2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1407,11 +1409,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>32304</v>
+        <v>36510</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3589.3333333333335</v>
+        <v>3651</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1423,11 +1425,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>20652</v>
+        <v>24080</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2294.6666666666665</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1439,11 +1441,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>20404</v>
+        <v>23292</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2267.1111111111113</v>
+        <v>2329.1999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1455,11 +1457,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>24407</v>
+        <v>27946</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2711.8888888888887</v>
+        <v>2794.6</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1471,11 +1473,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>39.333333333333336</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1487,11 +1489,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$19</f>
-        <v>830</v>
+        <v>1063</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>92.222222222222229</v>
+        <v>106.3</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1503,11 +1505,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$20</f>
-        <v>1168</v>
+        <v>1442</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>129.77777777777777</v>
+        <v>144.19999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1519,11 +1521,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$21</f>
-        <v>1002</v>
+        <v>1311</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>111.33333333333333</v>
+        <v>131.1</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1535,11 +1537,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>2194</v>
+        <v>2384</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>243.77777777777777</v>
+        <v>238.4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1551,11 +1553,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>1252</v>
+        <v>1298</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>139.11111111111111</v>
+        <v>129.80000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1567,11 +1569,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>4679</v>
+        <v>5003</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>519.88888888888891</v>
+        <v>500.3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1583,11 +1585,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>7208</v>
+        <v>7763</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>800.88888888888891</v>
+        <v>776.3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1599,11 +1601,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1615,11 +1617,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>582</v>
+        <v>1500</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>64.666666666666671</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1631,11 +1633,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>6157</v>
+        <v>6782</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>684.11111111111109</v>
+        <v>678.2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1647,11 +1649,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>10752</v>
+        <v>11052</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>1194.6666666666667</v>
+        <v>1105.2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1663,11 +1665,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>4631</v>
+        <v>4932</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>514.55555555555554</v>
+        <v>493.2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1679,11 +1681,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>3386</v>
+        <v>3391</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>376.22222222222223</v>
+        <v>339.1</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1695,11 +1697,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1164</v>
+        <v>1326</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>129.33333333333334</v>
+        <v>132.6</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1711,11 +1713,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>1048</v>
+        <v>1192</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>116.44444444444444</v>
+        <v>119.2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1727,11 +1729,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>5670</v>
+        <v>6145</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>630</v>
+        <v>614.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1743,11 +1745,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>6252</v>
+        <v>6715</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>694.66666666666663</v>
+        <v>671.5</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1759,11 +1761,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>8184</v>
+        <v>8316</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>909.33333333333337</v>
+        <v>831.6</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1775,11 +1777,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>5496</v>
+        <v>5818</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>610.66666666666663</v>
+        <v>581.79999999999995</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1795,7 +1797,7 @@
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>19.444444444444443</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1807,11 +1809,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>5251</v>
+        <v>5701</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>583.44444444444446</v>
+        <v>570.1</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1827,7 +1829,7 @@
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>78.777777777777771</v>
+        <v>70.900000000000006</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1839,11 +1841,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>2720</v>
+        <v>3036</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>302.22222222222223</v>
+        <v>303.60000000000002</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1855,11 +1857,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>4857</v>
+        <v>5285</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>539.66666666666663</v>
+        <v>528.5</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1871,11 +1873,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>2881</v>
+        <v>3223</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>320.11111111111109</v>
+        <v>322.3</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1887,11 +1889,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>2394</v>
+        <v>2734</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>266</v>
+        <v>273.39999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1903,11 +1905,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>48.555555555555557</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1919,11 +1921,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>902</v>
+        <v>933</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>100.22222222222223</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1939,7 +1941,7 @@
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>60.666666666666664</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1955,7 +1957,7 @@
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>51.888888888888886</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1979,11 +1981,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>2.2222222222222223</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2040,19 +2042,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>237806</v>
+        <v>263164</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>235631</v>
+        <v>260939</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>26422.888888888891</v>
+        <v>26316.400000000001</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>581303.55555555562</v>
+        <v>578960.80000000005</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2060,11 +2062,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.36640612120063543</v>
+        <v>0.40547715566320452</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-411217</v>
+        <v>-385859</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2100,7 +2102,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>2175</v>
+        <v>2225</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2108,7 +2110,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2116,11 +2118,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268D22F9-AA54-4820-BC5C-234BB7FE00A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56467A7A-F3E9-4335-94C0-BB86503FDA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -451,6 +451,7 @@
       <sheetName val="INVENTARIO NACIONAL 13-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 18-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -467,36 +468,37 @@
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
-      <sheetData sheetId="11">
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12">
         <row r="3">
           <cell r="G3">
-            <v>263164</v>
+            <v>288295</v>
           </cell>
           <cell r="H3">
-            <v>260939</v>
+            <v>285950</v>
           </cell>
           <cell r="I3">
-            <v>26316.400000000001</v>
+            <v>26208.636363636364</v>
           </cell>
           <cell r="J3">
-            <v>578960.80000000005</v>
+            <v>576590</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.40547715566320452</v>
+            <v>0.44419843364564893</v>
           </cell>
           <cell r="M3">
-            <v>-385859</v>
+            <v>-360728</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>11756</v>
+            <v>12944</v>
           </cell>
           <cell r="D4">
-            <v>1175.5999999999999</v>
+            <v>1176.7272727272727</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -519,188 +521,188 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>823</v>
+            <v>903</v>
           </cell>
           <cell r="D5">
-            <v>82.3</v>
+            <v>82.090909090909093</v>
           </cell>
           <cell r="G5">
-            <v>2225</v>
+            <v>2345</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
           </cell>
           <cell r="I5">
-            <v>46251</v>
+            <v>46252</v>
           </cell>
           <cell r="J5">
             <v>46265</v>
           </cell>
           <cell r="K5">
+            <v>11</v>
+          </cell>
+          <cell r="L5">
             <v>10</v>
-          </cell>
-          <cell r="L5">
-            <v>11</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>4634</v>
+            <v>5279</v>
           </cell>
           <cell r="D6">
-            <v>463.4</v>
+            <v>479.90909090909093</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1004</v>
+            <v>1061</v>
           </cell>
           <cell r="D7">
-            <v>100.4</v>
+            <v>96.454545454545453</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>90</v>
+            <v>105</v>
           </cell>
           <cell r="D8">
-            <v>9</v>
+            <v>9.545454545454545</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>14437</v>
+            <v>15948</v>
           </cell>
           <cell r="D9">
-            <v>1443.7</v>
+            <v>1449.8181818181818</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>1441</v>
+            <v>1537</v>
           </cell>
           <cell r="D10">
-            <v>144.1</v>
+            <v>139.72727272727272</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>3157</v>
+            <v>3403</v>
           </cell>
           <cell r="D11">
-            <v>315.7</v>
+            <v>309.36363636363637</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>7180</v>
+            <v>7625</v>
           </cell>
           <cell r="D12">
-            <v>718</v>
+            <v>693.18181818181813</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>3422</v>
+            <v>3542</v>
           </cell>
           <cell r="D13">
-            <v>342.2</v>
+            <v>322</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>36510</v>
+            <v>39911</v>
           </cell>
           <cell r="D14">
-            <v>3651</v>
+            <v>3628.2727272727275</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>24080</v>
+            <v>26342</v>
           </cell>
           <cell r="D15">
-            <v>2408</v>
+            <v>2394.7272727272725</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>23292</v>
+            <v>25420</v>
           </cell>
           <cell r="D16">
-            <v>2329.1999999999998</v>
+            <v>2310.909090909091</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>27946</v>
+            <v>30373</v>
           </cell>
           <cell r="D17">
-            <v>2794.6</v>
+            <v>2761.181818181818</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>355</v>
+            <v>365</v>
           </cell>
           <cell r="D18">
-            <v>35.5</v>
+            <v>33.18181818181818</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>1063</v>
+            <v>1700</v>
           </cell>
           <cell r="D19">
-            <v>106.3</v>
+            <v>154.54545454545453</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>1442</v>
+            <v>2154</v>
           </cell>
           <cell r="D20">
-            <v>144.19999999999999</v>
+            <v>195.81818181818181</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>1311</v>
+            <v>2025</v>
           </cell>
           <cell r="D21">
-            <v>131.1</v>
+            <v>184.09090909090909</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>2384</v>
+            <v>2523</v>
           </cell>
           <cell r="D22">
-            <v>238.4</v>
+            <v>229.36363636363637</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>1298</v>
+            <v>1391</v>
           </cell>
           <cell r="D23">
-            <v>129.80000000000001</v>
+            <v>126.45454545454545</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>5003</v>
+            <v>5336</v>
           </cell>
           <cell r="D24">
-            <v>500.3</v>
+            <v>485.09090909090907</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>7763</v>
+            <v>8373</v>
           </cell>
           <cell r="D25">
-            <v>776.3</v>
+            <v>761.18181818181813</v>
           </cell>
         </row>
         <row r="26">
@@ -708,203 +710,203 @@
             <v>100</v>
           </cell>
           <cell r="D26">
-            <v>10</v>
+            <v>9.0909090909090917</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>1500</v>
+            <v>1682</v>
           </cell>
           <cell r="D27">
-            <v>150</v>
+            <v>152.90909090909091</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>6782</v>
+            <v>7434</v>
           </cell>
           <cell r="D28">
-            <v>678.2</v>
+            <v>675.81818181818187</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>11052</v>
+            <v>12107</v>
           </cell>
           <cell r="D29">
-            <v>1105.2</v>
+            <v>1100.6363636363637</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>4932</v>
+            <v>5311</v>
           </cell>
           <cell r="D30">
-            <v>493.2</v>
+            <v>482.81818181818181</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>3391</v>
+            <v>3730</v>
           </cell>
           <cell r="D31">
-            <v>339.1</v>
+            <v>339.09090909090907</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>1326</v>
+            <v>47</v>
           </cell>
           <cell r="D32">
-            <v>132.6</v>
+            <v>4.2727272727272725</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>1192</v>
+            <v>46</v>
           </cell>
           <cell r="D33">
-            <v>119.2</v>
+            <v>4.1818181818181817</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>6145</v>
+            <v>1424</v>
           </cell>
           <cell r="D34">
-            <v>614.5</v>
+            <v>129.45454545454547</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>6715</v>
+            <v>1357</v>
           </cell>
           <cell r="D35">
-            <v>671.5</v>
+            <v>123.36363636363636</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>8316</v>
+            <v>6422</v>
           </cell>
           <cell r="D36">
-            <v>831.6</v>
+            <v>583.81818181818187</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>5818</v>
+            <v>7168</v>
           </cell>
           <cell r="D37">
-            <v>581.79999999999995</v>
+            <v>651.63636363636363</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>175</v>
+            <v>8941</v>
           </cell>
           <cell r="D38">
-            <v>17.5</v>
+            <v>812.81818181818187</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>5701</v>
+            <v>6311</v>
           </cell>
           <cell r="D39">
-            <v>570.1</v>
+            <v>573.72727272727275</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>709</v>
+            <v>191</v>
           </cell>
           <cell r="D40">
-            <v>70.900000000000006</v>
+            <v>17.363636363636363</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>3036</v>
+            <v>6086</v>
           </cell>
           <cell r="D41">
-            <v>303.60000000000002</v>
+            <v>553.27272727272725</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>5285</v>
+            <v>712</v>
           </cell>
           <cell r="D42">
-            <v>528.5</v>
+            <v>64.727272727272734</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>3223</v>
+            <v>3447</v>
           </cell>
           <cell r="D43">
-            <v>322.3</v>
+            <v>313.36363636363637</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>2734</v>
+            <v>5851</v>
           </cell>
           <cell r="D44">
-            <v>273.39999999999998</v>
+            <v>531.90909090909088</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>446</v>
+            <v>3575</v>
           </cell>
           <cell r="D45">
-            <v>44.6</v>
+            <v>325</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>933</v>
+            <v>3107</v>
           </cell>
           <cell r="D46">
-            <v>93.3</v>
+            <v>282.45454545454544</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>546</v>
+            <v>506</v>
           </cell>
           <cell r="D47">
-            <v>54.6</v>
+            <v>46</v>
           </cell>
         </row>
         <row r="48">
           <cell r="C48">
-            <v>467</v>
+            <v>1021</v>
           </cell>
           <cell r="D48">
-            <v>46.7</v>
+            <v>92.818181818181813</v>
           </cell>
         </row>
         <row r="49">
           <cell r="C49">
-            <v>0</v>
+            <v>612</v>
           </cell>
           <cell r="D49">
-            <v>0</v>
+            <v>55.636363636363633</v>
           </cell>
         </row>
         <row r="50">
           <cell r="C50">
-            <v>24</v>
+            <v>476</v>
           </cell>
           <cell r="D50">
-            <v>2.4</v>
+            <v>43.272727272727273</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1249,11 +1251,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>11756</v>
+        <v>12944</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1175.5999999999999</v>
+        <v>1176.7272727272727</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1265,11 +1267,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>823</v>
+        <v>903</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>82.3</v>
+        <v>82.090909090909093</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1281,11 +1283,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>4634</v>
+        <v>5279</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>463.4</v>
+        <v>479.90909090909093</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1297,11 +1299,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1004</v>
+        <v>1061</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>100.4</v>
+        <v>96.454545454545453</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1313,11 +1315,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>9</v>
+        <v>9.545454545454545</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1329,11 +1331,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>14437</v>
+        <v>15948</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1443.7</v>
+        <v>1449.8181818181818</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1345,11 +1347,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>1441</v>
+        <v>1537</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>144.1</v>
+        <v>139.72727272727272</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1361,11 +1363,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>3157</v>
+        <v>3403</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>315.7</v>
+        <v>309.36363636363637</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1377,11 +1379,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>7180</v>
+        <v>7625</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>718</v>
+        <v>693.18181818181813</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1393,11 +1395,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>3422</v>
+        <v>3542</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>342.2</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1409,11 +1411,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>36510</v>
+        <v>39911</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3651</v>
+        <v>3628.2727272727275</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1425,11 +1427,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>24080</v>
+        <v>26342</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2408</v>
+        <v>2394.7272727272725</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1441,11 +1443,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>23292</v>
+        <v>25420</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2329.1999999999998</v>
+        <v>2310.909090909091</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1457,11 +1459,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>27946</v>
+        <v>30373</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2794.6</v>
+        <v>2761.181818181818</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1473,11 +1475,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>35.5</v>
+        <v>33.18181818181818</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1489,11 +1491,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$19</f>
-        <v>1063</v>
+        <v>1700</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>106.3</v>
+        <v>154.54545454545453</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1505,11 +1507,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$20</f>
-        <v>1442</v>
+        <v>2154</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>144.19999999999999</v>
+        <v>195.81818181818181</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1521,11 +1523,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$21</f>
-        <v>1311</v>
+        <v>2025</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>131.1</v>
+        <v>184.09090909090909</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1537,11 +1539,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>2384</v>
+        <v>2523</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>238.4</v>
+        <v>229.36363636363637</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1553,11 +1555,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>1298</v>
+        <v>1391</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>129.80000000000001</v>
+        <v>126.45454545454545</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1569,11 +1571,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>5003</v>
+        <v>5336</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>500.3</v>
+        <v>485.09090909090907</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1585,11 +1587,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>7763</v>
+        <v>8373</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>776.3</v>
+        <v>761.18181818181813</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1605,7 +1607,7 @@
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>10</v>
+        <v>9.0909090909090917</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1617,11 +1619,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>1500</v>
+        <v>1682</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>150</v>
+        <v>152.90909090909091</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1633,11 +1635,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>6782</v>
+        <v>7434</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>678.2</v>
+        <v>675.81818181818187</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1649,11 +1651,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>11052</v>
+        <v>12107</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>1105.2</v>
+        <v>1100.6363636363637</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1665,11 +1667,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>4932</v>
+        <v>5311</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>493.2</v>
+        <v>482.81818181818181</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1681,11 +1683,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>3391</v>
+        <v>3730</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>339.1</v>
+        <v>339.09090909090907</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1697,11 +1699,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1326</v>
+        <v>47</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>132.6</v>
+        <v>4.2727272727272725</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1713,11 +1715,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>1192</v>
+        <v>46</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>119.2</v>
+        <v>4.1818181818181817</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1729,11 +1731,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>6145</v>
+        <v>1424</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>614.5</v>
+        <v>129.45454545454547</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1745,11 +1747,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>6715</v>
+        <v>1357</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>671.5</v>
+        <v>123.36363636363636</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1761,11 +1763,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>8316</v>
+        <v>6422</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>831.6</v>
+        <v>583.81818181818187</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1777,11 +1779,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>5818</v>
+        <v>7168</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>581.79999999999995</v>
+        <v>651.63636363636363</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1793,11 +1795,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>175</v>
+        <v>8941</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>17.5</v>
+        <v>812.81818181818187</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1809,11 +1811,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>5701</v>
+        <v>6311</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>570.1</v>
+        <v>573.72727272727275</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1825,11 +1827,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>709</v>
+        <v>191</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>70.900000000000006</v>
+        <v>17.363636363636363</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1841,11 +1843,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>3036</v>
+        <v>6086</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>303.60000000000002</v>
+        <v>553.27272727272725</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1857,11 +1859,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>5285</v>
+        <v>712</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>528.5</v>
+        <v>64.727272727272734</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1873,11 +1875,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>3223</v>
+        <v>3447</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>322.3</v>
+        <v>313.36363636363637</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1889,11 +1891,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>2734</v>
+        <v>5851</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>273.39999999999998</v>
+        <v>531.90909090909088</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1905,11 +1907,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>446</v>
+        <v>3575</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>44.6</v>
+        <v>325</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1921,11 +1923,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>933</v>
+        <v>3107</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>93.3</v>
+        <v>282.45454545454544</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1937,11 +1939,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>546</v>
+        <v>506</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>54.6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1953,11 +1955,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>467</v>
+        <v>1021</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>46.7</v>
+        <v>92.818181818181813</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1967,11 +1969,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>0</v>
+        <v>55.636363636363633</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1981,11 +1983,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>24</v>
+        <v>476</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>2.4</v>
+        <v>43.272727272727273</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2042,19 +2044,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>263164</v>
+        <v>288295</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>260939</v>
+        <v>285950</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>26316.400000000001</v>
+        <v>26208.636363636364</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>578960.80000000005</v>
+        <v>576590</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2062,11 +2064,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.40547715566320452</v>
+        <v>0.44419843364564893</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-385859</v>
+        <v>-360728</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2102,7 +2104,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>2225</v>
+        <v>2345</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2110,7 +2112,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2118,11 +2120,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56467A7A-F3E9-4335-94C0-BB86503FDA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72A40CD-26E0-4B18-9774-0DA75DE07971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>FORECAST</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>Cremigurt Mora 150g</t>
+  </si>
+  <si>
+    <t>Cremigurt Power Piña Colada 150g</t>
+  </si>
+  <si>
+    <t>Cremigurt Power Dulce de leche 150g</t>
   </si>
 </sst>
 </file>
@@ -340,7 +346,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -363,12 +369,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -416,6 +435,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,6 +472,7 @@
       <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 18-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 19-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -469,36 +490,37 @@
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
-      <sheetData sheetId="12">
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13">
         <row r="3">
           <cell r="G3">
-            <v>288295</v>
+            <v>315548</v>
           </cell>
           <cell r="H3">
-            <v>285950</v>
+            <v>313016</v>
           </cell>
           <cell r="I3">
-            <v>26208.636363636364</v>
+            <v>26295.666666666668</v>
           </cell>
           <cell r="J3">
-            <v>576590</v>
+            <v>578504.66666666674</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.44419843364564893</v>
+            <v>0.48618924136740915</v>
           </cell>
           <cell r="M3">
-            <v>-360728</v>
+            <v>-333475</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>12944</v>
+            <v>13945</v>
           </cell>
           <cell r="D4">
-            <v>1176.7272727272727</v>
+            <v>1162.0833333333333</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -521,188 +543,188 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>903</v>
+            <v>997</v>
           </cell>
           <cell r="D5">
-            <v>82.090909090909093</v>
+            <v>83.083333333333329</v>
           </cell>
           <cell r="G5">
-            <v>2345</v>
+            <v>2532</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
           </cell>
           <cell r="I5">
-            <v>46252</v>
+            <v>46253</v>
           </cell>
           <cell r="J5">
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>11</v>
+            <v>12</v>
           </cell>
           <cell r="L5">
-            <v>10</v>
+            <v>9</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>5279</v>
+            <v>5593</v>
           </cell>
           <cell r="D6">
-            <v>479.90909090909093</v>
+            <v>466.08333333333331</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1061</v>
+            <v>1090</v>
           </cell>
           <cell r="D7">
-            <v>96.454545454545453</v>
+            <v>90.833333333333329</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>105</v>
+            <v>113</v>
           </cell>
           <cell r="D8">
-            <v>9.545454545454545</v>
+            <v>9.4166666666666661</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>15948</v>
+            <v>16767</v>
           </cell>
           <cell r="D9">
-            <v>1449.8181818181818</v>
+            <v>1397.25</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>1537</v>
+            <v>1661</v>
           </cell>
           <cell r="D10">
-            <v>139.72727272727272</v>
+            <v>138.41666666666666</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>3403</v>
+            <v>3691</v>
           </cell>
           <cell r="D11">
-            <v>309.36363636363637</v>
+            <v>307.58333333333331</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>7625</v>
+            <v>8552</v>
           </cell>
           <cell r="D12">
-            <v>693.18181818181813</v>
+            <v>712.66666666666663</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>3542</v>
+            <v>4013</v>
           </cell>
           <cell r="D13">
-            <v>322</v>
+            <v>334.41666666666669</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>39911</v>
+            <v>43335</v>
           </cell>
           <cell r="D14">
-            <v>3628.2727272727275</v>
+            <v>3611.25</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>26342</v>
+            <v>28511</v>
           </cell>
           <cell r="D15">
-            <v>2394.7272727272725</v>
+            <v>2375.9166666666665</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>25420</v>
+            <v>27524</v>
           </cell>
           <cell r="D16">
-            <v>2310.909090909091</v>
+            <v>2293.6666666666665</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>30373</v>
+            <v>33187</v>
           </cell>
           <cell r="D17">
-            <v>2761.181818181818</v>
+            <v>2765.5833333333335</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>365</v>
+            <v>385</v>
           </cell>
           <cell r="D18">
-            <v>33.18181818181818</v>
+            <v>32.083333333333336</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>1700</v>
+            <v>2468</v>
           </cell>
           <cell r="D19">
-            <v>154.54545454545453</v>
+            <v>205.66666666666666</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>2154</v>
+            <v>2949</v>
           </cell>
           <cell r="D20">
-            <v>195.81818181818181</v>
+            <v>245.75</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>2025</v>
+            <v>2795</v>
           </cell>
           <cell r="D21">
-            <v>184.09090909090909</v>
+            <v>232.91666666666666</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>2523</v>
+            <v>2764</v>
           </cell>
           <cell r="D22">
-            <v>229.36363636363637</v>
+            <v>230.33333333333334</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>1391</v>
+            <v>1577</v>
           </cell>
           <cell r="D23">
-            <v>126.45454545454545</v>
+            <v>131.41666666666666</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>5336</v>
+            <v>6005</v>
           </cell>
           <cell r="D24">
-            <v>485.09090909090907</v>
+            <v>500.41666666666669</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>8373</v>
+            <v>9413</v>
           </cell>
           <cell r="D25">
-            <v>761.18181818181813</v>
+            <v>784.41666666666663</v>
           </cell>
         </row>
         <row r="26">
@@ -710,127 +732,127 @@
             <v>100</v>
           </cell>
           <cell r="D26">
-            <v>9.0909090909090917</v>
+            <v>8.3333333333333339</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>1682</v>
+            <v>1704</v>
           </cell>
           <cell r="D27">
-            <v>152.90909090909091</v>
+            <v>142</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>7434</v>
+            <v>7963</v>
           </cell>
           <cell r="D28">
-            <v>675.81818181818187</v>
+            <v>663.58333333333337</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>12107</v>
+            <v>13000</v>
           </cell>
           <cell r="D29">
-            <v>1100.6363636363637</v>
+            <v>1083.3333333333333</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>5311</v>
+            <v>5922</v>
           </cell>
           <cell r="D30">
-            <v>482.81818181818181</v>
+            <v>493.5</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>3730</v>
+            <v>4298</v>
           </cell>
           <cell r="D31">
-            <v>339.09090909090907</v>
+            <v>358.16666666666669</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>47</v>
+            <v>234</v>
           </cell>
           <cell r="D32">
-            <v>4.2727272727272725</v>
+            <v>19.5</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>46</v>
+            <v>197</v>
           </cell>
           <cell r="D33">
-            <v>4.1818181818181817</v>
+            <v>16.416666666666668</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>1424</v>
+            <v>1581</v>
           </cell>
           <cell r="D34">
-            <v>129.45454545454547</v>
+            <v>131.75</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>1357</v>
+            <v>1531</v>
           </cell>
           <cell r="D35">
-            <v>123.36363636363636</v>
+            <v>127.58333333333333</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>6422</v>
+            <v>7053</v>
           </cell>
           <cell r="D36">
-            <v>583.81818181818187</v>
+            <v>587.75</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>7168</v>
+            <v>7865</v>
           </cell>
           <cell r="D37">
-            <v>651.63636363636363</v>
+            <v>655.41666666666663</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>8941</v>
+            <v>9825</v>
           </cell>
           <cell r="D38">
-            <v>812.81818181818187</v>
+            <v>818.75</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>6311</v>
+            <v>6846</v>
           </cell>
           <cell r="D39">
-            <v>573.72727272727275</v>
+            <v>570.5</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>191</v>
+            <v>298</v>
           </cell>
           <cell r="D40">
-            <v>17.363636363636363</v>
+            <v>24.833333333333332</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>6086</v>
+            <v>6861</v>
           </cell>
           <cell r="D41">
-            <v>553.27272727272725</v>
+            <v>571.75</v>
           </cell>
         </row>
         <row r="42">
@@ -838,55 +860,55 @@
             <v>712</v>
           </cell>
           <cell r="D42">
-            <v>64.727272727272734</v>
+            <v>59.333333333333336</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>3447</v>
+            <v>3598</v>
           </cell>
           <cell r="D43">
-            <v>313.36363636363637</v>
+            <v>299.83333333333331</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>5851</v>
+            <v>6237</v>
           </cell>
           <cell r="D44">
-            <v>531.90909090909088</v>
+            <v>519.75</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>3575</v>
+            <v>3758</v>
           </cell>
           <cell r="D45">
-            <v>325</v>
+            <v>313.16666666666669</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>3107</v>
+            <v>3314</v>
           </cell>
           <cell r="D46">
-            <v>282.45454545454544</v>
+            <v>276.16666666666669</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>506</v>
+            <v>554</v>
           </cell>
           <cell r="D47">
-            <v>46</v>
+            <v>46.166666666666664</v>
           </cell>
         </row>
         <row r="48">
           <cell r="C48">
-            <v>1021</v>
+            <v>1076</v>
           </cell>
           <cell r="D48">
-            <v>92.818181818181813</v>
+            <v>89.666666666666671</v>
           </cell>
         </row>
         <row r="49">
@@ -894,19 +916,19 @@
             <v>612</v>
           </cell>
           <cell r="D49">
-            <v>55.636363636363633</v>
+            <v>51</v>
           </cell>
         </row>
         <row r="50">
           <cell r="C50">
-            <v>476</v>
+            <v>516</v>
           </cell>
           <cell r="D50">
-            <v>43.272727272727273</v>
+            <v>43</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1209,7 +1231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55CD20E1-8530-482E-BAF2-454F195C9DA1}">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="10"/>
@@ -1251,11 +1273,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>12944</v>
+        <v>13945</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1176.7272727272727</v>
+        <v>1162.0833333333333</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1267,11 +1289,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>903</v>
+        <v>997</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>82.090909090909093</v>
+        <v>83.083333333333329</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1283,11 +1305,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>5279</v>
+        <v>5593</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>479.90909090909093</v>
+        <v>466.08333333333331</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1299,11 +1321,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1061</v>
+        <v>1090</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>96.454545454545453</v>
+        <v>90.833333333333329</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1315,11 +1337,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>9.545454545454545</v>
+        <v>9.4166666666666661</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1331,11 +1353,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>15948</v>
+        <v>16767</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1449.8181818181818</v>
+        <v>1397.25</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1347,11 +1369,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>1537</v>
+        <v>1661</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>139.72727272727272</v>
+        <v>138.41666666666666</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1363,11 +1385,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>3403</v>
+        <v>3691</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>309.36363636363637</v>
+        <v>307.58333333333331</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1379,11 +1401,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>7625</v>
+        <v>8552</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>693.18181818181813</v>
+        <v>712.66666666666663</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1395,11 +1417,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>3542</v>
+        <v>4013</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>322</v>
+        <v>334.41666666666669</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1411,11 +1433,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>39911</v>
+        <v>43335</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3628.2727272727275</v>
+        <v>3611.25</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1427,11 +1449,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>26342</v>
+        <v>28511</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2394.7272727272725</v>
+        <v>2375.9166666666665</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1443,11 +1465,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>25420</v>
+        <v>27524</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2310.909090909091</v>
+        <v>2293.6666666666665</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1459,11 +1481,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>30373</v>
+        <v>33187</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2761.181818181818</v>
+        <v>2765.5833333333335</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1475,11 +1497,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>33.18181818181818</v>
+        <v>32.083333333333336</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1491,11 +1513,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$19</f>
-        <v>1700</v>
+        <v>2468</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>154.54545454545453</v>
+        <v>205.66666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1507,11 +1529,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$20</f>
-        <v>2154</v>
+        <v>2949</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>195.81818181818181</v>
+        <v>245.75</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1523,11 +1545,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$21</f>
-        <v>2025</v>
+        <v>2795</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>184.09090909090909</v>
+        <v>232.91666666666666</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1539,11 +1561,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>2523</v>
+        <v>2764</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>229.36363636363637</v>
+        <v>230.33333333333334</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1555,11 +1577,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>1391</v>
+        <v>1577</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>126.45454545454545</v>
+        <v>131.41666666666666</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1571,11 +1593,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>5336</v>
+        <v>6005</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>485.09090909090907</v>
+        <v>500.41666666666669</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1587,11 +1609,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>8373</v>
+        <v>9413</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>761.18181818181813</v>
+        <v>784.41666666666663</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1607,7 +1629,7 @@
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>9.0909090909090917</v>
+        <v>8.3333333333333339</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1619,11 +1641,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>1682</v>
+        <v>1704</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>152.90909090909091</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1635,11 +1657,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>7434</v>
+        <v>7963</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>675.81818181818187</v>
+        <v>663.58333333333337</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1651,11 +1673,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>12107</v>
+        <v>13000</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>1100.6363636363637</v>
+        <v>1083.3333333333333</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1667,11 +1689,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>5311</v>
+        <v>5922</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>482.81818181818181</v>
+        <v>493.5</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1683,315 +1705,347 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>3730</v>
+        <v>4298</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>339.09090909090907</v>
+        <v>358.16666666666669</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="15">
-        <v>131700</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>29</v>
+        <v>131154</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>59</v>
       </c>
       <c r="C30" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>47</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!$C$32</f>
+        <v>234</v>
       </c>
       <c r="D30" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>4.2727272727272725</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$32</f>
+        <v>19.5</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="15">
-        <v>131701</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>30</v>
+        <v>131155</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>60</v>
       </c>
       <c r="C31" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>46</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!$C$33</f>
+        <v>197</v>
       </c>
       <c r="D31" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>4.1818181818181817</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$33</f>
+        <v>16.416666666666668</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="15">
-        <v>132150</v>
+        <v>131700</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C32" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>1424</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
+        <v>234</v>
       </c>
       <c r="D32" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>129.45454545454547</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
+        <v>19.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="15">
-        <v>132151</v>
+        <v>131701</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C33" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>1357</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
+        <v>197</v>
       </c>
       <c r="D33" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>123.36363636363636</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
+        <v>16.416666666666668</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="15">
-        <v>132152</v>
+        <v>132150</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C34" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>6422</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
+        <v>1581</v>
       </c>
       <c r="D34" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>583.81818181818187</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
+        <v>131.75</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="15">
-        <v>132153</v>
+        <v>132151</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C35" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>7168</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
+        <v>1531</v>
       </c>
       <c r="D35" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>651.63636363636363</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
+        <v>127.58333333333333</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="15">
-        <v>140230</v>
+        <v>132152</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C36" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>8941</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
+        <v>7053</v>
       </c>
       <c r="D36" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>812.81818181818187</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
+        <v>587.75</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="15">
-        <v>140231</v>
+        <v>132153</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C37" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>6311</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
+        <v>7865</v>
       </c>
       <c r="D37" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>573.72727272727275</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
+        <v>655.41666666666663</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
-        <v>140232</v>
+        <v>140230</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C38" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>191</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
+        <v>9825</v>
       </c>
       <c r="D38" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>17.363636363636363</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
+        <v>818.75</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="15">
-        <v>150360</v>
+        <v>140231</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C39" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>6086</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
+        <v>6846</v>
       </c>
       <c r="D39" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>553.27272727272725</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
+        <v>570.5</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="15">
+        <v>140232</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="13">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
+        <v>298</v>
+      </c>
+      <c r="D40" s="12">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
+        <v>24.833333333333332</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="15">
+        <v>150360</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="13">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
+        <v>6861</v>
+      </c>
+      <c r="D41" s="12">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
+        <v>571.75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="15">
         <v>150361</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B42" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="13">
+      <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
         <v>712</v>
       </c>
-      <c r="D40" s="12">
+      <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>64.727272727272734</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="15">
-        <v>150362</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>3447</v>
-      </c>
-      <c r="D41" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>313.36363636363637</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="15">
-        <v>150363</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>5851</v>
-      </c>
-      <c r="D42" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>531.90909090909088</v>
+        <v>59.333333333333336</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="15">
-        <v>151500</v>
+        <v>150362</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C43" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>3575</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
+        <v>3598</v>
       </c>
       <c r="D43" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>325</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
+        <v>299.83333333333331</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="15">
-        <v>151501</v>
+        <v>150363</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C44" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>3107</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
+        <v>6237</v>
       </c>
       <c r="D44" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>282.45454545454544</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
+        <v>519.75</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="15">
-        <v>151502</v>
+        <v>151500</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C45" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>506</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
+        <v>3758</v>
       </c>
       <c r="D45" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>46</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
+        <v>313.16666666666669</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="15">
+        <v>151501</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="13">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
+        <v>3314</v>
+      </c>
+      <c r="D46" s="12">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
+        <v>276.16666666666669</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="15">
+        <v>151502</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="13">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
+        <v>554</v>
+      </c>
+      <c r="D47" s="12">
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
+        <v>46.166666666666664</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="15">
         <v>151503</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B48" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="13">
+      <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>1021</v>
-      </c>
-      <c r="D46" s="12">
+        <v>1076</v>
+      </c>
+      <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>92.818181818181813</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
-      <c r="B47" s="8" t="s">
+        <v>89.666666666666671</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="15"/>
+      <c r="B49" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="13">
+      <c r="C49" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
         <v>612</v>
       </c>
-      <c r="D47" s="12">
+      <c r="D49" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>55.636363636363633</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="15"/>
-      <c r="B48" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="15"/>
+      <c r="B50" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="13">
+      <c r="C50" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>476</v>
-      </c>
-      <c r="D48" s="12">
+        <v>516</v>
+      </c>
+      <c r="D50" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>43.272727272727273</v>
-      </c>
-    </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C49" s="11"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C51" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2044,19 +2098,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>288295</v>
+        <v>315548</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>285950</v>
+        <v>313016</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>26208.636363636364</v>
+        <v>26295.666666666668</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>576590</v>
+        <v>578504.66666666674</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2064,11 +2118,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.44419843364564893</v>
+        <v>0.48618924136740915</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-360728</v>
+        <v>-333475</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2104,7 +2158,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>2345</v>
+        <v>2532</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2112,7 +2166,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2120,11 +2174,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72A40CD-26E0-4B18-9774-0DA75DE07971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099BF8C0-6BB3-44F7-9D31-C4888B6FE34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -432,10 +432,10 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -473,6 +473,8 @@
       <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 18-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 19-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 19-08-26-2"/>
+      <sheetName val="INVENTARIO NACIONAL 20-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -491,36 +493,38 @@
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
-      <sheetData sheetId="13">
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15">
         <row r="3">
           <cell r="G3">
-            <v>315548</v>
+            <v>342446</v>
           </cell>
           <cell r="H3">
-            <v>313016</v>
+            <v>339790</v>
           </cell>
           <cell r="I3">
-            <v>26295.666666666668</v>
+            <v>26342</v>
           </cell>
           <cell r="J3">
-            <v>578504.66666666674</v>
+            <v>579524</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.48618924136740915</v>
+            <v>0.52763307309602281</v>
           </cell>
           <cell r="M3">
-            <v>-333475</v>
+            <v>-306577</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>13945</v>
+            <v>14933</v>
           </cell>
           <cell r="D4">
-            <v>1162.0833333333333</v>
+            <v>1148.6923076923076</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -543,188 +547,188 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>997</v>
+            <v>1083</v>
           </cell>
           <cell r="D5">
-            <v>83.083333333333329</v>
+            <v>83.307692307692307</v>
           </cell>
           <cell r="G5">
-            <v>2532</v>
+            <v>2656</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
           </cell>
           <cell r="I5">
-            <v>46253</v>
+            <v>46254</v>
           </cell>
           <cell r="J5">
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>12</v>
+            <v>13</v>
           </cell>
           <cell r="L5">
-            <v>9</v>
+            <v>8</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>5593</v>
+            <v>6069</v>
           </cell>
           <cell r="D6">
-            <v>466.08333333333331</v>
+            <v>466.84615384615387</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1090</v>
+            <v>1181</v>
           </cell>
           <cell r="D7">
-            <v>90.833333333333329</v>
+            <v>90.84615384615384</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>113</v>
+            <v>131</v>
           </cell>
           <cell r="D8">
-            <v>9.4166666666666661</v>
+            <v>10.076923076923077</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>16767</v>
+            <v>17712</v>
           </cell>
           <cell r="D9">
-            <v>1397.25</v>
+            <v>1362.4615384615386</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>1661</v>
+            <v>1821</v>
           </cell>
           <cell r="D10">
-            <v>138.41666666666666</v>
+            <v>140.07692307692307</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>3691</v>
+            <v>4219</v>
           </cell>
           <cell r="D11">
-            <v>307.58333333333331</v>
+            <v>324.53846153846155</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>8552</v>
+            <v>9468</v>
           </cell>
           <cell r="D12">
-            <v>712.66666666666663</v>
+            <v>728.30769230769226</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>4013</v>
+            <v>4480</v>
           </cell>
           <cell r="D13">
-            <v>334.41666666666669</v>
+            <v>344.61538461538464</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>43335</v>
+            <v>46505</v>
           </cell>
           <cell r="D14">
-            <v>3611.25</v>
+            <v>3577.3076923076924</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>28511</v>
+            <v>30586</v>
           </cell>
           <cell r="D15">
-            <v>2375.9166666666665</v>
+            <v>2352.7692307692309</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>27524</v>
+            <v>29622</v>
           </cell>
           <cell r="D16">
-            <v>2293.6666666666665</v>
+            <v>2278.6153846153848</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>33187</v>
+            <v>35532</v>
           </cell>
           <cell r="D17">
-            <v>2765.5833333333335</v>
+            <v>2733.2307692307691</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>385</v>
+            <v>392</v>
           </cell>
           <cell r="D18">
-            <v>32.083333333333336</v>
+            <v>30.153846153846153</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>2468</v>
+            <v>3327</v>
           </cell>
           <cell r="D19">
-            <v>205.66666666666666</v>
+            <v>255.92307692307693</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>2949</v>
+            <v>3865</v>
           </cell>
           <cell r="D20">
-            <v>245.75</v>
+            <v>297.30769230769232</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>2795</v>
+            <v>3717</v>
           </cell>
           <cell r="D21">
-            <v>232.91666666666666</v>
+            <v>285.92307692307691</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>2764</v>
+            <v>3028</v>
           </cell>
           <cell r="D22">
-            <v>230.33333333333334</v>
+            <v>232.92307692307693</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>1577</v>
+            <v>1771</v>
           </cell>
           <cell r="D23">
-            <v>131.41666666666666</v>
+            <v>136.23076923076923</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>6005</v>
+            <v>6553</v>
           </cell>
           <cell r="D24">
-            <v>500.41666666666669</v>
+            <v>504.07692307692309</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>9413</v>
+            <v>10172</v>
           </cell>
           <cell r="D25">
-            <v>784.41666666666663</v>
+            <v>782.46153846153845</v>
           </cell>
         </row>
         <row r="26">
@@ -732,7 +736,7 @@
             <v>100</v>
           </cell>
           <cell r="D26">
-            <v>8.3333333333333339</v>
+            <v>7.6923076923076925</v>
           </cell>
         </row>
         <row r="27">
@@ -740,119 +744,119 @@
             <v>1704</v>
           </cell>
           <cell r="D27">
-            <v>142</v>
+            <v>131.07692307692307</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>7963</v>
+            <v>8332</v>
           </cell>
           <cell r="D28">
-            <v>663.58333333333337</v>
+            <v>640.92307692307691</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>13000</v>
+            <v>13836</v>
           </cell>
           <cell r="D29">
-            <v>1083.3333333333333</v>
+            <v>1064.3076923076924</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>5922</v>
+            <v>6527</v>
           </cell>
           <cell r="D30">
-            <v>493.5</v>
+            <v>502.07692307692309</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>4298</v>
+            <v>4629</v>
           </cell>
           <cell r="D31">
-            <v>358.16666666666669</v>
+            <v>356.07692307692309</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>234</v>
+            <v>417</v>
           </cell>
           <cell r="D32">
-            <v>19.5</v>
+            <v>32.07692307692308</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>197</v>
+            <v>380</v>
           </cell>
           <cell r="D33">
-            <v>16.416666666666668</v>
+            <v>29.23076923076923</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>1581</v>
+            <v>1660</v>
           </cell>
           <cell r="D34">
-            <v>131.75</v>
+            <v>127.69230769230769</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>1531</v>
+            <v>1695</v>
           </cell>
           <cell r="D35">
-            <v>127.58333333333333</v>
+            <v>130.38461538461539</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>7053</v>
+            <v>7926</v>
           </cell>
           <cell r="D36">
-            <v>587.75</v>
+            <v>609.69230769230774</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>7865</v>
+            <v>8479</v>
           </cell>
           <cell r="D37">
-            <v>655.41666666666663</v>
+            <v>652.23076923076928</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>9825</v>
+            <v>10798</v>
           </cell>
           <cell r="D38">
-            <v>818.75</v>
+            <v>830.61538461538464</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>6846</v>
+            <v>7479</v>
           </cell>
           <cell r="D39">
-            <v>570.5</v>
+            <v>575.30769230769226</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>298</v>
+            <v>634</v>
           </cell>
           <cell r="D40">
-            <v>24.833333333333332</v>
+            <v>48.769230769230766</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>6861</v>
+            <v>7324</v>
           </cell>
           <cell r="D41">
-            <v>571.75</v>
+            <v>563.38461538461536</v>
           </cell>
         </row>
         <row r="42">
@@ -860,75 +864,75 @@
             <v>712</v>
           </cell>
           <cell r="D42">
-            <v>59.333333333333336</v>
+            <v>54.769230769230766</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>3598</v>
+            <v>3853</v>
           </cell>
           <cell r="D43">
-            <v>299.83333333333331</v>
+            <v>296.38461538461536</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>6237</v>
+            <v>6621</v>
           </cell>
           <cell r="D44">
-            <v>519.75</v>
+            <v>509.30769230769232</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>3758</v>
+            <v>3943</v>
           </cell>
           <cell r="D45">
-            <v>313.16666666666669</v>
+            <v>303.30769230769232</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>3314</v>
+            <v>3534</v>
           </cell>
           <cell r="D46">
-            <v>276.16666666666669</v>
+            <v>271.84615384615387</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>554</v>
+            <v>600</v>
           </cell>
           <cell r="D47">
-            <v>46.166666666666664</v>
+            <v>46.153846153846153</v>
           </cell>
         </row>
         <row r="48">
           <cell r="C48">
-            <v>1076</v>
+            <v>1213</v>
           </cell>
           <cell r="D48">
-            <v>89.666666666666671</v>
+            <v>93.307692307692307</v>
           </cell>
         </row>
         <row r="49">
           <cell r="C49">
-            <v>612</v>
+            <v>668</v>
           </cell>
           <cell r="D49">
-            <v>51</v>
+            <v>51.384615384615387</v>
           </cell>
         </row>
         <row r="50">
           <cell r="C50">
-            <v>516</v>
+            <v>532</v>
           </cell>
           <cell r="D50">
-            <v>43</v>
+            <v>40.92307692307692</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="14"/>
+      <sheetData sheetId="16"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1273,11 +1277,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>13945</v>
+        <v>14933</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1162.0833333333333</v>
+        <v>1148.6923076923076</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1289,11 +1293,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>997</v>
+        <v>1083</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>83.083333333333329</v>
+        <v>83.307692307692307</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1305,11 +1309,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>5593</v>
+        <v>6069</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>466.08333333333331</v>
+        <v>466.84615384615387</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1321,11 +1325,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1090</v>
+        <v>1181</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>90.833333333333329</v>
+        <v>90.84615384615384</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1337,11 +1341,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>9.4166666666666661</v>
+        <v>10.076923076923077</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1353,11 +1357,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>16767</v>
+        <v>17712</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1397.25</v>
+        <v>1362.4615384615386</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1369,11 +1373,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>1661</v>
+        <v>1821</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>138.41666666666666</v>
+        <v>140.07692307692307</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1385,11 +1389,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>3691</v>
+        <v>4219</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>307.58333333333331</v>
+        <v>324.53846153846155</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1401,11 +1405,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>8552</v>
+        <v>9468</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>712.66666666666663</v>
+        <v>728.30769230769226</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1417,11 +1421,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>4013</v>
+        <v>4480</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>334.41666666666669</v>
+        <v>344.61538461538464</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1433,11 +1437,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>43335</v>
+        <v>46505</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3611.25</v>
+        <v>3577.3076923076924</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1449,11 +1453,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>28511</v>
+        <v>30586</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2375.9166666666665</v>
+        <v>2352.7692307692309</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1465,11 +1469,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>27524</v>
+        <v>29622</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2293.6666666666665</v>
+        <v>2278.6153846153848</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1481,11 +1485,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>33187</v>
+        <v>35532</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2765.5833333333335</v>
+        <v>2733.2307692307691</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1497,11 +1501,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>32.083333333333336</v>
+        <v>30.153846153846153</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1513,11 +1517,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$19</f>
-        <v>2468</v>
+        <v>3327</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>205.66666666666666</v>
+        <v>255.92307692307693</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1529,11 +1533,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$20</f>
-        <v>2949</v>
+        <v>3865</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>245.75</v>
+        <v>297.30769230769232</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1545,11 +1549,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$21</f>
-        <v>2795</v>
+        <v>3717</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>232.91666666666666</v>
+        <v>285.92307692307691</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1561,11 +1565,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>2764</v>
+        <v>3028</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>230.33333333333334</v>
+        <v>232.92307692307693</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1577,11 +1581,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>1577</v>
+        <v>1771</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>131.41666666666666</v>
+        <v>136.23076923076923</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1593,11 +1597,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>6005</v>
+        <v>6553</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>500.41666666666669</v>
+        <v>504.07692307692309</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1609,11 +1613,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>9413</v>
+        <v>10172</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>784.41666666666663</v>
+        <v>782.46153846153845</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1629,7 +1633,7 @@
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>8.3333333333333339</v>
+        <v>7.6923076923076925</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1645,7 +1649,7 @@
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>142</v>
+        <v>131.07692307692307</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1657,11 +1661,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>7963</v>
+        <v>8332</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>663.58333333333337</v>
+        <v>640.92307692307691</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1673,11 +1677,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>13000</v>
+        <v>13836</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>1083.3333333333333</v>
+        <v>1064.3076923076924</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1689,11 +1693,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>5922</v>
+        <v>6527</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>493.5</v>
+        <v>502.07692307692309</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1705,43 +1709,43 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>4298</v>
+        <v>4629</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>358.16666666666669</v>
+        <v>356.07692307692309</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="15">
         <v>131154</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="20" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$32</f>
-        <v>234</v>
+        <v>417</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$32</f>
-        <v>19.5</v>
+        <v>32.07692307692308</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="15">
         <v>131155</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="20" t="s">
         <v>60</v>
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$33</f>
-        <v>197</v>
+        <v>380</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$33</f>
-        <v>16.416666666666668</v>
+        <v>29.23076923076923</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1753,11 +1757,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>234</v>
+        <v>417</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>19.5</v>
+        <v>32.07692307692308</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1769,11 +1773,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>197</v>
+        <v>380</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>16.416666666666668</v>
+        <v>29.23076923076923</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1785,11 +1789,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>1581</v>
+        <v>1660</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>131.75</v>
+        <v>127.69230769230769</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1801,11 +1805,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>1531</v>
+        <v>1695</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>127.58333333333333</v>
+        <v>130.38461538461539</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1817,11 +1821,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>7053</v>
+        <v>7926</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>587.75</v>
+        <v>609.69230769230774</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1833,11 +1837,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>7865</v>
+        <v>8479</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>655.41666666666663</v>
+        <v>652.23076923076928</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1849,11 +1853,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>9825</v>
+        <v>10798</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>818.75</v>
+        <v>830.61538461538464</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1865,11 +1869,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>6846</v>
+        <v>7479</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>570.5</v>
+        <v>575.30769230769226</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1881,11 +1885,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>298</v>
+        <v>634</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>24.833333333333332</v>
+        <v>48.769230769230766</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1897,11 +1901,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>6861</v>
+        <v>7324</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>571.75</v>
+        <v>563.38461538461536</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1917,7 +1921,7 @@
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>59.333333333333336</v>
+        <v>54.769230769230766</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1929,11 +1933,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>3598</v>
+        <v>3853</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>299.83333333333331</v>
+        <v>296.38461538461536</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1945,11 +1949,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>6237</v>
+        <v>6621</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>519.75</v>
+        <v>509.30769230769232</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1961,11 +1965,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>3758</v>
+        <v>3943</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>313.16666666666669</v>
+        <v>303.30769230769232</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1977,11 +1981,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>3314</v>
+        <v>3534</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>276.16666666666669</v>
+        <v>271.84615384615387</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1993,11 +1997,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>554</v>
+        <v>600</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>46.166666666666664</v>
+        <v>46.153846153846153</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2009,11 +2013,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>1076</v>
+        <v>1213</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>89.666666666666671</v>
+        <v>93.307692307692307</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2023,11 +2027,11 @@
       </c>
       <c r="C49" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>612</v>
+        <v>668</v>
       </c>
       <c r="D49" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>51</v>
+        <v>51.384615384615387</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2037,11 +2041,11 @@
       </c>
       <c r="C50" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="D50" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>43</v>
+        <v>40.92307692307692</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2062,15 +2066,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2098,19 +2102,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>315548</v>
+        <v>342446</v>
       </c>
       <c r="B3" s="3">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>313016</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!$H$3</f>
+        <v>339790</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>26295.666666666668</v>
+        <v>26342</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>578504.66666666674</v>
+        <v>579524</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2118,11 +2122,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.48618924136740915</v>
+        <v>0.52763307309602281</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-333475</v>
+        <v>-306577</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2158,7 +2162,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>2532</v>
+        <v>2656</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2166,7 +2170,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2174,11 +2178,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099BF8C0-6BB3-44F7-9D31-C4888B6FE34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31D73C7-1293-4677-BE91-1CF973142B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <externalReferences>
     <externalReference r:id="rId3"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -475,6 +475,9 @@
       <sheetName val="INVENTARIO NACIONAL 19-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 19-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 20-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 20-08-26-2"/>
+      <sheetName val="INVENTARIO NACIONAL 21-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -495,36 +498,39 @@
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
-      <sheetData sheetId="15">
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18">
         <row r="3">
           <cell r="G3">
-            <v>342446</v>
+            <v>395896</v>
           </cell>
           <cell r="H3">
-            <v>339790</v>
+            <v>392273</v>
           </cell>
           <cell r="I3">
-            <v>26342</v>
+            <v>26393.066666666666</v>
           </cell>
           <cell r="J3">
-            <v>579524</v>
+            <v>580647.46666666667</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.52763307309602281</v>
+            <v>0.60998762755711278</v>
           </cell>
           <cell r="M3">
-            <v>-306577</v>
+            <v>-253127</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>14933</v>
+            <v>17561</v>
           </cell>
           <cell r="D4">
-            <v>1148.6923076923076</v>
+            <v>1170.7333333333333</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -547,188 +553,188 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>1083</v>
+            <v>1222</v>
           </cell>
           <cell r="D5">
-            <v>83.307692307692307</v>
+            <v>81.466666666666669</v>
           </cell>
           <cell r="G5">
-            <v>2656</v>
+            <v>3623</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
           </cell>
           <cell r="I5">
-            <v>46254</v>
+            <v>46258</v>
           </cell>
           <cell r="J5">
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>13</v>
+            <v>15</v>
           </cell>
           <cell r="L5">
-            <v>8</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>6069</v>
+            <v>7371</v>
           </cell>
           <cell r="D6">
-            <v>466.84615384615387</v>
+            <v>491.4</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1181</v>
+            <v>1426</v>
           </cell>
           <cell r="D7">
-            <v>90.84615384615384</v>
+            <v>95.066666666666663</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>131</v>
+            <v>178</v>
           </cell>
           <cell r="D8">
-            <v>10.076923076923077</v>
+            <v>11.866666666666667</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>17712</v>
+            <v>20999</v>
           </cell>
           <cell r="D9">
-            <v>1362.4615384615386</v>
+            <v>1399.9333333333334</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>1821</v>
+            <v>2241</v>
           </cell>
           <cell r="D10">
-            <v>140.07692307692307</v>
+            <v>149.4</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>4219</v>
+            <v>4814</v>
           </cell>
           <cell r="D11">
-            <v>324.53846153846155</v>
+            <v>320.93333333333334</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>9468</v>
+            <v>10803</v>
           </cell>
           <cell r="D12">
-            <v>728.30769230769226</v>
+            <v>720.2</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>4480</v>
+            <v>5091</v>
           </cell>
           <cell r="D13">
-            <v>344.61538461538464</v>
+            <v>339.4</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>46505</v>
+            <v>52737</v>
           </cell>
           <cell r="D14">
-            <v>3577.3076923076924</v>
+            <v>3515.8</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>30586</v>
+            <v>34319</v>
           </cell>
           <cell r="D15">
-            <v>2352.7692307692309</v>
+            <v>2287.9333333333334</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>29622</v>
+            <v>33549</v>
           </cell>
           <cell r="D16">
-            <v>2278.6153846153848</v>
+            <v>2236.6</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>35532</v>
+            <v>39946</v>
           </cell>
           <cell r="D17">
-            <v>2733.2307692307691</v>
+            <v>2663.0666666666666</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>392</v>
+            <v>396</v>
           </cell>
           <cell r="D18">
-            <v>30.153846153846153</v>
+            <v>26.4</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>3327</v>
+            <v>4507</v>
           </cell>
           <cell r="D19">
-            <v>255.92307692307693</v>
+            <v>300.46666666666664</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>3865</v>
+            <v>5130</v>
           </cell>
           <cell r="D20">
-            <v>297.30769230769232</v>
+            <v>342</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>3717</v>
+            <v>4885</v>
           </cell>
           <cell r="D21">
-            <v>285.92307692307691</v>
+            <v>325.66666666666669</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>3028</v>
+            <v>3520</v>
           </cell>
           <cell r="D22">
-            <v>232.92307692307693</v>
+            <v>234.66666666666666</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>1771</v>
+            <v>1990</v>
           </cell>
           <cell r="D23">
-            <v>136.23076923076923</v>
+            <v>132.66666666666666</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>6553</v>
+            <v>7475</v>
           </cell>
           <cell r="D24">
-            <v>504.07692307692309</v>
+            <v>498.33333333333331</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>10172</v>
+            <v>11707</v>
           </cell>
           <cell r="D25">
-            <v>782.46153846153845</v>
+            <v>780.4666666666667</v>
           </cell>
         </row>
         <row r="26">
@@ -736,127 +742,127 @@
             <v>100</v>
           </cell>
           <cell r="D26">
-            <v>7.6923076923076925</v>
+            <v>6.666666666666667</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>1704</v>
+            <v>1804</v>
           </cell>
           <cell r="D27">
-            <v>131.07692307692307</v>
+            <v>120.26666666666667</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>8332</v>
+            <v>10451</v>
           </cell>
           <cell r="D28">
-            <v>640.92307692307691</v>
+            <v>696.73333333333335</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>13836</v>
+            <v>18176</v>
           </cell>
           <cell r="D29">
-            <v>1064.3076923076924</v>
+            <v>1211.7333333333333</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>6527</v>
+            <v>7663</v>
           </cell>
           <cell r="D30">
-            <v>502.07692307692309</v>
+            <v>510.86666666666667</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>4629</v>
+            <v>5361</v>
           </cell>
           <cell r="D31">
-            <v>356.07692307692309</v>
+            <v>357.4</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>417</v>
+            <v>657</v>
           </cell>
           <cell r="D32">
-            <v>32.07692307692308</v>
+            <v>43.8</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>380</v>
+            <v>635</v>
           </cell>
           <cell r="D33">
-            <v>29.23076923076923</v>
+            <v>42.333333333333336</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>1660</v>
+            <v>1783</v>
           </cell>
           <cell r="D34">
-            <v>127.69230769230769</v>
+            <v>118.86666666666666</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>1695</v>
+            <v>1994</v>
           </cell>
           <cell r="D35">
-            <v>130.38461538461539</v>
+            <v>132.93333333333334</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>7926</v>
+            <v>8897</v>
           </cell>
           <cell r="D36">
-            <v>609.69230769230774</v>
+            <v>593.13333333333333</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>8479</v>
+            <v>9517</v>
           </cell>
           <cell r="D37">
-            <v>652.23076923076928</v>
+            <v>634.4666666666667</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>10798</v>
+            <v>12624</v>
           </cell>
           <cell r="D38">
-            <v>830.61538461538464</v>
+            <v>841.6</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>7479</v>
+            <v>8410</v>
           </cell>
           <cell r="D39">
-            <v>575.30769230769226</v>
+            <v>560.66666666666663</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>634</v>
+            <v>1181</v>
           </cell>
           <cell r="D40">
-            <v>48.769230769230766</v>
+            <v>78.733333333333334</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>7324</v>
+            <v>7648</v>
           </cell>
           <cell r="D41">
-            <v>563.38461538461536</v>
+            <v>509.86666666666667</v>
           </cell>
         </row>
         <row r="42">
@@ -864,75 +870,75 @@
             <v>712</v>
           </cell>
           <cell r="D42">
-            <v>54.769230769230766</v>
+            <v>47.466666666666669</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>3853</v>
+            <v>4298</v>
           </cell>
           <cell r="D43">
-            <v>296.38461538461536</v>
+            <v>286.53333333333336</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>6621</v>
+            <v>7149</v>
           </cell>
           <cell r="D44">
-            <v>509.30769230769232</v>
+            <v>476.6</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>3943</v>
+            <v>4261</v>
           </cell>
           <cell r="D45">
-            <v>303.30769230769232</v>
+            <v>284.06666666666666</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>3534</v>
+            <v>3783</v>
           </cell>
           <cell r="D46">
-            <v>271.84615384615387</v>
+            <v>252.2</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>600</v>
+            <v>660</v>
           </cell>
           <cell r="D47">
-            <v>46.153846153846153</v>
+            <v>44</v>
           </cell>
         </row>
         <row r="48">
           <cell r="C48">
-            <v>1213</v>
+            <v>1281</v>
           </cell>
           <cell r="D48">
-            <v>93.307692307692307</v>
+            <v>85.4</v>
           </cell>
         </row>
         <row r="49">
           <cell r="C49">
-            <v>668</v>
+            <v>720</v>
           </cell>
           <cell r="D49">
-            <v>51.384615384615387</v>
+            <v>48</v>
           </cell>
         </row>
         <row r="50">
           <cell r="C50">
-            <v>532</v>
+            <v>597</v>
           </cell>
           <cell r="D50">
-            <v>40.92307692307692</v>
+            <v>39.799999999999997</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="16"/>
+      <sheetData sheetId="19"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1277,11 +1283,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>14933</v>
+        <v>17561</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1148.6923076923076</v>
+        <v>1170.7333333333333</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1293,11 +1299,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>1083</v>
+        <v>1222</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>83.307692307692307</v>
+        <v>81.466666666666669</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1309,11 +1315,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>6069</v>
+        <v>7371</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>466.84615384615387</v>
+        <v>491.4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1325,11 +1331,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1181</v>
+        <v>1426</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>90.84615384615384</v>
+        <v>95.066666666666663</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1341,11 +1347,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>10.076923076923077</v>
+        <v>11.866666666666667</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1357,11 +1363,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>17712</v>
+        <v>20999</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1362.4615384615386</v>
+        <v>1399.9333333333334</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1373,11 +1379,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>1821</v>
+        <v>2241</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>140.07692307692307</v>
+        <v>149.4</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1389,11 +1395,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>4219</v>
+        <v>4814</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>324.53846153846155</v>
+        <v>320.93333333333334</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1405,11 +1411,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>9468</v>
+        <v>10803</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>728.30769230769226</v>
+        <v>720.2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1421,11 +1427,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>4480</v>
+        <v>5091</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>344.61538461538464</v>
+        <v>339.4</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1437,11 +1443,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>46505</v>
+        <v>52737</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3577.3076923076924</v>
+        <v>3515.8</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1453,11 +1459,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>30586</v>
+        <v>34319</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2352.7692307692309</v>
+        <v>2287.9333333333334</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1469,11 +1475,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>29622</v>
+        <v>33549</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2278.6153846153848</v>
+        <v>2236.6</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1485,11 +1491,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>35532</v>
+        <v>39946</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2733.2307692307691</v>
+        <v>2663.0666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1501,11 +1507,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>30.153846153846153</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1517,11 +1523,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$19</f>
-        <v>3327</v>
+        <v>4507</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>255.92307692307693</v>
+        <v>300.46666666666664</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1533,11 +1539,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$20</f>
-        <v>3865</v>
+        <v>5130</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>297.30769230769232</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1549,11 +1555,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$21</f>
-        <v>3717</v>
+        <v>4885</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>285.92307692307691</v>
+        <v>325.66666666666669</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1565,11 +1571,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>3028</v>
+        <v>3520</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>232.92307692307693</v>
+        <v>234.66666666666666</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1581,11 +1587,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>1771</v>
+        <v>1990</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>136.23076923076923</v>
+        <v>132.66666666666666</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1597,11 +1603,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>6553</v>
+        <v>7475</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>504.07692307692309</v>
+        <v>498.33333333333331</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1613,11 +1619,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>10172</v>
+        <v>11707</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>782.46153846153845</v>
+        <v>780.4666666666667</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1633,7 +1639,7 @@
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>7.6923076923076925</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1645,11 +1651,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>1704</v>
+        <v>1804</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>131.07692307692307</v>
+        <v>120.26666666666667</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1661,11 +1667,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>8332</v>
+        <v>10451</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>640.92307692307691</v>
+        <v>696.73333333333335</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1677,11 +1683,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>13836</v>
+        <v>18176</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>1064.3076923076924</v>
+        <v>1211.7333333333333</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1693,11 +1699,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>6527</v>
+        <v>7663</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>502.07692307692309</v>
+        <v>510.86666666666667</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1709,11 +1715,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>4629</v>
+        <v>5361</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>356.07692307692309</v>
+        <v>357.4</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1725,11 +1731,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$32</f>
-        <v>417</v>
+        <v>657</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$32</f>
-        <v>32.07692307692308</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1741,11 +1747,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$33</f>
-        <v>380</v>
+        <v>635</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$33</f>
-        <v>29.23076923076923</v>
+        <v>42.333333333333336</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1757,11 +1763,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>417</v>
+        <v>657</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>32.07692307692308</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1773,11 +1779,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>380</v>
+        <v>635</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>29.23076923076923</v>
+        <v>42.333333333333336</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1789,11 +1795,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>1660</v>
+        <v>1783</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>127.69230769230769</v>
+        <v>118.86666666666666</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1805,11 +1811,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>1695</v>
+        <v>1994</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>130.38461538461539</v>
+        <v>132.93333333333334</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1821,11 +1827,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>7926</v>
+        <v>8897</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>609.69230769230774</v>
+        <v>593.13333333333333</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1837,11 +1843,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>8479</v>
+        <v>9517</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>652.23076923076928</v>
+        <v>634.4666666666667</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1853,11 +1859,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>10798</v>
+        <v>12624</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>830.61538461538464</v>
+        <v>841.6</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1869,11 +1875,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>7479</v>
+        <v>8410</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>575.30769230769226</v>
+        <v>560.66666666666663</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1885,11 +1891,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>634</v>
+        <v>1181</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>48.769230769230766</v>
+        <v>78.733333333333334</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1901,11 +1907,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>7324</v>
+        <v>7648</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>563.38461538461536</v>
+        <v>509.86666666666667</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1921,7 +1927,7 @@
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>54.769230769230766</v>
+        <v>47.466666666666669</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1933,11 +1939,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>3853</v>
+        <v>4298</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>296.38461538461536</v>
+        <v>286.53333333333336</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1949,11 +1955,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>6621</v>
+        <v>7149</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>509.30769230769232</v>
+        <v>476.6</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1965,11 +1971,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>3943</v>
+        <v>4261</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>303.30769230769232</v>
+        <v>284.06666666666666</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1981,11 +1987,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>3534</v>
+        <v>3783</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>271.84615384615387</v>
+        <v>252.2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1997,11 +2003,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>46.153846153846153</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2013,11 +2019,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>1213</v>
+        <v>1281</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>93.307692307692307</v>
+        <v>85.4</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2027,11 +2033,11 @@
       </c>
       <c r="C49" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>668</v>
+        <v>720</v>
       </c>
       <c r="D49" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>51.384615384615387</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2041,11 +2047,11 @@
       </c>
       <c r="C50" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>532</v>
+        <v>597</v>
       </c>
       <c r="D50" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>40.92307692307692</v>
+        <v>39.799999999999997</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2102,19 +2108,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>342446</v>
+        <v>395896</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$H$3</f>
-        <v>339790</v>
+        <v>392273</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>26342</v>
+        <v>26393.066666666666</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>579524</v>
+        <v>580647.46666666667</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2122,11 +2128,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.52763307309602281</v>
+        <v>0.60998762755711278</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-306577</v>
+        <v>-253127</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2162,7 +2168,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>2656</v>
+        <v>3623</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2170,7 +2176,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2178,11 +2184,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31D73C7-1293-4677-BE91-1CF973142B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC521F04-0FC3-4BDF-AF18-1622C1F8DB41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -478,6 +478,7 @@
       <sheetName val="INVENTARIO NACIONAL 20-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 21-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -501,36 +502,37 @@
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
-      <sheetData sheetId="18">
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19">
         <row r="3">
           <cell r="G3">
-            <v>395896</v>
+            <v>420459</v>
           </cell>
           <cell r="H3">
-            <v>392273</v>
+            <v>416619</v>
           </cell>
           <cell r="I3">
-            <v>26393.066666666666</v>
+            <v>26278.6875</v>
           </cell>
           <cell r="J3">
-            <v>580647.46666666667</v>
+            <v>578131.125</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.60998762755711278</v>
+            <v>0.64783374395052251</v>
           </cell>
           <cell r="M3">
-            <v>-253127</v>
+            <v>-228564</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>17561</v>
+            <v>18695</v>
           </cell>
           <cell r="D4">
-            <v>1170.7333333333333</v>
+            <v>1168.4375</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -553,392 +555,392 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>1222</v>
+            <v>1231</v>
           </cell>
           <cell r="D5">
-            <v>81.466666666666669</v>
+            <v>76.9375</v>
           </cell>
           <cell r="G5">
-            <v>3623</v>
+            <v>3840</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
           </cell>
           <cell r="I5">
-            <v>46258</v>
+            <v>46259</v>
           </cell>
           <cell r="J5">
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>15</v>
+            <v>16</v>
           </cell>
           <cell r="L5">
-            <v>6</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>7371</v>
+            <v>7874</v>
           </cell>
           <cell r="D6">
-            <v>491.4</v>
+            <v>492.125</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1426</v>
+            <v>1429</v>
           </cell>
           <cell r="D7">
-            <v>95.066666666666663</v>
+            <v>89.3125</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>178</v>
+            <v>175</v>
           </cell>
           <cell r="D8">
-            <v>11.866666666666667</v>
+            <v>10.9375</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>20999</v>
+            <v>22765</v>
           </cell>
           <cell r="D9">
-            <v>1399.9333333333334</v>
+            <v>1422.8125</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>2241</v>
+            <v>2317</v>
           </cell>
           <cell r="D10">
-            <v>149.4</v>
+            <v>144.8125</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>4814</v>
+            <v>5012</v>
           </cell>
           <cell r="D11">
-            <v>320.93333333333334</v>
+            <v>313.25</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>10803</v>
+            <v>11418</v>
           </cell>
           <cell r="D12">
-            <v>720.2</v>
+            <v>713.625</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>5091</v>
+            <v>5302</v>
           </cell>
           <cell r="D13">
-            <v>339.4</v>
+            <v>331.375</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>52737</v>
+            <v>55927</v>
           </cell>
           <cell r="D14">
-            <v>3515.8</v>
+            <v>3495.4375</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>34319</v>
+            <v>36473</v>
           </cell>
           <cell r="D15">
-            <v>2287.9333333333334</v>
+            <v>2279.5625</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>33549</v>
+            <v>35567</v>
           </cell>
           <cell r="D16">
-            <v>2236.6</v>
+            <v>2222.9375</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>39946</v>
+            <v>42142</v>
           </cell>
           <cell r="D17">
-            <v>2663.0666666666666</v>
+            <v>2633.875</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>396</v>
+            <v>340</v>
           </cell>
           <cell r="D18">
-            <v>26.4</v>
+            <v>21.25</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>4507</v>
+            <v>5025</v>
           </cell>
           <cell r="D19">
-            <v>300.46666666666664</v>
+            <v>314.0625</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>5130</v>
+            <v>5702</v>
           </cell>
           <cell r="D20">
-            <v>342</v>
+            <v>356.375</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>4885</v>
+            <v>5480</v>
           </cell>
           <cell r="D21">
-            <v>325.66666666666669</v>
+            <v>342.5</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>3520</v>
+            <v>3611</v>
           </cell>
           <cell r="D22">
-            <v>234.66666666666666</v>
+            <v>225.6875</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>1990</v>
+            <v>2086</v>
           </cell>
           <cell r="D23">
-            <v>132.66666666666666</v>
+            <v>130.375</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>7475</v>
+            <v>7836</v>
           </cell>
           <cell r="D24">
-            <v>498.33333333333331</v>
+            <v>489.75</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>11707</v>
+            <v>12374</v>
           </cell>
           <cell r="D25">
-            <v>780.4666666666667</v>
+            <v>773.375</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>100</v>
+            <v>1236</v>
           </cell>
           <cell r="D26">
-            <v>6.666666666666667</v>
+            <v>77.25</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>1804</v>
+            <v>11488</v>
           </cell>
           <cell r="D27">
-            <v>120.26666666666667</v>
+            <v>718</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>10451</v>
+            <v>19062</v>
           </cell>
           <cell r="D28">
-            <v>696.73333333333335</v>
+            <v>1191.375</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>18176</v>
+            <v>8133</v>
           </cell>
           <cell r="D29">
-            <v>1211.7333333333333</v>
+            <v>508.3125</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>7663</v>
+            <v>5983</v>
           </cell>
           <cell r="D30">
-            <v>510.86666666666667</v>
+            <v>373.9375</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>5361</v>
+            <v>810</v>
           </cell>
           <cell r="D31">
-            <v>357.4</v>
+            <v>50.625</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>657</v>
+            <v>789</v>
           </cell>
           <cell r="D32">
-            <v>43.8</v>
+            <v>49.3125</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>635</v>
+            <v>1827</v>
           </cell>
           <cell r="D33">
-            <v>42.333333333333336</v>
+            <v>114.1875</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>1783</v>
+            <v>2103</v>
           </cell>
           <cell r="D34">
-            <v>118.86666666666666</v>
+            <v>131.4375</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>1994</v>
+            <v>9547</v>
           </cell>
           <cell r="D35">
-            <v>132.93333333333334</v>
+            <v>596.6875</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>8897</v>
+            <v>9977</v>
           </cell>
           <cell r="D36">
-            <v>593.13333333333333</v>
+            <v>623.5625</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>9517</v>
+            <v>13247</v>
           </cell>
           <cell r="D37">
-            <v>634.4666666666667</v>
+            <v>827.9375</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>12624</v>
+            <v>8915</v>
           </cell>
           <cell r="D38">
-            <v>841.6</v>
+            <v>557.1875</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>8410</v>
+            <v>42</v>
           </cell>
           <cell r="D39">
-            <v>560.66666666666663</v>
+            <v>2.625</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>1181</v>
+            <v>8</v>
           </cell>
           <cell r="D40">
-            <v>78.733333333333334</v>
+            <v>0.5</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>7648</v>
+            <v>1392</v>
           </cell>
           <cell r="D41">
-            <v>509.86666666666667</v>
+            <v>87</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>712</v>
+            <v>7945</v>
           </cell>
           <cell r="D42">
-            <v>47.466666666666669</v>
+            <v>496.5625</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>4298</v>
+            <v>665</v>
           </cell>
           <cell r="D43">
-            <v>286.53333333333336</v>
+            <v>41.5625</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>7149</v>
+            <v>4594</v>
           </cell>
           <cell r="D44">
-            <v>476.6</v>
+            <v>287.125</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>4261</v>
+            <v>7723</v>
           </cell>
           <cell r="D45">
-            <v>284.06666666666666</v>
+            <v>482.6875</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>3783</v>
+            <v>4555</v>
           </cell>
           <cell r="D46">
-            <v>252.2</v>
+            <v>284.6875</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>660</v>
+            <v>4102</v>
           </cell>
           <cell r="D47">
-            <v>44</v>
+            <v>256.375</v>
           </cell>
         </row>
         <row r="48">
           <cell r="C48">
-            <v>1281</v>
+            <v>755</v>
           </cell>
           <cell r="D48">
-            <v>85.4</v>
+            <v>47.1875</v>
           </cell>
         </row>
         <row r="49">
           <cell r="C49">
-            <v>720</v>
+            <v>1476</v>
           </cell>
           <cell r="D49">
-            <v>48</v>
+            <v>92.25</v>
           </cell>
         </row>
         <row r="50">
           <cell r="C50">
-            <v>597</v>
+            <v>789</v>
           </cell>
           <cell r="D50">
-            <v>39.799999999999997</v>
+            <v>49.3125</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1283,11 +1285,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>17561</v>
+        <v>18695</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1170.7333333333333</v>
+        <v>1168.4375</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1299,11 +1301,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>1222</v>
+        <v>1231</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>81.466666666666669</v>
+        <v>76.9375</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1315,11 +1317,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>7371</v>
+        <v>7874</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>491.4</v>
+        <v>492.125</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1331,11 +1333,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>95.066666666666663</v>
+        <v>89.3125</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1347,11 +1349,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>11.866666666666667</v>
+        <v>10.9375</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1363,11 +1365,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>20999</v>
+        <v>22765</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1399.9333333333334</v>
+        <v>1422.8125</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1379,11 +1381,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2241</v>
+        <v>2317</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>149.4</v>
+        <v>144.8125</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1395,11 +1397,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>4814</v>
+        <v>5012</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>320.93333333333334</v>
+        <v>313.25</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1411,11 +1413,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>10803</v>
+        <v>11418</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>720.2</v>
+        <v>713.625</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1427,11 +1429,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>5091</v>
+        <v>5302</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>339.4</v>
+        <v>331.375</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1443,11 +1445,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>52737</v>
+        <v>55927</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3515.8</v>
+        <v>3495.4375</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1459,11 +1461,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>34319</v>
+        <v>36473</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2287.9333333333334</v>
+        <v>2279.5625</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1475,11 +1477,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>33549</v>
+        <v>35567</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2236.6</v>
+        <v>2222.9375</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1491,11 +1493,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>39946</v>
+        <v>42142</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2663.0666666666666</v>
+        <v>2633.875</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1507,11 +1509,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>396</v>
+        <v>340</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>26.4</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1523,11 +1525,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$19</f>
-        <v>4507</v>
+        <v>5025</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>300.46666666666664</v>
+        <v>314.0625</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1539,11 +1541,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$20</f>
-        <v>5130</v>
+        <v>5702</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>342</v>
+        <v>356.375</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1555,11 +1557,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$21</f>
-        <v>4885</v>
+        <v>5480</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>325.66666666666669</v>
+        <v>342.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1571,11 +1573,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>3520</v>
+        <v>3611</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>234.66666666666666</v>
+        <v>225.6875</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1587,11 +1589,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>1990</v>
+        <v>2086</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>132.66666666666666</v>
+        <v>130.375</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1603,11 +1605,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>7475</v>
+        <v>7836</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>498.33333333333331</v>
+        <v>489.75</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1619,11 +1621,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>11707</v>
+        <v>12374</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>780.4666666666667</v>
+        <v>773.375</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1635,11 +1637,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>100</v>
+        <v>1236</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>6.666666666666667</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1651,11 +1653,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>1804</v>
+        <v>11488</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>120.26666666666667</v>
+        <v>718</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1667,11 +1669,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>10451</v>
+        <v>19062</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>696.73333333333335</v>
+        <v>1191.375</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1683,11 +1685,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>18176</v>
+        <v>8133</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>1211.7333333333333</v>
+        <v>508.3125</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1699,11 +1701,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>7663</v>
+        <v>5983</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>510.86666666666667</v>
+        <v>373.9375</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1715,11 +1717,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>5361</v>
+        <v>810</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>357.4</v>
+        <v>50.625</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1731,11 +1733,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$32</f>
-        <v>657</v>
+        <v>789</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$32</f>
-        <v>43.8</v>
+        <v>49.3125</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1747,11 +1749,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$33</f>
-        <v>635</v>
+        <v>1827</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$33</f>
-        <v>42.333333333333336</v>
+        <v>114.1875</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1763,11 +1765,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>657</v>
+        <v>789</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>43.8</v>
+        <v>49.3125</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1779,11 +1781,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>635</v>
+        <v>1827</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>42.333333333333336</v>
+        <v>114.1875</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1795,11 +1797,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>1783</v>
+        <v>2103</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>118.86666666666666</v>
+        <v>131.4375</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1811,11 +1813,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>1994</v>
+        <v>9547</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>132.93333333333334</v>
+        <v>596.6875</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1827,11 +1829,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>8897</v>
+        <v>9977</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>593.13333333333333</v>
+        <v>623.5625</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1843,11 +1845,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>9517</v>
+        <v>13247</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>634.4666666666667</v>
+        <v>827.9375</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1859,11 +1861,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>12624</v>
+        <v>8915</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>841.6</v>
+        <v>557.1875</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1875,11 +1877,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>8410</v>
+        <v>42</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>560.66666666666663</v>
+        <v>2.625</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1891,11 +1893,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>1181</v>
+        <v>8</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>78.733333333333334</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1907,11 +1909,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>7648</v>
+        <v>1392</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>509.86666666666667</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1923,11 +1925,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>712</v>
+        <v>7945</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>47.466666666666669</v>
+        <v>496.5625</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1939,11 +1941,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>4298</v>
+        <v>665</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>286.53333333333336</v>
+        <v>41.5625</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1955,11 +1957,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>7149</v>
+        <v>4594</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>476.6</v>
+        <v>287.125</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1971,11 +1973,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>4261</v>
+        <v>7723</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>284.06666666666666</v>
+        <v>482.6875</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1987,11 +1989,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>3783</v>
+        <v>4555</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>252.2</v>
+        <v>284.6875</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2003,11 +2005,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>660</v>
+        <v>4102</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>44</v>
+        <v>256.375</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2019,11 +2021,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>1281</v>
+        <v>755</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>85.4</v>
+        <v>47.1875</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2033,11 +2035,11 @@
       </c>
       <c r="C49" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>720</v>
+        <v>1476</v>
       </c>
       <c r="D49" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>48</v>
+        <v>92.25</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2047,11 +2049,11 @@
       </c>
       <c r="C50" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>597</v>
+        <v>789</v>
       </c>
       <c r="D50" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>39.799999999999997</v>
+        <v>49.3125</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2108,19 +2110,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>395896</v>
+        <v>420459</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$H$3</f>
-        <v>392273</v>
+        <v>416619</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>26393.066666666666</v>
+        <v>26278.6875</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>580647.46666666667</v>
+        <v>578131.125</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2128,11 +2130,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.60998762755711278</v>
+        <v>0.64783374395052251</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-253127</v>
+        <v>-228564</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2168,7 +2170,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>3623</v>
+        <v>3840</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2176,7 +2178,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2184,11 +2186,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC521F04-0FC3-4BDF-AF18-1622C1F8DB41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2157A0-CFFC-470C-ADC3-9549DA66C191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -479,6 +479,7 @@
       <sheetName val="INVENTARIO NACIONAL 21-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -503,36 +504,37 @@
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
-      <sheetData sheetId="19">
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20">
         <row r="3">
           <cell r="G3">
-            <v>420459</v>
+            <v>440459</v>
           </cell>
           <cell r="H3">
-            <v>416619</v>
+            <v>442804</v>
           </cell>
           <cell r="I3">
-            <v>26278.6875</v>
+            <v>25909.352941176472</v>
           </cell>
           <cell r="J3">
-            <v>578131.125</v>
+            <v>570005.76470588241</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.64783374395052251</v>
+            <v>0.67864929286019138</v>
           </cell>
           <cell r="M3">
-            <v>-228564</v>
+            <v>-208564</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>18695</v>
+            <v>19802</v>
           </cell>
           <cell r="D4">
-            <v>1168.4375</v>
+            <v>1164.8235294117646</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -555,13 +557,13 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>1231</v>
+            <v>1239</v>
           </cell>
           <cell r="D5">
-            <v>76.9375</v>
+            <v>72.882352941176464</v>
           </cell>
           <cell r="G5">
-            <v>3840</v>
+            <v>-2345</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
@@ -573,7 +575,7 @@
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>16</v>
+            <v>17</v>
           </cell>
           <cell r="L5">
             <v>5</v>
@@ -581,366 +583,366 @@
         </row>
         <row r="6">
           <cell r="C6">
-            <v>7874</v>
+            <v>8245</v>
           </cell>
           <cell r="D6">
-            <v>492.125</v>
+            <v>485</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1429</v>
+            <v>1486</v>
           </cell>
           <cell r="D7">
-            <v>89.3125</v>
+            <v>87.411764705882348</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>175</v>
+            <v>190</v>
           </cell>
           <cell r="D8">
-            <v>10.9375</v>
+            <v>11.176470588235293</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>22765</v>
+            <v>24109</v>
           </cell>
           <cell r="D9">
-            <v>1422.8125</v>
+            <v>1418.1764705882354</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>2317</v>
+            <v>2431</v>
           </cell>
           <cell r="D10">
-            <v>144.8125</v>
+            <v>143</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>5012</v>
+            <v>5338</v>
           </cell>
           <cell r="D11">
-            <v>313.25</v>
+            <v>314</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>11418</v>
+            <v>12299</v>
           </cell>
           <cell r="D12">
-            <v>713.625</v>
+            <v>723.47058823529414</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>5302</v>
+            <v>5814</v>
           </cell>
           <cell r="D13">
-            <v>331.375</v>
+            <v>342</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>55927</v>
+            <v>59012</v>
           </cell>
           <cell r="D14">
-            <v>3495.4375</v>
+            <v>3471.294117647059</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>36473</v>
+            <v>38309</v>
           </cell>
           <cell r="D15">
-            <v>2279.5625</v>
+            <v>2253.4705882352941</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>35567</v>
+            <v>37525</v>
           </cell>
           <cell r="D16">
-            <v>2222.9375</v>
+            <v>2207.3529411764707</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>42142</v>
+            <v>44495</v>
           </cell>
           <cell r="D17">
-            <v>2633.875</v>
+            <v>2617.3529411764707</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>340</v>
+            <v>321</v>
           </cell>
           <cell r="D18">
-            <v>21.25</v>
+            <v>18.882352941176471</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>5025</v>
+            <v>5830</v>
           </cell>
           <cell r="D19">
-            <v>314.0625</v>
+            <v>342.94117647058823</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>5702</v>
+            <v>6605</v>
           </cell>
           <cell r="D20">
-            <v>356.375</v>
+            <v>388.52941176470586</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>5480</v>
+            <v>6362</v>
           </cell>
           <cell r="D21">
-            <v>342.5</v>
+            <v>374.23529411764707</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>3611</v>
+            <v>3860</v>
           </cell>
           <cell r="D22">
-            <v>225.6875</v>
+            <v>227.05882352941177</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>2086</v>
+            <v>2226</v>
           </cell>
           <cell r="D23">
-            <v>130.375</v>
+            <v>130.94117647058823</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>7836</v>
+            <v>8484</v>
           </cell>
           <cell r="D24">
-            <v>489.75</v>
+            <v>499.05882352941177</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>12374</v>
+            <v>13405</v>
           </cell>
           <cell r="D25">
-            <v>773.375</v>
+            <v>788.52941176470586</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>1236</v>
+            <v>1256</v>
           </cell>
           <cell r="D26">
-            <v>77.25</v>
+            <v>73.882352941176464</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>11488</v>
+            <v>11997</v>
           </cell>
           <cell r="D27">
-            <v>718</v>
+            <v>705.70588235294122</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>19062</v>
+            <v>19686</v>
           </cell>
           <cell r="D28">
-            <v>1191.375</v>
+            <v>1158</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>8133</v>
+            <v>8624</v>
           </cell>
           <cell r="D29">
-            <v>508.3125</v>
+            <v>507.29411764705884</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>5983</v>
+            <v>6538</v>
           </cell>
           <cell r="D30">
-            <v>373.9375</v>
+            <v>384.58823529411762</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>810</v>
+            <v>1002</v>
           </cell>
           <cell r="D31">
-            <v>50.625</v>
+            <v>58.941176470588232</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>789</v>
+            <v>966</v>
           </cell>
           <cell r="D32">
-            <v>49.3125</v>
+            <v>56.823529411764703</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>1827</v>
+            <v>1933</v>
           </cell>
           <cell r="D33">
-            <v>114.1875</v>
+            <v>113.70588235294117</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>2103</v>
+            <v>2218</v>
           </cell>
           <cell r="D34">
-            <v>131.4375</v>
+            <v>130.47058823529412</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>9547</v>
+            <v>10343</v>
           </cell>
           <cell r="D35">
-            <v>596.6875</v>
+            <v>608.41176470588232</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>9977</v>
+            <v>10536</v>
           </cell>
           <cell r="D36">
-            <v>623.5625</v>
+            <v>619.76470588235293</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>13247</v>
+            <v>13971</v>
           </cell>
           <cell r="D37">
-            <v>827.9375</v>
+            <v>821.82352941176475</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>8915</v>
+            <v>9401</v>
           </cell>
           <cell r="D38">
-            <v>557.1875</v>
+            <v>553</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>42</v>
+            <v>44</v>
           </cell>
           <cell r="D39">
-            <v>2.625</v>
+            <v>2.5882352941176472</v>
           </cell>
         </row>
         <row r="40">
           <cell r="C40">
-            <v>8</v>
+            <v>9</v>
           </cell>
           <cell r="D40">
-            <v>0.5</v>
+            <v>0.52941176470588236</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>1392</v>
+            <v>1817</v>
           </cell>
           <cell r="D41">
-            <v>87</v>
+            <v>106.88235294117646</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>7945</v>
+            <v>8509</v>
           </cell>
           <cell r="D42">
-            <v>496.5625</v>
+            <v>500.52941176470586</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>665</v>
+            <v>658</v>
           </cell>
           <cell r="D43">
-            <v>41.5625</v>
+            <v>38.705882352941174</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>4594</v>
+            <v>4878</v>
           </cell>
           <cell r="D44">
-            <v>287.125</v>
+            <v>286.94117647058823</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>7723</v>
+            <v>8078</v>
           </cell>
           <cell r="D45">
-            <v>482.6875</v>
+            <v>475.1764705882353</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>4555</v>
+            <v>4691</v>
           </cell>
           <cell r="D46">
-            <v>284.6875</v>
+            <v>275.94117647058823</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>4102</v>
+            <v>4296</v>
           </cell>
           <cell r="D47">
-            <v>256.375</v>
+            <v>252.70588235294119</v>
           </cell>
         </row>
         <row r="48">
           <cell r="C48">
-            <v>755</v>
+            <v>827</v>
           </cell>
           <cell r="D48">
-            <v>47.1875</v>
+            <v>48.647058823529413</v>
           </cell>
         </row>
         <row r="49">
           <cell r="C49">
-            <v>1476</v>
+            <v>1578</v>
           </cell>
           <cell r="D49">
-            <v>92.25</v>
+            <v>92.82352941176471</v>
           </cell>
         </row>
         <row r="50">
           <cell r="C50">
-            <v>789</v>
+            <v>844</v>
           </cell>
           <cell r="D50">
-            <v>49.3125</v>
+            <v>49.647058823529413</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1285,11 +1287,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>18695</v>
+        <v>19802</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1168.4375</v>
+        <v>1164.8235294117646</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1301,11 +1303,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>1231</v>
+        <v>1239</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>76.9375</v>
+        <v>72.882352941176464</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1317,11 +1319,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>7874</v>
+        <v>8245</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>492.125</v>
+        <v>485</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1333,11 +1335,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1429</v>
+        <v>1486</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>89.3125</v>
+        <v>87.411764705882348</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1349,11 +1351,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>10.9375</v>
+        <v>11.176470588235293</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1365,11 +1367,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>22765</v>
+        <v>24109</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1422.8125</v>
+        <v>1418.1764705882354</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1381,11 +1383,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2317</v>
+        <v>2431</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>144.8125</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1397,11 +1399,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>5012</v>
+        <v>5338</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>313.25</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1413,11 +1415,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>11418</v>
+        <v>12299</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>713.625</v>
+        <v>723.47058823529414</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1429,11 +1431,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>5302</v>
+        <v>5814</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>331.375</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1445,11 +1447,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>55927</v>
+        <v>59012</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3495.4375</v>
+        <v>3471.294117647059</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1461,11 +1463,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>36473</v>
+        <v>38309</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2279.5625</v>
+        <v>2253.4705882352941</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1477,11 +1479,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>35567</v>
+        <v>37525</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2222.9375</v>
+        <v>2207.3529411764707</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1493,11 +1495,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>42142</v>
+        <v>44495</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2633.875</v>
+        <v>2617.3529411764707</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1509,11 +1511,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>21.25</v>
+        <v>18.882352941176471</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1525,11 +1527,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$19</f>
-        <v>5025</v>
+        <v>5830</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>314.0625</v>
+        <v>342.94117647058823</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1541,11 +1543,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$20</f>
-        <v>5702</v>
+        <v>6605</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>356.375</v>
+        <v>388.52941176470586</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1557,11 +1559,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$21</f>
-        <v>5480</v>
+        <v>6362</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>342.5</v>
+        <v>374.23529411764707</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1573,11 +1575,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>3611</v>
+        <v>3860</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>225.6875</v>
+        <v>227.05882352941177</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1589,11 +1591,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>2086</v>
+        <v>2226</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>130.375</v>
+        <v>130.94117647058823</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1605,11 +1607,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>7836</v>
+        <v>8484</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>489.75</v>
+        <v>499.05882352941177</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1621,11 +1623,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>12374</v>
+        <v>13405</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>773.375</v>
+        <v>788.52941176470586</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1637,11 +1639,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>1236</v>
+        <v>1256</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>77.25</v>
+        <v>73.882352941176464</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1653,11 +1655,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>11488</v>
+        <v>11997</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>718</v>
+        <v>705.70588235294122</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1669,11 +1671,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>19062</v>
+        <v>19686</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>1191.375</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1685,11 +1687,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>8133</v>
+        <v>8624</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>508.3125</v>
+        <v>507.29411764705884</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1701,11 +1703,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>5983</v>
+        <v>6538</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>373.9375</v>
+        <v>384.58823529411762</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1717,11 +1719,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>810</v>
+        <v>1002</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>50.625</v>
+        <v>58.941176470588232</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1733,11 +1735,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$32</f>
-        <v>789</v>
+        <v>966</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$32</f>
-        <v>49.3125</v>
+        <v>56.823529411764703</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1749,11 +1751,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$33</f>
-        <v>1827</v>
+        <v>1933</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$33</f>
-        <v>114.1875</v>
+        <v>113.70588235294117</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1765,11 +1767,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>789</v>
+        <v>966</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>49.3125</v>
+        <v>56.823529411764703</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1781,11 +1783,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>1827</v>
+        <v>1933</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>114.1875</v>
+        <v>113.70588235294117</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1797,11 +1799,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>2103</v>
+        <v>2218</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>131.4375</v>
+        <v>130.47058823529412</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1813,11 +1815,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>9547</v>
+        <v>10343</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>596.6875</v>
+        <v>608.41176470588232</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1829,11 +1831,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>9977</v>
+        <v>10536</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>623.5625</v>
+        <v>619.76470588235293</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1845,11 +1847,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>13247</v>
+        <v>13971</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>827.9375</v>
+        <v>821.82352941176475</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1861,11 +1863,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>8915</v>
+        <v>9401</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>557.1875</v>
+        <v>553</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1877,11 +1879,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>2.625</v>
+        <v>2.5882352941176472</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1893,11 +1895,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>0.5</v>
+        <v>0.52941176470588236</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1909,11 +1911,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>1392</v>
+        <v>1817</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>87</v>
+        <v>106.88235294117646</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1925,11 +1927,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>7945</v>
+        <v>8509</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>496.5625</v>
+        <v>500.52941176470586</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1941,11 +1943,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>41.5625</v>
+        <v>38.705882352941174</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1957,11 +1959,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>4594</v>
+        <v>4878</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>287.125</v>
+        <v>286.94117647058823</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1973,11 +1975,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>7723</v>
+        <v>8078</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>482.6875</v>
+        <v>475.1764705882353</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1989,11 +1991,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>4555</v>
+        <v>4691</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>284.6875</v>
+        <v>275.94117647058823</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2005,11 +2007,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>4102</v>
+        <v>4296</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>256.375</v>
+        <v>252.70588235294119</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2021,11 +2023,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>755</v>
+        <v>827</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>47.1875</v>
+        <v>48.647058823529413</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2035,11 +2037,11 @@
       </c>
       <c r="C49" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>1476</v>
+        <v>1578</v>
       </c>
       <c r="D49" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>92.25</v>
+        <v>92.82352941176471</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2049,11 +2051,11 @@
       </c>
       <c r="C50" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>789</v>
+        <v>844</v>
       </c>
       <c r="D50" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>49.3125</v>
+        <v>49.647058823529413</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2110,19 +2112,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>420459</v>
+        <v>440459</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$H$3</f>
-        <v>416619</v>
+        <v>442804</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>26278.6875</v>
+        <v>25909.352941176472</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>578131.125</v>
+        <v>570005.76470588241</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2130,11 +2132,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.64783374395052251</v>
+        <v>0.67864929286019138</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-228564</v>
+        <v>-208564</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2170,7 +2172,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>3840</v>
+        <v>-2345</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2186,7 +2188,7 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2157A0-CFFC-470C-ADC3-9549DA66C191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9F4704-FA6D-49BB-904B-0B8A3F35AAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -480,6 +480,8 @@
       <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
+      <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
+      <sheetName val="Hoja1"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -505,36 +507,38 @@
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
-      <sheetData sheetId="20">
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22">
         <row r="3">
           <cell r="G3">
-            <v>440459</v>
+            <v>483786</v>
           </cell>
           <cell r="H3">
-            <v>442804</v>
+            <v>479652</v>
           </cell>
           <cell r="I3">
-            <v>25909.352941176472</v>
+            <v>26877</v>
           </cell>
           <cell r="J3">
-            <v>570005.76470588241</v>
+            <v>591294</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.67864929286019138</v>
+            <v>0.74540655724065252</v>
           </cell>
           <cell r="M3">
-            <v>-208564</v>
+            <v>-165237</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>19802</v>
+            <v>21331</v>
           </cell>
           <cell r="D4">
-            <v>1164.8235294117646</v>
+            <v>1185.0555555555557</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -557,124 +561,124 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>1239</v>
+            <v>1295</v>
           </cell>
           <cell r="D5">
-            <v>72.882352941176464</v>
+            <v>71.944444444444443</v>
           </cell>
           <cell r="G5">
-            <v>-2345</v>
+            <v>4134</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
           </cell>
           <cell r="I5">
-            <v>46259</v>
+            <v>46261</v>
           </cell>
           <cell r="J5">
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>17</v>
+            <v>18</v>
           </cell>
           <cell r="L5">
-            <v>5</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>8245</v>
+            <v>8856</v>
           </cell>
           <cell r="D6">
-            <v>485</v>
+            <v>492</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1486</v>
+            <v>1543</v>
           </cell>
           <cell r="D7">
-            <v>87.411764705882348</v>
+            <v>85.722222222222229</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>190</v>
+            <v>198</v>
           </cell>
           <cell r="D8">
-            <v>11.176470588235293</v>
+            <v>11</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>24109</v>
+            <v>25827</v>
           </cell>
           <cell r="D9">
-            <v>1418.1764705882354</v>
+            <v>1434.8333333333333</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>2431</v>
+            <v>2591</v>
           </cell>
           <cell r="D10">
-            <v>143</v>
+            <v>143.94444444444446</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>5338</v>
+            <v>5792</v>
           </cell>
           <cell r="D11">
-            <v>314</v>
+            <v>321.77777777777777</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>12299</v>
+            <v>13464</v>
           </cell>
           <cell r="D12">
-            <v>723.47058823529414</v>
+            <v>748</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>5814</v>
+            <v>6354</v>
           </cell>
           <cell r="D13">
-            <v>342</v>
+            <v>353</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>59012</v>
+            <v>62600</v>
           </cell>
           <cell r="D14">
-            <v>3471.294117647059</v>
+            <v>3477.7777777777778</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>38309</v>
+            <v>40825</v>
           </cell>
           <cell r="D15">
-            <v>2253.4705882352941</v>
+            <v>2268.0555555555557</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>37525</v>
+            <v>39689</v>
           </cell>
           <cell r="D16">
-            <v>2207.3529411764707</v>
+            <v>2204.9444444444443</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>44495</v>
+            <v>47466</v>
           </cell>
           <cell r="D17">
-            <v>2617.3529411764707</v>
+            <v>2637</v>
           </cell>
         </row>
         <row r="18">
@@ -682,167 +686,167 @@
             <v>321</v>
           </cell>
           <cell r="D18">
-            <v>18.882352941176471</v>
+            <v>17.833333333333332</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>5830</v>
+            <v>6456</v>
           </cell>
           <cell r="D19">
-            <v>342.94117647058823</v>
+            <v>358.66666666666669</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>6605</v>
+            <v>7377</v>
           </cell>
           <cell r="D20">
-            <v>388.52941176470586</v>
+            <v>409.83333333333331</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>6362</v>
+            <v>7059</v>
           </cell>
           <cell r="D21">
-            <v>374.23529411764707</v>
+            <v>392.16666666666669</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>3860</v>
+            <v>4120</v>
           </cell>
           <cell r="D22">
-            <v>227.05882352941177</v>
+            <v>228.88888888888889</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>2226</v>
+            <v>2436</v>
           </cell>
           <cell r="D23">
-            <v>130.94117647058823</v>
+            <v>135.33333333333334</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>8484</v>
+            <v>9192</v>
           </cell>
           <cell r="D24">
-            <v>499.05882352941177</v>
+            <v>510.66666666666669</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>13405</v>
+            <v>14608</v>
           </cell>
           <cell r="D25">
-            <v>788.52941176470586</v>
+            <v>811.55555555555554</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>1256</v>
+            <v>1254</v>
           </cell>
           <cell r="D26">
-            <v>73.882352941176464</v>
+            <v>69.666666666666671</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>11997</v>
+            <v>12765</v>
           </cell>
           <cell r="D27">
-            <v>705.70588235294122</v>
+            <v>709.16666666666663</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>19686</v>
+            <v>20919</v>
           </cell>
           <cell r="D28">
-            <v>1158</v>
+            <v>1162.1666666666667</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>8624</v>
+            <v>9290</v>
           </cell>
           <cell r="D29">
-            <v>507.29411764705884</v>
+            <v>516.11111111111109</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>6538</v>
+            <v>7123</v>
           </cell>
           <cell r="D30">
-            <v>384.58823529411762</v>
+            <v>395.72222222222223</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>1002</v>
+            <v>1219</v>
           </cell>
           <cell r="D31">
-            <v>58.941176470588232</v>
+            <v>67.722222222222229</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>966</v>
+            <v>1178</v>
           </cell>
           <cell r="D32">
-            <v>56.823529411764703</v>
+            <v>65.444444444444443</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>1933</v>
+            <v>2066</v>
           </cell>
           <cell r="D33">
-            <v>113.70588235294117</v>
+            <v>114.77777777777777</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>2218</v>
+            <v>2419</v>
           </cell>
           <cell r="D34">
-            <v>130.47058823529412</v>
+            <v>134.38888888888889</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>10343</v>
+            <v>11470</v>
           </cell>
           <cell r="D35">
-            <v>608.41176470588232</v>
+            <v>637.22222222222217</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>10536</v>
+            <v>11365</v>
           </cell>
           <cell r="D36">
-            <v>619.76470588235293</v>
+            <v>631.38888888888891</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>13971</v>
+            <v>15144</v>
           </cell>
           <cell r="D37">
-            <v>821.82352941176475</v>
+            <v>841.33333333333337</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>9401</v>
+            <v>10263</v>
           </cell>
           <cell r="D38">
-            <v>553</v>
+            <v>570.16666666666663</v>
           </cell>
         </row>
         <row r="39">
@@ -850,7 +854,7 @@
             <v>44</v>
           </cell>
           <cell r="D39">
-            <v>2.5882352941176472</v>
+            <v>2.4444444444444446</v>
           </cell>
         </row>
         <row r="40">
@@ -858,91 +862,91 @@
             <v>9</v>
           </cell>
           <cell r="D40">
-            <v>0.52941176470588236</v>
+            <v>0.5</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>1817</v>
+            <v>2422</v>
           </cell>
           <cell r="D41">
-            <v>106.88235294117646</v>
+            <v>134.55555555555554</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>8509</v>
+            <v>9460</v>
           </cell>
           <cell r="D42">
-            <v>500.52941176470586</v>
+            <v>525.55555555555554</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>658</v>
+            <v>685</v>
           </cell>
           <cell r="D43">
-            <v>38.705882352941174</v>
+            <v>38.055555555555557</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>4878</v>
+            <v>5446</v>
           </cell>
           <cell r="D44">
-            <v>286.94117647058823</v>
+            <v>302.55555555555554</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>8078</v>
+            <v>9712</v>
           </cell>
           <cell r="D45">
-            <v>475.1764705882353</v>
+            <v>539.55555555555554</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>4691</v>
+            <v>5691</v>
           </cell>
           <cell r="D46">
-            <v>275.94117647058823</v>
+            <v>316.16666666666669</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>4296</v>
+            <v>5281</v>
           </cell>
           <cell r="D47">
-            <v>252.70588235294119</v>
+            <v>293.38888888888891</v>
           </cell>
         </row>
         <row r="48">
           <cell r="C48">
-            <v>827</v>
+            <v>1095</v>
           </cell>
           <cell r="D48">
-            <v>48.647058823529413</v>
+            <v>60.833333333333336</v>
           </cell>
         </row>
         <row r="49">
           <cell r="C49">
-            <v>1578</v>
+            <v>1965</v>
           </cell>
           <cell r="D49">
-            <v>92.82352941176471</v>
+            <v>109.16666666666667</v>
           </cell>
         </row>
         <row r="50">
           <cell r="C50">
-            <v>844</v>
+            <v>932</v>
           </cell>
           <cell r="D50">
-            <v>49.647058823529413</v>
+            <v>51.777777777777779</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="21"/>
+      <sheetData sheetId="23"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1287,11 +1291,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>19802</v>
+        <v>21331</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1164.8235294117646</v>
+        <v>1185.0555555555557</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1303,11 +1307,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>1239</v>
+        <v>1295</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>72.882352941176464</v>
+        <v>71.944444444444443</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1319,11 +1323,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>8245</v>
+        <v>8856</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1335,11 +1339,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1486</v>
+        <v>1543</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>87.411764705882348</v>
+        <v>85.722222222222229</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1351,11 +1355,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>11.176470588235293</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1367,11 +1371,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>24109</v>
+        <v>25827</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1418.1764705882354</v>
+        <v>1434.8333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1383,11 +1387,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2431</v>
+        <v>2591</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>143</v>
+        <v>143.94444444444446</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1399,11 +1403,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>5338</v>
+        <v>5792</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>314</v>
+        <v>321.77777777777777</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1415,11 +1419,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>12299</v>
+        <v>13464</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>723.47058823529414</v>
+        <v>748</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1431,11 +1435,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>5814</v>
+        <v>6354</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1447,11 +1451,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>59012</v>
+        <v>62600</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3471.294117647059</v>
+        <v>3477.7777777777778</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1463,11 +1467,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>38309</v>
+        <v>40825</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2253.4705882352941</v>
+        <v>2268.0555555555557</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1479,11 +1483,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>37525</v>
+        <v>39689</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2207.3529411764707</v>
+        <v>2204.9444444444443</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1495,11 +1499,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>44495</v>
+        <v>47466</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2617.3529411764707</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1515,7 +1519,7 @@
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>18.882352941176471</v>
+        <v>17.833333333333332</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1527,11 +1531,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$19</f>
-        <v>5830</v>
+        <v>6456</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>342.94117647058823</v>
+        <v>358.66666666666669</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1543,11 +1547,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$20</f>
-        <v>6605</v>
+        <v>7377</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>388.52941176470586</v>
+        <v>409.83333333333331</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1559,11 +1563,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$21</f>
-        <v>6362</v>
+        <v>7059</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>374.23529411764707</v>
+        <v>392.16666666666669</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1575,11 +1579,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>3860</v>
+        <v>4120</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>227.05882352941177</v>
+        <v>228.88888888888889</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1591,11 +1595,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>2226</v>
+        <v>2436</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>130.94117647058823</v>
+        <v>135.33333333333334</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1607,11 +1611,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>8484</v>
+        <v>9192</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>499.05882352941177</v>
+        <v>510.66666666666669</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1623,11 +1627,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>13405</v>
+        <v>14608</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>788.52941176470586</v>
+        <v>811.55555555555554</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1639,11 +1643,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>73.882352941176464</v>
+        <v>69.666666666666671</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1655,11 +1659,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>11997</v>
+        <v>12765</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>705.70588235294122</v>
+        <v>709.16666666666663</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1671,11 +1675,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>19686</v>
+        <v>20919</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>1158</v>
+        <v>1162.1666666666667</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1687,11 +1691,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>8624</v>
+        <v>9290</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>507.29411764705884</v>
+        <v>516.11111111111109</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1703,11 +1707,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>6538</v>
+        <v>7123</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>384.58823529411762</v>
+        <v>395.72222222222223</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1719,11 +1723,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>1002</v>
+        <v>1219</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>58.941176470588232</v>
+        <v>67.722222222222229</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1735,11 +1739,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$32</f>
-        <v>966</v>
+        <v>1178</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$32</f>
-        <v>56.823529411764703</v>
+        <v>65.444444444444443</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1751,11 +1755,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$33</f>
-        <v>1933</v>
+        <v>2066</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$33</f>
-        <v>113.70588235294117</v>
+        <v>114.77777777777777</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1767,11 +1771,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>966</v>
+        <v>1178</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>56.823529411764703</v>
+        <v>65.444444444444443</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1783,11 +1787,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>1933</v>
+        <v>2066</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>113.70588235294117</v>
+        <v>114.77777777777777</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1799,11 +1803,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>2218</v>
+        <v>2419</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>130.47058823529412</v>
+        <v>134.38888888888889</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1815,11 +1819,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>10343</v>
+        <v>11470</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>608.41176470588232</v>
+        <v>637.22222222222217</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1831,11 +1835,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>10536</v>
+        <v>11365</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>619.76470588235293</v>
+        <v>631.38888888888891</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1847,11 +1851,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>13971</v>
+        <v>15144</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>821.82352941176475</v>
+        <v>841.33333333333337</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1863,11 +1867,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>9401</v>
+        <v>10263</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>553</v>
+        <v>570.16666666666663</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1883,7 +1887,7 @@
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>2.5882352941176472</v>
+        <v>2.4444444444444446</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1899,7 +1903,7 @@
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>0.52941176470588236</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1911,11 +1915,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>1817</v>
+        <v>2422</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>106.88235294117646</v>
+        <v>134.55555555555554</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1927,11 +1931,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>8509</v>
+        <v>9460</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>500.52941176470586</v>
+        <v>525.55555555555554</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1943,11 +1947,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>658</v>
+        <v>685</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>38.705882352941174</v>
+        <v>38.055555555555557</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1959,11 +1963,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>4878</v>
+        <v>5446</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>286.94117647058823</v>
+        <v>302.55555555555554</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1975,11 +1979,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>8078</v>
+        <v>9712</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>475.1764705882353</v>
+        <v>539.55555555555554</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1991,11 +1995,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>4691</v>
+        <v>5691</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>275.94117647058823</v>
+        <v>316.16666666666669</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2007,11 +2011,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>4296</v>
+        <v>5281</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>252.70588235294119</v>
+        <v>293.38888888888891</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2023,11 +2027,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>827</v>
+        <v>1095</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>48.647058823529413</v>
+        <v>60.833333333333336</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2037,11 +2041,11 @@
       </c>
       <c r="C49" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>1578</v>
+        <v>1965</v>
       </c>
       <c r="D49" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>92.82352941176471</v>
+        <v>109.16666666666667</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2051,11 +2055,11 @@
       </c>
       <c r="C50" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>844</v>
+        <v>932</v>
       </c>
       <c r="D50" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>49.647058823529413</v>
+        <v>51.777777777777779</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2112,19 +2116,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>440459</v>
+        <v>483786</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$H$3</f>
-        <v>442804</v>
+        <v>479652</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>25909.352941176472</v>
+        <v>26877</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>570005.76470588241</v>
+        <v>591294</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2132,11 +2136,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.67864929286019138</v>
+        <v>0.74540655724065252</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-208564</v>
+        <v>-165237</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2172,7 +2176,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>-2345</v>
+        <v>4134</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2180,7 +2184,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2188,11 +2192,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9F4704-FA6D-49BB-904B-0B8A3F35AAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A32876-6FE2-47DF-9692-90019904B731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <externalReferences>
     <externalReference r:id="rId3"/>
   </externalReferences>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -481,6 +481,7 @@
       <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 28-08-26"/>
       <sheetName val="Hoja1"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -509,36 +510,37 @@
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
-      <sheetData sheetId="22">
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23">
         <row r="3">
           <cell r="G3">
-            <v>483786</v>
+            <v>501124</v>
           </cell>
           <cell r="H3">
-            <v>479652</v>
+            <v>505258</v>
           </cell>
           <cell r="I3">
-            <v>26877</v>
+            <v>26592.526315789473</v>
           </cell>
           <cell r="J3">
-            <v>591294</v>
+            <v>558443.05263157899</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.74540655724065252</v>
+            <v>0.77212055659044443</v>
           </cell>
           <cell r="M3">
-            <v>-165237</v>
+            <v>-147899</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>21331</v>
+            <v>22253</v>
           </cell>
           <cell r="D4">
-            <v>1185.0555555555557</v>
+            <v>1171.2105263157894</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -561,10 +563,10 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>1295</v>
+            <v>1372</v>
           </cell>
           <cell r="D5">
-            <v>71.944444444444443</v>
+            <v>72.21052631578948</v>
           </cell>
           <cell r="G5">
             <v>4134</v>
@@ -573,288 +575,288 @@
             <v>46237</v>
           </cell>
           <cell r="I5">
-            <v>46261</v>
+            <v>46262</v>
           </cell>
           <cell r="J5">
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>18</v>
+            <v>19</v>
           </cell>
           <cell r="L5">
-            <v>3</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>8856</v>
+            <v>9372</v>
           </cell>
           <cell r="D6">
-            <v>492</v>
+            <v>493.26315789473682</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1543</v>
+            <v>1657</v>
           </cell>
           <cell r="D7">
-            <v>85.722222222222229</v>
+            <v>87.21052631578948</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>198</v>
+            <v>219</v>
           </cell>
           <cell r="D8">
-            <v>11</v>
+            <v>11.526315789473685</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>25827</v>
+            <v>27315</v>
           </cell>
           <cell r="D9">
-            <v>1434.8333333333333</v>
+            <v>1437.6315789473683</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>2591</v>
+            <v>2701</v>
           </cell>
           <cell r="D10">
-            <v>143.94444444444446</v>
+            <v>142.15789473684211</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>5792</v>
+            <v>6214</v>
           </cell>
           <cell r="D11">
-            <v>321.77777777777777</v>
+            <v>327.05263157894734</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>13464</v>
+            <v>14202</v>
           </cell>
           <cell r="D12">
-            <v>748</v>
+            <v>747.47368421052636</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>6354</v>
+            <v>6620</v>
           </cell>
           <cell r="D13">
-            <v>353</v>
+            <v>348.42105263157896</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>62600</v>
+            <v>65735</v>
           </cell>
           <cell r="D14">
-            <v>3477.7777777777778</v>
+            <v>3459.7368421052633</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>40825</v>
+            <v>42819</v>
           </cell>
           <cell r="D15">
-            <v>2268.0555555555557</v>
+            <v>2253.6315789473683</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>39689</v>
+            <v>41641</v>
           </cell>
           <cell r="D16">
-            <v>2204.9444444444443</v>
+            <v>2191.6315789473683</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>47466</v>
+            <v>49875</v>
           </cell>
           <cell r="D17">
-            <v>2637</v>
+            <v>2625</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>321</v>
+            <v>286</v>
           </cell>
           <cell r="D18">
-            <v>17.833333333333332</v>
+            <v>15.052631578947368</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>6456</v>
+            <v>6944</v>
           </cell>
           <cell r="D19">
-            <v>358.66666666666669</v>
+            <v>365.4736842105263</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>7377</v>
+            <v>7836</v>
           </cell>
           <cell r="D20">
-            <v>409.83333333333331</v>
+            <v>412.42105263157896</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>7059</v>
+            <v>7432</v>
           </cell>
           <cell r="D21">
-            <v>392.16666666666669</v>
+            <v>391.15789473684208</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>4120</v>
+            <v>4394</v>
           </cell>
           <cell r="D22">
-            <v>228.88888888888889</v>
+            <v>231.26315789473685</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>2436</v>
+            <v>2566</v>
           </cell>
           <cell r="D23">
-            <v>135.33333333333334</v>
+            <v>135.05263157894737</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>9192</v>
+            <v>9587</v>
           </cell>
           <cell r="D24">
-            <v>510.66666666666669</v>
+            <v>504.57894736842104</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>14608</v>
+            <v>15155</v>
           </cell>
           <cell r="D25">
-            <v>811.55555555555554</v>
+            <v>797.63157894736844</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>1254</v>
+            <v>1274</v>
           </cell>
           <cell r="D26">
-            <v>69.666666666666671</v>
+            <v>67.05263157894737</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>12765</v>
+            <v>13543</v>
           </cell>
           <cell r="D27">
-            <v>709.16666666666663</v>
+            <v>712.78947368421052</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>20919</v>
+            <v>22455</v>
           </cell>
           <cell r="D28">
-            <v>1162.1666666666667</v>
+            <v>1181.8421052631579</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>9290</v>
+            <v>9733</v>
           </cell>
           <cell r="D29">
-            <v>516.11111111111109</v>
+            <v>512.26315789473688</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>7123</v>
+            <v>7551</v>
           </cell>
           <cell r="D30">
-            <v>395.72222222222223</v>
+            <v>397.42105263157896</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>1219</v>
+            <v>1396</v>
           </cell>
           <cell r="D31">
-            <v>67.722222222222229</v>
+            <v>73.473684210526315</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>1178</v>
+            <v>1331</v>
           </cell>
           <cell r="D32">
-            <v>65.444444444444443</v>
+            <v>70.05263157894737</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>2066</v>
+            <v>2196</v>
           </cell>
           <cell r="D33">
-            <v>114.77777777777777</v>
+            <v>115.57894736842105</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>2419</v>
+            <v>2511</v>
           </cell>
           <cell r="D34">
-            <v>134.38888888888889</v>
+            <v>132.15789473684211</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>11470</v>
+            <v>12271</v>
           </cell>
           <cell r="D35">
-            <v>637.22222222222217</v>
+            <v>645.84210526315792</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>11365</v>
+            <v>11967</v>
           </cell>
           <cell r="D36">
-            <v>631.38888888888891</v>
+            <v>629.84210526315792</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>15144</v>
+            <v>15894</v>
           </cell>
           <cell r="D37">
-            <v>841.33333333333337</v>
+            <v>836.52631578947364</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>10263</v>
+            <v>10808</v>
           </cell>
           <cell r="D38">
-            <v>570.16666666666663</v>
+            <v>568.84210526315792</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>44</v>
+            <v>47</v>
           </cell>
           <cell r="D39">
-            <v>2.4444444444444446</v>
+            <v>2.4736842105263159</v>
           </cell>
         </row>
         <row r="40">
@@ -862,91 +864,91 @@
             <v>9</v>
           </cell>
           <cell r="D40">
-            <v>0.5</v>
+            <v>0.47368421052631576</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>2422</v>
+            <v>2567</v>
           </cell>
           <cell r="D41">
-            <v>134.55555555555554</v>
+            <v>135.10526315789474</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>9460</v>
+            <v>9957</v>
           </cell>
           <cell r="D42">
-            <v>525.55555555555554</v>
+            <v>524.0526315789474</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>685</v>
+            <v>1122</v>
           </cell>
           <cell r="D43">
-            <v>38.055555555555557</v>
+            <v>59.05263157894737</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>5446</v>
+            <v>5712</v>
           </cell>
           <cell r="D44">
-            <v>302.55555555555554</v>
+            <v>300.63157894736844</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>9712</v>
+            <v>10090</v>
           </cell>
           <cell r="D45">
-            <v>539.55555555555554</v>
+            <v>531.0526315789474</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>5691</v>
+            <v>5892</v>
           </cell>
           <cell r="D46">
-            <v>316.16666666666669</v>
+            <v>310.10526315789474</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>5281</v>
+            <v>5525</v>
           </cell>
           <cell r="D47">
-            <v>293.38888888888891</v>
+            <v>290.78947368421052</v>
           </cell>
         </row>
         <row r="48">
           <cell r="C48">
-            <v>1095</v>
+            <v>1116</v>
           </cell>
           <cell r="D48">
-            <v>60.833333333333336</v>
+            <v>58.736842105263158</v>
           </cell>
         </row>
         <row r="49">
           <cell r="C49">
-            <v>1965</v>
+            <v>2046</v>
           </cell>
           <cell r="D49">
-            <v>109.16666666666667</v>
+            <v>107.68421052631579</v>
           </cell>
         </row>
         <row r="50">
           <cell r="C50">
-            <v>932</v>
+            <v>971</v>
           </cell>
           <cell r="D50">
-            <v>51.777777777777779</v>
+            <v>51.10526315789474</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1291,11 +1293,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>21331</v>
+        <v>22253</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1185.0555555555557</v>
+        <v>1171.2105263157894</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1307,11 +1309,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>1295</v>
+        <v>1372</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>71.944444444444443</v>
+        <v>72.21052631578948</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1323,11 +1325,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>8856</v>
+        <v>9372</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>492</v>
+        <v>493.26315789473682</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1339,11 +1341,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1543</v>
+        <v>1657</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>85.722222222222229</v>
+        <v>87.21052631578948</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1355,11 +1357,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>11</v>
+        <v>11.526315789473685</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1371,11 +1373,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>25827</v>
+        <v>27315</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1434.8333333333333</v>
+        <v>1437.6315789473683</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1387,11 +1389,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2591</v>
+        <v>2701</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>143.94444444444446</v>
+        <v>142.15789473684211</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1403,11 +1405,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>5792</v>
+        <v>6214</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>321.77777777777777</v>
+        <v>327.05263157894734</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1419,11 +1421,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>13464</v>
+        <v>14202</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>748</v>
+        <v>747.47368421052636</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1435,11 +1437,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>6354</v>
+        <v>6620</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>353</v>
+        <v>348.42105263157896</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1451,11 +1453,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>62600</v>
+        <v>65735</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3477.7777777777778</v>
+        <v>3459.7368421052633</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1467,11 +1469,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>40825</v>
+        <v>42819</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2268.0555555555557</v>
+        <v>2253.6315789473683</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1483,11 +1485,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>39689</v>
+        <v>41641</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2204.9444444444443</v>
+        <v>2191.6315789473683</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1499,11 +1501,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>47466</v>
+        <v>49875</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2637</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1515,11 +1517,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>321</v>
+        <v>286</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>17.833333333333332</v>
+        <v>15.052631578947368</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1531,11 +1533,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$19</f>
-        <v>6456</v>
+        <v>6944</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>358.66666666666669</v>
+        <v>365.4736842105263</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1547,11 +1549,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$20</f>
-        <v>7377</v>
+        <v>7836</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>409.83333333333331</v>
+        <v>412.42105263157896</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1563,11 +1565,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$21</f>
-        <v>7059</v>
+        <v>7432</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>392.16666666666669</v>
+        <v>391.15789473684208</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1579,11 +1581,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>4120</v>
+        <v>4394</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>228.88888888888889</v>
+        <v>231.26315789473685</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1595,11 +1597,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>2436</v>
+        <v>2566</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>135.33333333333334</v>
+        <v>135.05263157894737</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1611,11 +1613,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>9192</v>
+        <v>9587</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>510.66666666666669</v>
+        <v>504.57894736842104</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1627,11 +1629,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>14608</v>
+        <v>15155</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>811.55555555555554</v>
+        <v>797.63157894736844</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1643,11 +1645,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>1254</v>
+        <v>1274</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>69.666666666666671</v>
+        <v>67.05263157894737</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1659,11 +1661,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>12765</v>
+        <v>13543</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>709.16666666666663</v>
+        <v>712.78947368421052</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1675,11 +1677,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>20919</v>
+        <v>22455</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>1162.1666666666667</v>
+        <v>1181.8421052631579</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1691,11 +1693,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>9290</v>
+        <v>9733</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>516.11111111111109</v>
+        <v>512.26315789473688</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1707,11 +1709,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>7123</v>
+        <v>7551</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>395.72222222222223</v>
+        <v>397.42105263157896</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1723,11 +1725,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>1219</v>
+        <v>1396</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>67.722222222222229</v>
+        <v>73.473684210526315</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1739,11 +1741,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$32</f>
-        <v>1178</v>
+        <v>1331</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$32</f>
-        <v>65.444444444444443</v>
+        <v>70.05263157894737</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1755,11 +1757,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$33</f>
-        <v>2066</v>
+        <v>2196</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$33</f>
-        <v>114.77777777777777</v>
+        <v>115.57894736842105</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1771,11 +1773,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1178</v>
+        <v>1331</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>65.444444444444443</v>
+        <v>70.05263157894737</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1787,11 +1789,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>2066</v>
+        <v>2196</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>114.77777777777777</v>
+        <v>115.57894736842105</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1803,11 +1805,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>2419</v>
+        <v>2511</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>134.38888888888889</v>
+        <v>132.15789473684211</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1819,11 +1821,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>11470</v>
+        <v>12271</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>637.22222222222217</v>
+        <v>645.84210526315792</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1835,11 +1837,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>11365</v>
+        <v>11967</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>631.38888888888891</v>
+        <v>629.84210526315792</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1851,11 +1853,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>15144</v>
+        <v>15894</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>841.33333333333337</v>
+        <v>836.52631578947364</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1867,11 +1869,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>10263</v>
+        <v>10808</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>570.16666666666663</v>
+        <v>568.84210526315792</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1883,11 +1885,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>2.4444444444444446</v>
+        <v>2.4736842105263159</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1903,7 +1905,7 @@
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>0.5</v>
+        <v>0.47368421052631576</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1915,11 +1917,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>2422</v>
+        <v>2567</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>134.55555555555554</v>
+        <v>135.10526315789474</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1931,11 +1933,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>9460</v>
+        <v>9957</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>525.55555555555554</v>
+        <v>524.0526315789474</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1947,11 +1949,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>685</v>
+        <v>1122</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>38.055555555555557</v>
+        <v>59.05263157894737</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1963,11 +1965,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>5446</v>
+        <v>5712</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>302.55555555555554</v>
+        <v>300.63157894736844</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1979,11 +1981,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>9712</v>
+        <v>10090</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>539.55555555555554</v>
+        <v>531.0526315789474</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1995,11 +1997,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>5691</v>
+        <v>5892</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>316.16666666666669</v>
+        <v>310.10526315789474</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2011,11 +2013,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>5281</v>
+        <v>5525</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>293.38888888888891</v>
+        <v>290.78947368421052</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2027,11 +2029,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>60.833333333333336</v>
+        <v>58.736842105263158</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2041,11 +2043,11 @@
       </c>
       <c r="C49" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>1965</v>
+        <v>2046</v>
       </c>
       <c r="D49" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>109.16666666666667</v>
+        <v>107.68421052631579</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2055,11 +2057,11 @@
       </c>
       <c r="C50" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>932</v>
+        <v>971</v>
       </c>
       <c r="D50" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>51.777777777777779</v>
+        <v>51.10526315789474</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2116,19 +2118,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>483786</v>
+        <v>501124</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$H$3</f>
-        <v>479652</v>
+        <v>505258</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>26877</v>
+        <v>26592.526315789473</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>591294</v>
+        <v>558443.05263157899</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2136,11 +2138,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.74540655724065252</v>
+        <v>0.77212055659044443</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-165237</v>
+        <v>-147899</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2184,7 +2186,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2192,11 +2194,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A32876-6FE2-47DF-9692-90019904B731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765EFE32-98AC-49FE-8331-5D6BE24F689E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -482,7 +482,8 @@
       <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-08-26"/>
-      <sheetName val="Hoja1"/>
+      <sheetName val="INVENTARIO NACIONAL 31-08-26"/>
+      <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -511,36 +512,37 @@
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
-      <sheetData sheetId="23">
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24">
         <row r="3">
           <cell r="G3">
-            <v>501124</v>
+            <v>521390</v>
           </cell>
           <cell r="H3">
-            <v>505258</v>
+            <v>525524</v>
           </cell>
           <cell r="I3">
-            <v>26592.526315789473</v>
+            <v>26276.2</v>
           </cell>
           <cell r="J3">
-            <v>558443.05263157899</v>
+            <v>551800.19999999995</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.77212055659044443</v>
+            <v>0.80334595230061179</v>
           </cell>
           <cell r="M3">
-            <v>-147899</v>
+            <v>-127633</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>22253</v>
+            <v>22945</v>
           </cell>
           <cell r="D4">
-            <v>1171.2105263157894</v>
+            <v>1147.25</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -563,10 +565,10 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>1372</v>
+            <v>1501</v>
           </cell>
           <cell r="D5">
-            <v>72.21052631578948</v>
+            <v>75.05</v>
           </cell>
           <cell r="G5">
             <v>4134</v>
@@ -575,176 +577,176 @@
             <v>46237</v>
           </cell>
           <cell r="I5">
-            <v>46262</v>
+            <v>46265</v>
           </cell>
           <cell r="J5">
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>19</v>
+            <v>20</v>
           </cell>
           <cell r="L5">
-            <v>2</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>9372</v>
+            <v>9703</v>
           </cell>
           <cell r="D6">
-            <v>493.26315789473682</v>
+            <v>485.15</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1657</v>
+            <v>1765</v>
           </cell>
           <cell r="D7">
-            <v>87.21052631578948</v>
+            <v>88.25</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>219</v>
+            <v>244</v>
           </cell>
           <cell r="D8">
-            <v>11.526315789473685</v>
+            <v>12.2</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>27315</v>
+            <v>28306</v>
           </cell>
           <cell r="D9">
-            <v>1437.6315789473683</v>
+            <v>1415.3</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>2701</v>
+            <v>2797</v>
           </cell>
           <cell r="D10">
-            <v>142.15789473684211</v>
+            <v>139.85</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>6214</v>
+            <v>6437</v>
           </cell>
           <cell r="D11">
-            <v>327.05263157894734</v>
+            <v>321.85000000000002</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>14202</v>
+            <v>14952</v>
           </cell>
           <cell r="D12">
-            <v>747.47368421052636</v>
+            <v>747.6</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>6620</v>
+            <v>7013</v>
           </cell>
           <cell r="D13">
-            <v>348.42105263157896</v>
+            <v>350.65</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>65735</v>
+            <v>68059</v>
           </cell>
           <cell r="D14">
-            <v>3459.7368421052633</v>
+            <v>3402.95</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>42819</v>
+            <v>44386</v>
           </cell>
           <cell r="D15">
-            <v>2253.6315789473683</v>
+            <v>2219.3000000000002</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>41641</v>
+            <v>42963</v>
           </cell>
           <cell r="D16">
-            <v>2191.6315789473683</v>
+            <v>2148.15</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>49875</v>
+            <v>51465</v>
           </cell>
           <cell r="D17">
-            <v>2625</v>
+            <v>2573.25</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>286</v>
+            <v>194</v>
           </cell>
           <cell r="D18">
-            <v>15.052631578947368</v>
+            <v>9.6999999999999993</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>6944</v>
+            <v>7342</v>
           </cell>
           <cell r="D19">
-            <v>365.4736842105263</v>
+            <v>367.1</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>7836</v>
+            <v>8294</v>
           </cell>
           <cell r="D20">
-            <v>412.42105263157896</v>
+            <v>414.7</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>7432</v>
+            <v>7683</v>
           </cell>
           <cell r="D21">
-            <v>391.15789473684208</v>
+            <v>384.15</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>4394</v>
+            <v>4655</v>
           </cell>
           <cell r="D22">
-            <v>231.26315789473685</v>
+            <v>232.75</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>2566</v>
+            <v>2711</v>
           </cell>
           <cell r="D23">
-            <v>135.05263157894737</v>
+            <v>135.55000000000001</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>9587</v>
+            <v>9927</v>
           </cell>
           <cell r="D24">
-            <v>504.57894736842104</v>
+            <v>496.35</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>15155</v>
+            <v>15700</v>
           </cell>
           <cell r="D25">
-            <v>797.63157894736844</v>
+            <v>785</v>
           </cell>
         </row>
         <row r="26">
@@ -752,103 +754,103 @@
             <v>1274</v>
           </cell>
           <cell r="D26">
-            <v>67.05263157894737</v>
+            <v>63.7</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>13543</v>
+            <v>14193</v>
           </cell>
           <cell r="D27">
-            <v>712.78947368421052</v>
+            <v>709.65</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>22455</v>
+            <v>23259</v>
           </cell>
           <cell r="D28">
-            <v>1181.8421052631579</v>
+            <v>1162.95</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>9733</v>
+            <v>10205</v>
           </cell>
           <cell r="D29">
-            <v>512.26315789473688</v>
+            <v>510.25</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>7551</v>
+            <v>8012</v>
           </cell>
           <cell r="D30">
-            <v>397.42105263157896</v>
+            <v>400.6</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>1396</v>
+            <v>1418</v>
           </cell>
           <cell r="D31">
-            <v>73.473684210526315</v>
+            <v>70.900000000000006</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>1331</v>
+            <v>1350</v>
           </cell>
           <cell r="D32">
-            <v>70.05263157894737</v>
+            <v>67.5</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>2196</v>
+            <v>2368</v>
           </cell>
           <cell r="D33">
-            <v>115.57894736842105</v>
+            <v>118.4</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>2511</v>
+            <v>2685</v>
           </cell>
           <cell r="D34">
-            <v>132.15789473684211</v>
+            <v>134.25</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>12271</v>
+            <v>12822</v>
           </cell>
           <cell r="D35">
-            <v>645.84210526315792</v>
+            <v>641.1</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>11967</v>
+            <v>12402</v>
           </cell>
           <cell r="D36">
-            <v>629.84210526315792</v>
+            <v>620.1</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>15894</v>
+            <v>16577</v>
           </cell>
           <cell r="D37">
-            <v>836.52631578947364</v>
+            <v>828.85</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>10808</v>
+            <v>11287</v>
           </cell>
           <cell r="D38">
-            <v>568.84210526315792</v>
+            <v>564.35</v>
           </cell>
         </row>
         <row r="39">
@@ -856,7 +858,7 @@
             <v>47</v>
           </cell>
           <cell r="D39">
-            <v>2.4736842105263159</v>
+            <v>2.35</v>
           </cell>
         </row>
         <row r="40">
@@ -864,91 +866,91 @@
             <v>9</v>
           </cell>
           <cell r="D40">
-            <v>0.47368421052631576</v>
+            <v>0.45</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>2567</v>
+            <v>2729</v>
           </cell>
           <cell r="D41">
-            <v>135.10526315789474</v>
+            <v>136.44999999999999</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>9957</v>
+            <v>10580</v>
           </cell>
           <cell r="D42">
-            <v>524.0526315789474</v>
+            <v>529</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>1122</v>
+            <v>1577</v>
           </cell>
           <cell r="D43">
-            <v>59.05263157894737</v>
+            <v>78.849999999999994</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>5712</v>
+            <v>5929</v>
           </cell>
           <cell r="D44">
-            <v>300.63157894736844</v>
+            <v>296.45</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>10090</v>
+            <v>10492</v>
           </cell>
           <cell r="D45">
-            <v>531.0526315789474</v>
+            <v>524.6</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>5892</v>
+            <v>6154</v>
           </cell>
           <cell r="D46">
-            <v>310.10526315789474</v>
+            <v>307.7</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>5525</v>
+            <v>5824</v>
           </cell>
           <cell r="D47">
-            <v>290.78947368421052</v>
+            <v>291.2</v>
           </cell>
         </row>
         <row r="48">
           <cell r="C48">
-            <v>1116</v>
+            <v>1126</v>
           </cell>
           <cell r="D48">
-            <v>58.736842105263158</v>
+            <v>56.3</v>
           </cell>
         </row>
         <row r="49">
           <cell r="C49">
-            <v>2046</v>
+            <v>2091</v>
           </cell>
           <cell r="D49">
-            <v>107.68421052631579</v>
+            <v>104.55</v>
           </cell>
         </row>
         <row r="50">
           <cell r="C50">
-            <v>971</v>
+            <v>984</v>
           </cell>
           <cell r="D50">
-            <v>51.10526315789474</v>
+            <v>49.2</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1293,11 +1295,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>22253</v>
+        <v>22945</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1171.2105263157894</v>
+        <v>1147.25</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1309,11 +1311,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>1372</v>
+        <v>1501</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>72.21052631578948</v>
+        <v>75.05</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1325,11 +1327,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>9372</v>
+        <v>9703</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>493.26315789473682</v>
+        <v>485.15</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1341,11 +1343,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1657</v>
+        <v>1765</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>87.21052631578948</v>
+        <v>88.25</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1357,11 +1359,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>11.526315789473685</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1373,11 +1375,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>27315</v>
+        <v>28306</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1437.6315789473683</v>
+        <v>1415.3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1389,11 +1391,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2701</v>
+        <v>2797</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>142.15789473684211</v>
+        <v>139.85</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1405,11 +1407,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>6214</v>
+        <v>6437</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>327.05263157894734</v>
+        <v>321.85000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1421,11 +1423,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>14202</v>
+        <v>14952</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>747.47368421052636</v>
+        <v>747.6</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1437,11 +1439,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>6620</v>
+        <v>7013</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>348.42105263157896</v>
+        <v>350.65</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1453,11 +1455,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>65735</v>
+        <v>68059</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3459.7368421052633</v>
+        <v>3402.95</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1469,11 +1471,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>42819</v>
+        <v>44386</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2253.6315789473683</v>
+        <v>2219.3000000000002</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1485,11 +1487,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>41641</v>
+        <v>42963</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2191.6315789473683</v>
+        <v>2148.15</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1501,11 +1503,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>49875</v>
+        <v>51465</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2625</v>
+        <v>2573.25</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1517,11 +1519,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>286</v>
+        <v>194</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>15.052631578947368</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1533,11 +1535,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$19</f>
-        <v>6944</v>
+        <v>7342</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>365.4736842105263</v>
+        <v>367.1</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1549,11 +1551,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$20</f>
-        <v>7836</v>
+        <v>8294</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>412.42105263157896</v>
+        <v>414.7</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1565,11 +1567,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$21</f>
-        <v>7432</v>
+        <v>7683</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>391.15789473684208</v>
+        <v>384.15</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1581,11 +1583,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>4394</v>
+        <v>4655</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>231.26315789473685</v>
+        <v>232.75</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1597,11 +1599,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>2566</v>
+        <v>2711</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>135.05263157894737</v>
+        <v>135.55000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1613,11 +1615,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>9587</v>
+        <v>9927</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>504.57894736842104</v>
+        <v>496.35</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1629,11 +1631,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>15155</v>
+        <v>15700</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>797.63157894736844</v>
+        <v>785</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1649,7 +1651,7 @@
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>67.05263157894737</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1661,11 +1663,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>13543</v>
+        <v>14193</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>712.78947368421052</v>
+        <v>709.65</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1677,11 +1679,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>22455</v>
+        <v>23259</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>1181.8421052631579</v>
+        <v>1162.95</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1693,11 +1695,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>9733</v>
+        <v>10205</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>512.26315789473688</v>
+        <v>510.25</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1709,11 +1711,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>7551</v>
+        <v>8012</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>397.42105263157896</v>
+        <v>400.6</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1725,11 +1727,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>1396</v>
+        <v>1418</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>73.473684210526315</v>
+        <v>70.900000000000006</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1741,11 +1743,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$32</f>
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$32</f>
-        <v>70.05263157894737</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1757,11 +1759,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$33</f>
-        <v>2196</v>
+        <v>2368</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$33</f>
-        <v>115.57894736842105</v>
+        <v>118.4</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1773,11 +1775,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>70.05263157894737</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1789,11 +1791,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>2196</v>
+        <v>2368</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>115.57894736842105</v>
+        <v>118.4</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1805,11 +1807,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>2511</v>
+        <v>2685</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>132.15789473684211</v>
+        <v>134.25</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1821,11 +1823,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>12271</v>
+        <v>12822</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>645.84210526315792</v>
+        <v>641.1</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1837,11 +1839,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>11967</v>
+        <v>12402</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>629.84210526315792</v>
+        <v>620.1</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1853,11 +1855,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>15894</v>
+        <v>16577</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>836.52631578947364</v>
+        <v>828.85</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1869,11 +1871,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>10808</v>
+        <v>11287</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>568.84210526315792</v>
+        <v>564.35</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1889,7 +1891,7 @@
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>2.4736842105263159</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1905,7 +1907,7 @@
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>0.47368421052631576</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1917,11 +1919,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>2567</v>
+        <v>2729</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>135.10526315789474</v>
+        <v>136.44999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1933,11 +1935,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>9957</v>
+        <v>10580</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>524.0526315789474</v>
+        <v>529</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1949,11 +1951,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>1122</v>
+        <v>1577</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>59.05263157894737</v>
+        <v>78.849999999999994</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1965,11 +1967,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>5712</v>
+        <v>5929</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>300.63157894736844</v>
+        <v>296.45</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1981,11 +1983,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>10090</v>
+        <v>10492</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>531.0526315789474</v>
+        <v>524.6</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1997,11 +1999,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>5892</v>
+        <v>6154</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>310.10526315789474</v>
+        <v>307.7</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2013,11 +2015,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>5525</v>
+        <v>5824</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>290.78947368421052</v>
+        <v>291.2</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2029,11 +2031,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>58.736842105263158</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2043,11 +2045,11 @@
       </c>
       <c r="C49" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>2046</v>
+        <v>2091</v>
       </c>
       <c r="D49" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>107.68421052631579</v>
+        <v>104.55</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2057,11 +2059,11 @@
       </c>
       <c r="C50" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>971</v>
+        <v>984</v>
       </c>
       <c r="D50" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>51.10526315789474</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2118,19 +2120,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>501124</v>
+        <v>521390</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$H$3</f>
-        <v>505258</v>
+        <v>525524</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>26592.526315789473</v>
+        <v>26276.2</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>558443.05263157899</v>
+        <v>551800.19999999995</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2138,11 +2140,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.77212055659044443</v>
+        <v>0.80334595230061179</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-147899</v>
+        <v>-127633</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2186,7 +2188,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2194,11 +2196,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765EFE32-98AC-49FE-8331-5D6BE24F689E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC3012A-785A-4EDD-9478-51CE838D52D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -483,6 +483,7 @@
       <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 31-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL CIERRE"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -513,36 +514,37 @@
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
-      <sheetData sheetId="24">
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25">
         <row r="3">
           <cell r="G3">
-            <v>521390</v>
+            <v>570325</v>
           </cell>
           <cell r="H3">
-            <v>525524</v>
+            <v>574918</v>
           </cell>
           <cell r="I3">
-            <v>26276.2</v>
+            <v>27377.047619047618</v>
           </cell>
           <cell r="J3">
-            <v>551800.19999999995</v>
+            <v>574918</v>
           </cell>
           <cell r="K3">
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.80334595230061179</v>
+            <v>0.87874389659534413</v>
           </cell>
           <cell r="M3">
-            <v>-127633</v>
+            <v>-78698</v>
           </cell>
         </row>
         <row r="4">
           <cell r="C4">
-            <v>22945</v>
+            <v>24950</v>
           </cell>
           <cell r="D4">
-            <v>1147.25</v>
+            <v>1188.0952380952381</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -565,13 +567,13 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>1501</v>
+            <v>1604</v>
           </cell>
           <cell r="D5">
-            <v>75.05</v>
+            <v>76.38095238095238</v>
           </cell>
           <cell r="G5">
-            <v>4134</v>
+            <v>-4593</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
@@ -583,282 +585,282 @@
             <v>46265</v>
           </cell>
           <cell r="K5">
-            <v>20</v>
+            <v>21</v>
           </cell>
           <cell r="L5">
-            <v>1</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="6">
           <cell r="C6">
-            <v>9703</v>
+            <v>10699</v>
           </cell>
           <cell r="D6">
-            <v>485.15</v>
+            <v>509.47619047619048</v>
           </cell>
         </row>
         <row r="7">
           <cell r="C7">
-            <v>1765</v>
+            <v>2058</v>
           </cell>
           <cell r="D7">
-            <v>88.25</v>
+            <v>98</v>
           </cell>
         </row>
         <row r="8">
           <cell r="C8">
-            <v>244</v>
+            <v>251</v>
           </cell>
           <cell r="D8">
-            <v>12.2</v>
+            <v>11.952380952380953</v>
           </cell>
         </row>
         <row r="9">
           <cell r="C9">
-            <v>28306</v>
+            <v>30667</v>
           </cell>
           <cell r="D9">
-            <v>1415.3</v>
+            <v>1460.3333333333333</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>2797</v>
+            <v>3158</v>
           </cell>
           <cell r="D10">
-            <v>139.85</v>
+            <v>150.38095238095238</v>
           </cell>
         </row>
         <row r="11">
           <cell r="C11">
-            <v>6437</v>
+            <v>7215</v>
           </cell>
           <cell r="D11">
-            <v>321.85000000000002</v>
+            <v>343.57142857142856</v>
           </cell>
         </row>
         <row r="12">
           <cell r="C12">
-            <v>14952</v>
+            <v>16090</v>
           </cell>
           <cell r="D12">
-            <v>747.6</v>
+            <v>766.19047619047615</v>
           </cell>
         </row>
         <row r="13">
           <cell r="C13">
-            <v>7013</v>
+            <v>7619</v>
           </cell>
           <cell r="D13">
-            <v>350.65</v>
+            <v>362.8095238095238</v>
           </cell>
         </row>
         <row r="14">
           <cell r="C14">
-            <v>68059</v>
+            <v>73952</v>
           </cell>
           <cell r="D14">
-            <v>3402.95</v>
+            <v>3521.5238095238096</v>
           </cell>
         </row>
         <row r="15">
           <cell r="C15">
-            <v>44386</v>
+            <v>48405</v>
           </cell>
           <cell r="D15">
-            <v>2219.3000000000002</v>
+            <v>2305</v>
           </cell>
         </row>
         <row r="16">
           <cell r="C16">
-            <v>42963</v>
+            <v>47596</v>
           </cell>
           <cell r="D16">
-            <v>2148.15</v>
+            <v>2266.4761904761904</v>
           </cell>
         </row>
         <row r="17">
           <cell r="C17">
-            <v>51465</v>
+            <v>56154</v>
           </cell>
           <cell r="D17">
-            <v>2573.25</v>
+            <v>2674</v>
           </cell>
         </row>
         <row r="18">
           <cell r="C18">
-            <v>194</v>
+            <v>245</v>
           </cell>
           <cell r="D18">
-            <v>9.6999999999999993</v>
+            <v>11.666666666666666</v>
           </cell>
         </row>
         <row r="19">
           <cell r="C19">
-            <v>7342</v>
+            <v>8173</v>
           </cell>
           <cell r="D19">
-            <v>367.1</v>
+            <v>389.1904761904762</v>
           </cell>
         </row>
         <row r="20">
           <cell r="C20">
-            <v>8294</v>
+            <v>8996</v>
           </cell>
           <cell r="D20">
-            <v>414.7</v>
+            <v>428.38095238095241</v>
           </cell>
         </row>
         <row r="21">
           <cell r="C21">
-            <v>7683</v>
+            <v>8206</v>
           </cell>
           <cell r="D21">
-            <v>384.15</v>
+            <v>390.76190476190476</v>
           </cell>
         </row>
         <row r="22">
           <cell r="C22">
-            <v>4655</v>
+            <v>5082</v>
           </cell>
           <cell r="D22">
-            <v>232.75</v>
+            <v>242</v>
           </cell>
         </row>
         <row r="23">
           <cell r="C23">
-            <v>2711</v>
+            <v>2986</v>
           </cell>
           <cell r="D23">
-            <v>135.55000000000001</v>
+            <v>142.1904761904762</v>
           </cell>
         </row>
         <row r="24">
           <cell r="C24">
-            <v>9927</v>
+            <v>10775</v>
           </cell>
           <cell r="D24">
-            <v>496.35</v>
+            <v>513.09523809523807</v>
           </cell>
         </row>
         <row r="25">
           <cell r="C25">
-            <v>15700</v>
+            <v>17039</v>
           </cell>
           <cell r="D25">
-            <v>785</v>
+            <v>811.38095238095241</v>
           </cell>
         </row>
         <row r="26">
           <cell r="C26">
-            <v>1274</v>
+            <v>1574</v>
           </cell>
           <cell r="D26">
-            <v>63.7</v>
+            <v>74.952380952380949</v>
           </cell>
         </row>
         <row r="27">
           <cell r="C27">
-            <v>14193</v>
+            <v>16547</v>
           </cell>
           <cell r="D27">
-            <v>709.65</v>
+            <v>787.95238095238096</v>
           </cell>
         </row>
         <row r="28">
           <cell r="C28">
-            <v>23259</v>
+            <v>26748</v>
           </cell>
           <cell r="D28">
-            <v>1162.95</v>
+            <v>1273.7142857142858</v>
           </cell>
         </row>
         <row r="29">
           <cell r="C29">
-            <v>10205</v>
+            <v>11113</v>
           </cell>
           <cell r="D29">
-            <v>510.25</v>
+            <v>529.19047619047615</v>
           </cell>
         </row>
         <row r="30">
           <cell r="C30">
-            <v>8012</v>
+            <v>8439</v>
           </cell>
           <cell r="D30">
-            <v>400.6</v>
+            <v>401.85714285714283</v>
           </cell>
         </row>
         <row r="31">
           <cell r="C31">
-            <v>1418</v>
+            <v>1598</v>
           </cell>
           <cell r="D31">
-            <v>70.900000000000006</v>
+            <v>76.095238095238102</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>1350</v>
+            <v>1514</v>
           </cell>
           <cell r="D32">
-            <v>67.5</v>
+            <v>72.095238095238102</v>
           </cell>
         </row>
         <row r="33">
           <cell r="C33">
-            <v>2368</v>
+            <v>2685</v>
           </cell>
           <cell r="D33">
-            <v>118.4</v>
+            <v>127.85714285714286</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>2685</v>
+            <v>3010</v>
           </cell>
           <cell r="D34">
-            <v>134.25</v>
+            <v>143.33333333333334</v>
           </cell>
         </row>
         <row r="35">
           <cell r="C35">
-            <v>12822</v>
+            <v>13696</v>
           </cell>
           <cell r="D35">
-            <v>641.1</v>
+            <v>652.19047619047615</v>
           </cell>
         </row>
         <row r="36">
           <cell r="C36">
-            <v>12402</v>
+            <v>13210</v>
           </cell>
           <cell r="D36">
-            <v>620.1</v>
+            <v>629.04761904761904</v>
           </cell>
         </row>
         <row r="37">
           <cell r="C37">
-            <v>16577</v>
+            <v>17896</v>
           </cell>
           <cell r="D37">
-            <v>828.85</v>
+            <v>852.19047619047615</v>
           </cell>
         </row>
         <row r="38">
           <cell r="C38">
-            <v>11287</v>
+            <v>12159</v>
           </cell>
           <cell r="D38">
-            <v>564.35</v>
+            <v>579</v>
           </cell>
         </row>
         <row r="39">
           <cell r="C39">
-            <v>47</v>
+            <v>52</v>
           </cell>
           <cell r="D39">
-            <v>2.35</v>
+            <v>2.4761904761904763</v>
           </cell>
         </row>
         <row r="40">
@@ -866,91 +868,91 @@
             <v>9</v>
           </cell>
           <cell r="D40">
-            <v>0.45</v>
+            <v>0.42857142857142855</v>
           </cell>
         </row>
         <row r="41">
           <cell r="C41">
-            <v>2729</v>
+            <v>2880</v>
           </cell>
           <cell r="D41">
-            <v>136.44999999999999</v>
+            <v>137.14285714285714</v>
           </cell>
         </row>
         <row r="42">
           <cell r="C42">
-            <v>10580</v>
+            <v>11643</v>
           </cell>
           <cell r="D42">
-            <v>529</v>
+            <v>554.42857142857144</v>
           </cell>
         </row>
         <row r="43">
           <cell r="C43">
-            <v>1577</v>
+            <v>2789</v>
           </cell>
           <cell r="D43">
-            <v>78.849999999999994</v>
+            <v>132.8095238095238</v>
           </cell>
         </row>
         <row r="44">
           <cell r="C44">
-            <v>5929</v>
+            <v>6219</v>
           </cell>
           <cell r="D44">
-            <v>296.45</v>
+            <v>296.14285714285717</v>
           </cell>
         </row>
         <row r="45">
           <cell r="C45">
-            <v>10492</v>
+            <v>11103</v>
           </cell>
           <cell r="D45">
-            <v>524.6</v>
+            <v>528.71428571428567</v>
           </cell>
         </row>
         <row r="46">
           <cell r="C46">
-            <v>6154</v>
+            <v>6417</v>
           </cell>
           <cell r="D46">
-            <v>307.7</v>
+            <v>305.57142857142856</v>
           </cell>
         </row>
         <row r="47">
           <cell r="C47">
-            <v>5824</v>
+            <v>6088</v>
           </cell>
           <cell r="D47">
-            <v>291.2</v>
+            <v>289.90476190476193</v>
           </cell>
         </row>
         <row r="48">
           <cell r="C48">
-            <v>1126</v>
+            <v>1212</v>
           </cell>
           <cell r="D48">
-            <v>56.3</v>
+            <v>57.714285714285715</v>
           </cell>
         </row>
         <row r="49">
           <cell r="C49">
-            <v>2091</v>
+            <v>2199</v>
           </cell>
           <cell r="D49">
-            <v>104.55</v>
+            <v>104.71428571428571</v>
           </cell>
         </row>
         <row r="50">
           <cell r="C50">
-            <v>984</v>
+            <v>1036</v>
           </cell>
           <cell r="D50">
-            <v>49.2</v>
+            <v>49.333333333333336</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1295,11 +1297,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>22945</v>
+        <v>24950</v>
       </c>
       <c r="D2" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1147.25</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D4</f>
+        <v>1188.0952380952381</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1311,11 +1313,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>1501</v>
+        <v>1604</v>
       </c>
       <c r="D3" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>75.05</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D5</f>
+        <v>76.38095238095238</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1327,11 +1329,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>9703</v>
+        <v>10699</v>
       </c>
       <c r="D4" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>485.15</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D6</f>
+        <v>509.47619047619048</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1343,11 +1345,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>1765</v>
+        <v>2058</v>
       </c>
       <c r="D5" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>88.25</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D7</f>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1359,11 +1361,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D6" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>12.2</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D8</f>
+        <v>11.952380952380953</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1375,11 +1377,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>28306</v>
+        <v>30667</v>
       </c>
       <c r="D7" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1415.3</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D9</f>
+        <v>1460.3333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1391,11 +1393,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>2797</v>
+        <v>3158</v>
       </c>
       <c r="D8" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>139.85</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D10</f>
+        <v>150.38095238095238</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1407,11 +1409,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>6437</v>
+        <v>7215</v>
       </c>
       <c r="D9" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>321.85000000000002</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D11</f>
+        <v>343.57142857142856</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1423,11 +1425,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>14952</v>
+        <v>16090</v>
       </c>
       <c r="D10" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>747.6</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D12</f>
+        <v>766.19047619047615</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1439,11 +1441,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>7013</v>
+        <v>7619</v>
       </c>
       <c r="D11" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>350.65</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D13</f>
+        <v>362.8095238095238</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1455,11 +1457,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>68059</v>
+        <v>73952</v>
       </c>
       <c r="D12" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3402.95</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D14</f>
+        <v>3521.5238095238096</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1471,11 +1473,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>44386</v>
+        <v>48405</v>
       </c>
       <c r="D13" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2219.3000000000002</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D15</f>
+        <v>2305</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1487,11 +1489,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>42963</v>
+        <v>47596</v>
       </c>
       <c r="D14" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2148.15</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D16</f>
+        <v>2266.4761904761904</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1503,11 +1505,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>51465</v>
+        <v>56154</v>
       </c>
       <c r="D15" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2573.25</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D17</f>
+        <v>2674</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1519,11 +1521,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>194</v>
+        <v>245</v>
       </c>
       <c r="D16" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>9.6999999999999993</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D18</f>
+        <v>11.666666666666666</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1535,11 +1537,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$19</f>
-        <v>7342</v>
+        <v>8173</v>
       </c>
       <c r="D17" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>367.1</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D19</f>
+        <v>389.1904761904762</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1551,11 +1553,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$20</f>
-        <v>8294</v>
+        <v>8996</v>
       </c>
       <c r="D18" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>414.7</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D20</f>
+        <v>428.38095238095241</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1567,11 +1569,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$21</f>
-        <v>7683</v>
+        <v>8206</v>
       </c>
       <c r="D19" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>384.15</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D21</f>
+        <v>390.76190476190476</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1583,11 +1585,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>4655</v>
+        <v>5082</v>
       </c>
       <c r="D20" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>232.75</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D22</f>
+        <v>242</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1599,11 +1601,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>2711</v>
+        <v>2986</v>
       </c>
       <c r="D21" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>135.55000000000001</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D23</f>
+        <v>142.1904761904762</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1615,11 +1617,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>9927</v>
+        <v>10775</v>
       </c>
       <c r="D22" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>496.35</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D24</f>
+        <v>513.09523809523807</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1631,11 +1633,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>15700</v>
+        <v>17039</v>
       </c>
       <c r="D23" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>785</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D25</f>
+        <v>811.38095238095241</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1647,11 +1649,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>1274</v>
+        <v>1574</v>
       </c>
       <c r="D24" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>63.7</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D26</f>
+        <v>74.952380952380949</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1663,11 +1665,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>14193</v>
+        <v>16547</v>
       </c>
       <c r="D25" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>709.65</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D27</f>
+        <v>787.95238095238096</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1679,11 +1681,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>23259</v>
+        <v>26748</v>
       </c>
       <c r="D26" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>1162.95</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D28</f>
+        <v>1273.7142857142858</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1695,11 +1697,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>10205</v>
+        <v>11113</v>
       </c>
       <c r="D27" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>510.25</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D29</f>
+        <v>529.19047619047615</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1711,11 +1713,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>8012</v>
+        <v>8439</v>
       </c>
       <c r="D28" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>400.6</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D30</f>
+        <v>401.85714285714283</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1727,11 +1729,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>1418</v>
+        <v>1598</v>
       </c>
       <c r="D29" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>70.900000000000006</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D31</f>
+        <v>76.095238095238102</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1743,11 +1745,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$32</f>
-        <v>1350</v>
+        <v>1514</v>
       </c>
       <c r="D30" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$32</f>
-        <v>67.5</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!$D$32</f>
+        <v>72.095238095238102</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1759,11 +1761,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$C$33</f>
-        <v>2368</v>
+        <v>2685</v>
       </c>
       <c r="D31" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!$D$33</f>
-        <v>118.4</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!$D$33</f>
+        <v>127.85714285714286</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1775,11 +1777,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1350</v>
+        <v>1514</v>
       </c>
       <c r="D32" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>67.5</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D32</f>
+        <v>72.095238095238102</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1791,11 +1793,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>2368</v>
+        <v>2685</v>
       </c>
       <c r="D33" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>118.4</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D33</f>
+        <v>127.85714285714286</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1807,11 +1809,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>2685</v>
+        <v>3010</v>
       </c>
       <c r="D34" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>134.25</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D34</f>
+        <v>143.33333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1823,11 +1825,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>12822</v>
+        <v>13696</v>
       </c>
       <c r="D35" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>641.1</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D35</f>
+        <v>652.19047619047615</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1839,11 +1841,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>12402</v>
+        <v>13210</v>
       </c>
       <c r="D36" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>620.1</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D36</f>
+        <v>629.04761904761904</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1855,11 +1857,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>16577</v>
+        <v>17896</v>
       </c>
       <c r="D37" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>828.85</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D37</f>
+        <v>852.19047619047615</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1871,11 +1873,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>11287</v>
+        <v>12159</v>
       </c>
       <c r="D38" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>564.35</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D38</f>
+        <v>579</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1887,11 +1889,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D39" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>2.35</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D39</f>
+        <v>2.4761904761904763</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1906,8 +1908,8 @@
         <v>9</v>
       </c>
       <c r="D40" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>0.45</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D40</f>
+        <v>0.42857142857142855</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1919,11 +1921,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>2729</v>
+        <v>2880</v>
       </c>
       <c r="D41" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>136.44999999999999</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D41</f>
+        <v>137.14285714285714</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1935,11 +1937,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>10580</v>
+        <v>11643</v>
       </c>
       <c r="D42" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>529</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D42</f>
+        <v>554.42857142857144</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1951,11 +1953,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>1577</v>
+        <v>2789</v>
       </c>
       <c r="D43" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>78.849999999999994</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D43</f>
+        <v>132.8095238095238</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1967,11 +1969,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>5929</v>
+        <v>6219</v>
       </c>
       <c r="D44" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>296.45</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D44</f>
+        <v>296.14285714285717</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1983,11 +1985,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>10492</v>
+        <v>11103</v>
       </c>
       <c r="D45" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>524.6</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D45</f>
+        <v>528.71428571428567</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1999,11 +2001,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>6154</v>
+        <v>6417</v>
       </c>
       <c r="D46" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>307.7</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D46</f>
+        <v>305.57142857142856</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2015,11 +2017,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>5824</v>
+        <v>6088</v>
       </c>
       <c r="D47" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>291.2</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D47</f>
+        <v>289.90476190476193</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2031,11 +2033,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>1126</v>
+        <v>1212</v>
       </c>
       <c r="D48" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>56.3</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D48</f>
+        <v>57.714285714285715</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2045,11 +2047,11 @@
       </c>
       <c r="C49" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>2091</v>
+        <v>2199</v>
       </c>
       <c r="D49" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>104.55</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D49</f>
+        <v>104.71428571428571</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2059,11 +2061,11 @@
       </c>
       <c r="C50" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>984</v>
+        <v>1036</v>
       </c>
       <c r="D50" s="12">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>49.2</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!D50</f>
+        <v>49.333333333333336</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2120,19 +2122,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>521390</v>
+        <v>570325</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$H$3</f>
-        <v>525524</v>
+        <v>574918</v>
       </c>
       <c r="C3" s="4">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>26276.2</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!I3</f>
+        <v>27377.047619047618</v>
       </c>
       <c r="D3" s="5">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>551800.19999999995</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!J3</f>
+        <v>574918</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2140,11 +2142,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.80334595230061179</v>
+        <v>0.87874389659534413</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-127633</v>
+        <v>-78698</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2180,14 +2182,14 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>4134</v>
+        <v>-4593</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
         <v>46237</v>
       </c>
       <c r="C5" s="16">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!I5</f>
         <v>46265</v>
       </c>
       <c r="D5" s="16">
@@ -2195,12 +2197,12 @@
         <v>46265</v>
       </c>
       <c r="E5" s="19">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>20</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!K5</f>
+        <v>21</v>
       </c>
       <c r="F5" s="17">
-        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>1</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!L5</f>
+        <v>0</v>
       </c>
       <c r="G5" s="11">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC3012A-785A-4EDD-9478-51CE838D52D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53B9ED9-41E9-4B05-B852-4E9857B7CD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -518,7 +518,7 @@
       <sheetData sheetId="25">
         <row r="3">
           <cell r="G3">
-            <v>570325</v>
+            <v>579511</v>
           </cell>
           <cell r="H3">
             <v>574918</v>
@@ -533,10 +533,10 @@
             <v>649023</v>
           </cell>
           <cell r="L3">
-            <v>0.87874389659534413</v>
+            <v>0.89289747820955501</v>
           </cell>
           <cell r="M3">
-            <v>-78698</v>
+            <v>-69512</v>
           </cell>
         </row>
         <row r="4">
@@ -573,7 +573,7 @@
             <v>76.38095238095238</v>
           </cell>
           <cell r="G5">
-            <v>-4593</v>
+            <v>4593</v>
           </cell>
           <cell r="H5">
             <v>46237</v>
@@ -2122,7 +2122,7 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>570325</v>
+        <v>579511</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!$H$3</f>
@@ -2142,11 +2142,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.87874389659534413</v>
+        <v>0.89289747820955501</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-78698</v>
+        <v>-69512</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2182,7 +2182,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>-4593</v>
+        <v>4593</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53B9ED9-41E9-4B05-B852-4E9857B7CD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C8ECB0-D974-4B51-B309-F3C6A33B35F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -38,13 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
-  <si>
-    <t>FORECAST</t>
-  </si>
-  <si>
-    <t>FORECAST EFFICIENCY</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>REFERENCIA INTERNA</t>
   </si>
@@ -52,175 +46,10 @@
     <t>PRODUCTO</t>
   </si>
   <si>
-    <t>Cremosillo Tradicional 150g</t>
-  </si>
-  <si>
-    <t>Cremosillo Coco 150g</t>
-  </si>
-  <si>
-    <t>Cremosillo Tradicional 230g</t>
-  </si>
-  <si>
-    <t>Cremosillo Tradicional 400g</t>
-  </si>
-  <si>
-    <t>Cremosillo Tradicional 1000g</t>
-  </si>
-  <si>
-    <t>Gelatina Saltarina Fresa 130g</t>
-  </si>
-  <si>
-    <t>Gelatina Saltarina Chicle 130g</t>
-  </si>
-  <si>
-    <t>Gelatina Saltarina Kolita 130g</t>
-  </si>
-  <si>
-    <t>Cremigurt Natural 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Dulce 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Griego Fresa 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Griego Durazno 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Griego Piña 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Griego 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Light 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Natural 700g</t>
-  </si>
-  <si>
-    <t>Cremigurt Dulce 700g</t>
-  </si>
-  <si>
-    <t>Cremigurt Griego Fresa 700g</t>
-  </si>
-  <si>
-    <t>Cremigurt Griego 700g</t>
-  </si>
-  <si>
-    <t>Cremigurt Light 700g</t>
-  </si>
-  <si>
-    <t>Griego Mykonos 700g</t>
-  </si>
-  <si>
-    <t>Cremigurt Power Natural 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Power Mantecado 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Power CheesseCake Fresa 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Power Cookies and Cream 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Power Natural 700g</t>
-  </si>
-  <si>
-    <t>Cremigurt Power Mantecado 700g</t>
-  </si>
-  <si>
-    <t>Cremigurt Griego Fresa S/A 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Griego Coco Vainilla S/A 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Griego Pie de Limón S/A 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Griego Caramelo Salado S/A 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Líquido Dulce 230g</t>
-  </si>
-  <si>
-    <t>Cremigurt Líquido Fresa 230g</t>
-  </si>
-  <si>
-    <t>Cremigurt Líquido Durazno 230g</t>
-  </si>
-  <si>
-    <t>Tevia Limon 360ml</t>
-  </si>
-  <si>
-    <t>Tevia Durazno 360ml</t>
-  </si>
-  <si>
-    <t>Tevia Blueberry 360ml</t>
-  </si>
-  <si>
-    <t>Tevia Tropical Punch 360ml</t>
-  </si>
-  <si>
-    <t>Tevia Limon 1.5L</t>
-  </si>
-  <si>
-    <t>Tevia Durazno 1.5 L</t>
-  </si>
-  <si>
-    <t>Tevia Blueberry 1.5 L</t>
-  </si>
-  <si>
-    <t>Tevia Tropical Punch 1.5 L</t>
-  </si>
-  <si>
-    <t>Cremigurt Griego Dulce 4 Kg</t>
-  </si>
-  <si>
-    <t>Cremigurt Griego Natural 4 Kg</t>
-  </si>
-  <si>
     <t>PROMEDIO DE VENTA DIARIA</t>
   </si>
   <si>
     <t>VENTA BRUTA</t>
-  </si>
-  <si>
-    <t>DASHBOARD</t>
-  </si>
-  <si>
-    <t>TOTAL UNITS SALES GROSS</t>
-  </si>
-  <si>
-    <t>TOTAL UNITS SALES NET</t>
-  </si>
-  <si>
-    <t>PROMD VTA DIA</t>
-  </si>
-  <si>
-    <t>PROMD VTA MES</t>
-  </si>
-  <si>
-    <t>DIF UNITS</t>
-  </si>
-  <si>
-    <t>Cremigurt Mango 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Ciruela 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Mora 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Power Piña Colada 150g</t>
-  </si>
-  <si>
-    <t>Cremigurt Power Dulce de leche 150g</t>
   </si>
 </sst>
 </file>
@@ -461,31 +290,11 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="INVENTARIO NACIONAL 04-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 05-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 06-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 07-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 10-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 11-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 12-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 13-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 18-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 19-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 19-08-26-2"/>
-      <sheetName val="INVENTARIO NACIONAL 20-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 20-08-26-2"/>
-      <sheetName val="INVENTARIO NACIONAL 21-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
-      <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 28-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 31-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL CIERRE"/>
+      <sheetName val="INVENTARIO NACIONAL INICIO"/>
+      <sheetName val="INVENTARIO NACIONAL 02-09-2026"/>
+      <sheetName val="INVENTARIO NACIONAL 03-09-26"/>
       <sheetName val="CCC"/>
-      <sheetName val="VINCULO VTS BY SKU JULIO"/>
+      <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
     </sheetNames>
@@ -495,56 +304,70 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25">
+      <sheetData sheetId="5">
+        <row r="1">
+          <cell r="G1" t="str">
+            <v>DASHBOARD</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="G2" t="str">
+            <v>TOTAL UNITS SALES GROSS</v>
+          </cell>
+          <cell r="H2" t="str">
+            <v>TOTAL UNITS SALES NET</v>
+          </cell>
+          <cell r="I2" t="str">
+            <v>PROMD VTA DIA</v>
+          </cell>
+          <cell r="J2" t="str">
+            <v>PROMD VTA MES</v>
+          </cell>
+          <cell r="K2" t="str">
+            <v>FORECAST</v>
+          </cell>
+          <cell r="L2" t="str">
+            <v>FORECAST EFFICIENCY</v>
+          </cell>
+          <cell r="M2" t="str">
+            <v>DIF UNITS</v>
+          </cell>
+        </row>
         <row r="3">
           <cell r="G3">
-            <v>579511</v>
+            <v>34173</v>
           </cell>
           <cell r="H3">
-            <v>574918</v>
+            <v>34173</v>
           </cell>
           <cell r="I3">
-            <v>27377.047619047618</v>
+            <v>17086.5</v>
           </cell>
           <cell r="J3">
-            <v>574918</v>
+            <v>375903</v>
           </cell>
           <cell r="K3">
-            <v>649023</v>
+            <v>632000</v>
           </cell>
           <cell r="L3">
-            <v>0.89289747820955501</v>
+            <v>5.4071202531645567E-2</v>
           </cell>
           <cell r="M3">
-            <v>-69512</v>
+            <v>-597827</v>
           </cell>
         </row>
         <row r="4">
+          <cell r="A4">
+            <v>110150</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>Cremosillo Tradicional 150g</v>
+          </cell>
           <cell r="C4">
-            <v>24950</v>
+            <v>1501</v>
           </cell>
           <cell r="D4">
-            <v>1188.0952380952381</v>
+            <v>750.5</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -566,393 +389,669 @@
           </cell>
         </row>
         <row r="5">
+          <cell r="A5">
+            <v>110151</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>Cremosillo Coco 150g</v>
+          </cell>
           <cell r="C5">
-            <v>1604</v>
+            <v>135</v>
           </cell>
           <cell r="D5">
-            <v>76.38095238095238</v>
+            <v>67.5</v>
           </cell>
           <cell r="G5">
-            <v>4593</v>
+            <v>0</v>
           </cell>
           <cell r="H5">
-            <v>46237</v>
+            <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46265</v>
+            <v>46268</v>
           </cell>
           <cell r="J5">
-            <v>46265</v>
+            <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>21</v>
+            <v>2</v>
           </cell>
           <cell r="L5">
-            <v>0</v>
+            <v>20</v>
           </cell>
         </row>
         <row r="6">
+          <cell r="A6">
+            <v>110230</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>Cremosillo Tradicional 230g</v>
+          </cell>
           <cell r="C6">
-            <v>10699</v>
+            <v>473</v>
           </cell>
           <cell r="D6">
-            <v>509.47619047619048</v>
+            <v>236.5</v>
           </cell>
         </row>
         <row r="7">
+          <cell r="A7">
+            <v>110400</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>Cremosillo Tradicional 400g</v>
+          </cell>
           <cell r="C7">
-            <v>2058</v>
+            <v>171</v>
           </cell>
           <cell r="D7">
-            <v>98</v>
+            <v>85.5</v>
           </cell>
         </row>
         <row r="8">
+          <cell r="A8">
+            <v>111000</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>Cremosillo Tradicional 1000g</v>
+          </cell>
           <cell r="C8">
-            <v>251</v>
+            <v>11</v>
           </cell>
           <cell r="D8">
-            <v>11.952380952380953</v>
+            <v>5.5</v>
           </cell>
         </row>
         <row r="9">
+          <cell r="A9">
+            <v>120130</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>Gelatina Saltarina Fresa 130g</v>
+          </cell>
           <cell r="C9">
-            <v>30667</v>
+            <v>1570</v>
           </cell>
           <cell r="D9">
-            <v>1460.3333333333333</v>
+            <v>785</v>
           </cell>
         </row>
         <row r="10">
+          <cell r="A10">
+            <v>120131</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>Gelatina Saltarina Chicle 130g</v>
+          </cell>
           <cell r="C10">
-            <v>3158</v>
+            <v>181</v>
           </cell>
           <cell r="D10">
-            <v>150.38095238095238</v>
+            <v>90.5</v>
           </cell>
         </row>
         <row r="11">
+          <cell r="A11">
+            <v>120132</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>Gelatina Saltarina Kolita 130g</v>
+          </cell>
           <cell r="C11">
-            <v>7215</v>
+            <v>362</v>
           </cell>
           <cell r="D11">
-            <v>343.57142857142856</v>
+            <v>181</v>
           </cell>
         </row>
         <row r="12">
+          <cell r="A12">
+            <v>130150</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>Cremigurt Natural 150g</v>
+          </cell>
           <cell r="C12">
-            <v>16090</v>
+            <v>1139</v>
           </cell>
           <cell r="D12">
-            <v>766.19047619047615</v>
+            <v>569.5</v>
           </cell>
         </row>
         <row r="13">
+          <cell r="A13">
+            <v>130151</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>Cremigurt Dulce 150g</v>
+          </cell>
           <cell r="C13">
-            <v>7619</v>
+            <v>456</v>
           </cell>
           <cell r="D13">
-            <v>362.8095238095238</v>
+            <v>228</v>
           </cell>
         </row>
         <row r="14">
+          <cell r="A14">
+            <v>130152</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v>Cremigurt Fresa 150g</v>
+          </cell>
           <cell r="C14">
-            <v>73952</v>
+            <v>4082</v>
           </cell>
           <cell r="D14">
-            <v>3521.5238095238096</v>
+            <v>2041</v>
           </cell>
         </row>
         <row r="15">
+          <cell r="A15">
+            <v>130153</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v>Cremigurt Durazno 150g</v>
+          </cell>
           <cell r="C15">
-            <v>48405</v>
+            <v>2584</v>
           </cell>
           <cell r="D15">
-            <v>2305</v>
+            <v>1292</v>
           </cell>
         </row>
         <row r="16">
+          <cell r="A16">
+            <v>130154</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v>Cremigurt Piña 150g</v>
+          </cell>
           <cell r="C16">
-            <v>47596</v>
+            <v>2632</v>
           </cell>
           <cell r="D16">
-            <v>2266.4761904761904</v>
+            <v>1316</v>
           </cell>
         </row>
         <row r="17">
+          <cell r="A17">
+            <v>130155</v>
+          </cell>
+          <cell r="B17" t="str">
+            <v>Cremigurt Griego 150g</v>
+          </cell>
           <cell r="C17">
-            <v>56154</v>
+            <v>3184</v>
           </cell>
           <cell r="D17">
-            <v>2674</v>
+            <v>1592</v>
           </cell>
         </row>
         <row r="18">
+          <cell r="A18">
+            <v>130157</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v>Cremigurt Griego Mango 150g</v>
+          </cell>
           <cell r="C18">
-            <v>245</v>
+            <v>1056</v>
           </cell>
           <cell r="D18">
-            <v>11.666666666666666</v>
+            <v>528</v>
           </cell>
         </row>
         <row r="19">
+          <cell r="A19">
+            <v>130158</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v>Cremigurt Griego Ciruela 150g</v>
+          </cell>
           <cell r="C19">
-            <v>8173</v>
+            <v>1366</v>
           </cell>
           <cell r="D19">
-            <v>389.1904761904762</v>
+            <v>683</v>
           </cell>
         </row>
         <row r="20">
+          <cell r="A20">
+            <v>130159</v>
+          </cell>
+          <cell r="B20" t="str">
+            <v>Cremigurt Griego Mora 150g</v>
+          </cell>
           <cell r="C20">
-            <v>8996</v>
+            <v>1391</v>
           </cell>
           <cell r="D20">
-            <v>428.38095238095241</v>
+            <v>695.5</v>
           </cell>
         </row>
         <row r="21">
+          <cell r="A21">
+            <v>130700</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v>Cremigurt Natural 700g</v>
+          </cell>
           <cell r="C21">
-            <v>8206</v>
+            <v>379</v>
           </cell>
           <cell r="D21">
-            <v>390.76190476190476</v>
+            <v>189.5</v>
           </cell>
         </row>
         <row r="22">
+          <cell r="A22">
+            <v>130701</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v>Cremigurt Dulce 700g</v>
+          </cell>
           <cell r="C22">
-            <v>5082</v>
+            <v>199</v>
           </cell>
           <cell r="D22">
-            <v>242</v>
+            <v>99.5</v>
           </cell>
         </row>
         <row r="23">
+          <cell r="A23">
+            <v>130702</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v>Cremigurt Griego Fresa 700g</v>
+          </cell>
           <cell r="C23">
-            <v>2986</v>
+            <v>760</v>
           </cell>
           <cell r="D23">
-            <v>142.1904761904762</v>
+            <v>380</v>
           </cell>
         </row>
         <row r="24">
+          <cell r="A24">
+            <v>130703</v>
+          </cell>
+          <cell r="B24" t="str">
+            <v>Cremigurt Griego 700g</v>
+          </cell>
           <cell r="C24">
-            <v>10775</v>
+            <v>1256</v>
           </cell>
           <cell r="D24">
-            <v>513.09523809523807</v>
+            <v>628</v>
           </cell>
         </row>
         <row r="25">
+          <cell r="A25">
+            <v>130707</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v>Griego Mykonos 700g</v>
+          </cell>
           <cell r="C25">
-            <v>17039</v>
+            <v>20</v>
           </cell>
           <cell r="D25">
-            <v>811.38095238095241</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="26">
+          <cell r="A26">
+            <v>131150</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v>Cremigurt Power Natural 150g</v>
+          </cell>
           <cell r="C26">
-            <v>1574</v>
+            <v>687</v>
           </cell>
           <cell r="D26">
-            <v>74.952380952380949</v>
+            <v>343.5</v>
           </cell>
         </row>
         <row r="27">
+          <cell r="A27">
+            <v>131151</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v>Cremigurt Power Mantecado 150g</v>
+          </cell>
           <cell r="C27">
-            <v>16547</v>
+            <v>618</v>
           </cell>
           <cell r="D27">
-            <v>787.95238095238096</v>
+            <v>309</v>
           </cell>
         </row>
         <row r="28">
+          <cell r="A28">
+            <v>131152</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>Cremigurt Power CheesseCake Fresa 150g</v>
+          </cell>
           <cell r="C28">
-            <v>26748</v>
+            <v>777</v>
           </cell>
           <cell r="D28">
-            <v>1273.7142857142858</v>
+            <v>388.5</v>
           </cell>
         </row>
         <row r="29">
+          <cell r="A29">
+            <v>131153</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v>Cremigurt Power Cookies and Cream 150g</v>
+          </cell>
           <cell r="C29">
-            <v>11113</v>
+            <v>473</v>
           </cell>
           <cell r="D29">
-            <v>529.19047619047615</v>
+            <v>236.5</v>
           </cell>
         </row>
         <row r="30">
+          <cell r="A30">
+            <v>131154</v>
+          </cell>
+          <cell r="B30" t="str">
+            <v>Cremigurt Power Piña Colada 150g</v>
+          </cell>
           <cell r="C30">
-            <v>8439</v>
+            <v>82</v>
           </cell>
           <cell r="D30">
-            <v>401.85714285714283</v>
+            <v>41</v>
           </cell>
         </row>
         <row r="31">
+          <cell r="A31">
+            <v>131155</v>
+          </cell>
+          <cell r="B31" t="str">
+            <v>Cremigurt Power Dulce de Leche 150g</v>
+          </cell>
           <cell r="C31">
-            <v>1598</v>
+            <v>140</v>
           </cell>
           <cell r="D31">
-            <v>76.095238095238102</v>
+            <v>70</v>
           </cell>
         </row>
         <row r="32">
+          <cell r="A32">
+            <v>131700</v>
+          </cell>
+          <cell r="B32" t="str">
+            <v>Cremigurt Power Natural 700g</v>
+          </cell>
           <cell r="C32">
-            <v>1514</v>
+            <v>198</v>
           </cell>
           <cell r="D32">
-            <v>72.095238095238102</v>
+            <v>99</v>
           </cell>
         </row>
         <row r="33">
+          <cell r="A33">
+            <v>131701</v>
+          </cell>
+          <cell r="B33" t="str">
+            <v>Cremigurt Power Mantecado 700g</v>
+          </cell>
           <cell r="C33">
-            <v>2685</v>
+            <v>133</v>
           </cell>
           <cell r="D33">
-            <v>127.85714285714286</v>
+            <v>66.5</v>
           </cell>
         </row>
         <row r="34">
+          <cell r="A34">
+            <v>132150</v>
+          </cell>
+          <cell r="B34" t="str">
+            <v>Cremigurt Griego Fresa S/A 150g</v>
+          </cell>
           <cell r="C34">
-            <v>3010</v>
+            <v>797</v>
           </cell>
           <cell r="D34">
-            <v>143.33333333333334</v>
+            <v>398.5</v>
           </cell>
         </row>
         <row r="35">
+          <cell r="A35">
+            <v>132151</v>
+          </cell>
+          <cell r="B35" t="str">
+            <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
+          </cell>
           <cell r="C35">
-            <v>13696</v>
+            <v>654</v>
           </cell>
           <cell r="D35">
-            <v>652.19047619047615</v>
+            <v>327</v>
           </cell>
         </row>
         <row r="36">
+          <cell r="A36">
+            <v>132152</v>
+          </cell>
+          <cell r="B36" t="str">
+            <v>Cremigurt Griego Pie de Limón S/A 150g</v>
+          </cell>
           <cell r="C36">
-            <v>13210</v>
+            <v>1045</v>
           </cell>
           <cell r="D36">
-            <v>629.04761904761904</v>
+            <v>522.5</v>
           </cell>
         </row>
         <row r="37">
+          <cell r="A37">
+            <v>132153</v>
+          </cell>
+          <cell r="B37" t="str">
+            <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
+          </cell>
           <cell r="C37">
-            <v>17896</v>
+            <v>619</v>
           </cell>
           <cell r="D37">
-            <v>852.19047619047615</v>
+            <v>309.5</v>
           </cell>
         </row>
         <row r="38">
+          <cell r="A38">
+            <v>134000</v>
+          </cell>
+          <cell r="B38" t="str">
+            <v>Cremigurt Griego Natural 4 Kg</v>
+          </cell>
           <cell r="C38">
-            <v>12159</v>
+            <v>9</v>
           </cell>
           <cell r="D38">
-            <v>579</v>
+            <v>4.5</v>
           </cell>
         </row>
         <row r="39">
+          <cell r="A39">
+            <v>134001</v>
+          </cell>
+          <cell r="B39" t="str">
+            <v>Cremigurt Griego Dulce 4 Kg</v>
+          </cell>
           <cell r="C39">
-            <v>52</v>
+            <v>4</v>
           </cell>
           <cell r="D39">
-            <v>2.4761904761904763</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="40">
+          <cell r="A40">
+            <v>140230</v>
+          </cell>
+          <cell r="B40" t="str">
+            <v>Cremigurt Líquido Dulce 230g</v>
+          </cell>
           <cell r="C40">
-            <v>9</v>
+            <v>238</v>
           </cell>
           <cell r="D40">
-            <v>0.42857142857142855</v>
+            <v>119</v>
           </cell>
         </row>
         <row r="41">
+          <cell r="A41">
+            <v>140231</v>
+          </cell>
+          <cell r="B41" t="str">
+            <v>Cremigurt Líquido Fresa 230g</v>
+          </cell>
           <cell r="C41">
-            <v>2880</v>
+            <v>518</v>
           </cell>
           <cell r="D41">
-            <v>137.14285714285714</v>
+            <v>259</v>
           </cell>
         </row>
         <row r="42">
+          <cell r="A42">
+            <v>140232</v>
+          </cell>
+          <cell r="B42" t="str">
+            <v>Cremigurt Líquido Durazno 230g</v>
+          </cell>
           <cell r="C42">
-            <v>11643</v>
+            <v>815</v>
           </cell>
           <cell r="D42">
-            <v>554.42857142857144</v>
+            <v>407.5</v>
           </cell>
         </row>
         <row r="43">
+          <cell r="A43">
+            <v>150360</v>
+          </cell>
+          <cell r="B43" t="str">
+            <v>Tevia Limon 360ml</v>
+          </cell>
           <cell r="C43">
-            <v>2789</v>
+            <v>235</v>
           </cell>
           <cell r="D43">
-            <v>132.8095238095238</v>
+            <v>117.5</v>
           </cell>
         </row>
         <row r="44">
+          <cell r="A44">
+            <v>150361</v>
+          </cell>
+          <cell r="B44" t="str">
+            <v>Tevia Durazno 360ml</v>
+          </cell>
           <cell r="C44">
-            <v>6219</v>
+            <v>460</v>
           </cell>
           <cell r="D44">
-            <v>296.14285714285717</v>
+            <v>230</v>
           </cell>
         </row>
         <row r="45">
+          <cell r="A45">
+            <v>150362</v>
+          </cell>
+          <cell r="B45" t="str">
+            <v>Tevia Blueberry 360ml</v>
+          </cell>
           <cell r="C45">
-            <v>11103</v>
+            <v>238</v>
           </cell>
           <cell r="D45">
-            <v>528.71428571428567</v>
+            <v>119</v>
           </cell>
         </row>
         <row r="46">
+          <cell r="A46">
+            <v>150363</v>
+          </cell>
+          <cell r="B46" t="str">
+            <v>Tevia Tropical Punch 360ml</v>
+          </cell>
           <cell r="C46">
-            <v>6417</v>
+            <v>289</v>
           </cell>
           <cell r="D46">
-            <v>305.57142857142856</v>
+            <v>144.5</v>
           </cell>
         </row>
         <row r="47">
+          <cell r="A47">
+            <v>151500</v>
+          </cell>
+          <cell r="B47" t="str">
+            <v>Tevia Limon 1.5L</v>
+          </cell>
           <cell r="C47">
-            <v>6088</v>
+            <v>70</v>
           </cell>
           <cell r="D47">
-            <v>289.90476190476193</v>
+            <v>35</v>
           </cell>
         </row>
         <row r="48">
+          <cell r="A48">
+            <v>151501</v>
+          </cell>
+          <cell r="B48" t="str">
+            <v>Tevia Durazno 1.5 L</v>
+          </cell>
           <cell r="C48">
-            <v>1212</v>
+            <v>103</v>
           </cell>
           <cell r="D48">
-            <v>57.714285714285715</v>
+            <v>51.5</v>
           </cell>
         </row>
         <row r="49">
+          <cell r="A49">
+            <v>151502</v>
+          </cell>
+          <cell r="B49" t="str">
+            <v>Tevia Blueberry 1.5 L</v>
+          </cell>
           <cell r="C49">
-            <v>2199</v>
+            <v>28</v>
           </cell>
           <cell r="D49">
-            <v>104.71428571428571</v>
+            <v>14</v>
           </cell>
         </row>
         <row r="50">
+          <cell r="A50">
+            <v>151503</v>
+          </cell>
+          <cell r="B50" t="str">
+            <v>Tevia Tropical Punch 1.5 L</v>
+          </cell>
           <cell r="C50">
-            <v>1036</v>
+            <v>35</v>
           </cell>
           <cell r="D50">
-            <v>49.333333333333336</v>
+            <v>17.5</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="26"/>
+      <sheetData sheetId="6"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1255,7 +1354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55CD20E1-8530-482E-BAF2-454F195C9DA1}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="10"/>
@@ -1276,800 +1375,866 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A4</f>
         <v>110150</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>4</v>
+      <c r="B2" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B4</f>
+        <v>Cremosillo Tradicional 150g</v>
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>24950</v>
+        <v>1501</v>
       </c>
       <c r="D2" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1188.0952380952381</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
+        <v>750.5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A5</f>
         <v>110151</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>5</v>
+      <c r="B3" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B5</f>
+        <v>Cremosillo Coco 150g</v>
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>1604</v>
+        <v>135</v>
       </c>
       <c r="D3" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>76.38095238095238</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
+        <v>67.5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A6</f>
         <v>110230</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>6</v>
+      <c r="B4" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B6</f>
+        <v>Cremosillo Tradicional 230g</v>
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>10699</v>
+        <v>473</v>
       </c>
       <c r="D4" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>509.47619047619048</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
+        <v>236.5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A7</f>
         <v>110400</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>7</v>
+      <c r="B5" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B7</f>
+        <v>Cremosillo Tradicional 400g</v>
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>2058</v>
+        <v>171</v>
       </c>
       <c r="D5" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>98</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
+        <v>85.5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A8</f>
         <v>111000</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>8</v>
+      <c r="B6" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B8</f>
+        <v>Cremosillo Tradicional 1000g</v>
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>251</v>
+        <v>11</v>
       </c>
       <c r="D6" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>11.952380952380953</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A9</f>
         <v>120130</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>9</v>
+      <c r="B7" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B9</f>
+        <v>Gelatina Saltarina Fresa 130g</v>
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>30667</v>
+        <v>1570</v>
       </c>
       <c r="D7" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1460.3333333333333</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
+        <v>785</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A10</f>
         <v>120131</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>10</v>
+      <c r="B8" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B10</f>
+        <v>Gelatina Saltarina Chicle 130g</v>
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>3158</v>
+        <v>181</v>
       </c>
       <c r="D8" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>150.38095238095238</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
+        <v>90.5</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A11</f>
         <v>120132</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>11</v>
+      <c r="B9" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B11</f>
+        <v>Gelatina Saltarina Kolita 130g</v>
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>7215</v>
+        <v>362</v>
       </c>
       <c r="D9" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>343.57142857142856</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A12</f>
         <v>130150</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>12</v>
+      <c r="B10" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B12</f>
+        <v>Cremigurt Natural 150g</v>
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>16090</v>
+        <v>1139</v>
       </c>
       <c r="D10" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>766.19047619047615</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
+        <v>569.5</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A13</f>
         <v>130151</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>13</v>
+      <c r="B11" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B13</f>
+        <v>Cremigurt Dulce 150g</v>
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>7619</v>
+        <v>456</v>
       </c>
       <c r="D11" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>362.8095238095238</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A14</f>
         <v>130152</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>14</v>
+      <c r="B12" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B14</f>
+        <v>Cremigurt Fresa 150g</v>
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>73952</v>
+        <v>4082</v>
       </c>
       <c r="D12" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3521.5238095238096</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
+        <v>2041</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A15</f>
         <v>130153</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>15</v>
+      <c r="B13" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B15</f>
+        <v>Cremigurt Durazno 150g</v>
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>48405</v>
+        <v>2584</v>
       </c>
       <c r="D13" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>2305</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
+        <v>1292</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A16</f>
         <v>130154</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>16</v>
+      <c r="B14" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B16</f>
+        <v>Cremigurt Piña 150g</v>
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>47596</v>
+        <v>2632</v>
       </c>
       <c r="D14" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2266.4761904761904</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
+        <v>1316</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A17</f>
         <v>130155</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>17</v>
+      <c r="B15" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B17</f>
+        <v>Cremigurt Griego 150g</v>
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>56154</v>
+        <v>3184</v>
       </c>
       <c r="D15" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2674</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
+        <v>1592</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
-        <v>130156</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>18</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A18</f>
+        <v>130157</v>
+      </c>
+      <c r="B16" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B18</f>
+        <v>Cremigurt Griego Mango 150g</v>
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>245</v>
+        <v>1056</v>
       </c>
       <c r="D16" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>11.666666666666666</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
+        <v>528</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
-        <v>130157</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>56</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A19</f>
+        <v>130158</v>
+      </c>
+      <c r="B17" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B19</f>
+        <v>Cremigurt Griego Ciruela 150g</v>
       </c>
       <c r="C17" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!$C$19</f>
-        <v>8173</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
+        <v>1366</v>
       </c>
       <c r="D17" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>389.1904761904762</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
+        <v>683</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="15">
-        <v>130158</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>57</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A20</f>
+        <v>130159</v>
+      </c>
+      <c r="B18" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B20</f>
+        <v>Cremigurt Griego Mora 150g</v>
       </c>
       <c r="C18" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!$C$20</f>
-        <v>8996</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
+        <v>1391</v>
       </c>
       <c r="D18" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>428.38095238095241</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
+        <v>695.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
-        <v>130159</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>58</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A21</f>
+        <v>130700</v>
+      </c>
+      <c r="B19" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B21</f>
+        <v>Cremigurt Natural 700g</v>
       </c>
       <c r="C19" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!$C$21</f>
-        <v>8206</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
+        <v>379</v>
       </c>
       <c r="D19" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>390.76190476190476</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
+        <v>189.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="15">
-        <v>130700</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>19</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A22</f>
+        <v>130701</v>
+      </c>
+      <c r="B20" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B22</f>
+        <v>Cremigurt Dulce 700g</v>
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>5082</v>
+        <v>199</v>
       </c>
       <c r="D20" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>242</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
+        <v>99.5</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="15">
-        <v>130701</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>20</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A23</f>
+        <v>130702</v>
+      </c>
+      <c r="B21" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B23</f>
+        <v>Cremigurt Griego Fresa 700g</v>
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>2986</v>
+        <v>760</v>
       </c>
       <c r="D21" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>142.1904761904762</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
+        <v>380</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="15">
-        <v>130702</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>21</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A24</f>
+        <v>130703</v>
+      </c>
+      <c r="B22" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B24</f>
+        <v>Cremigurt Griego 700g</v>
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>10775</v>
+        <v>1256</v>
       </c>
       <c r="D22" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>513.09523809523807</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
+        <v>628</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="15">
-        <v>130703</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>22</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A25</f>
+        <v>130707</v>
+      </c>
+      <c r="B23" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B25</f>
+        <v>Griego Mykonos 700g</v>
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>17039</v>
+        <v>20</v>
       </c>
       <c r="D23" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>811.38095238095241</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
-        <v>130704</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>23</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A26</f>
+        <v>131150</v>
+      </c>
+      <c r="B24" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B26</f>
+        <v>Cremigurt Power Natural 150g</v>
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>1574</v>
+        <v>687</v>
       </c>
       <c r="D24" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>74.952380952380949</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
+        <v>343.5</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="15">
-        <v>130707</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>24</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A27</f>
+        <v>131151</v>
+      </c>
+      <c r="B25" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B27</f>
+        <v>Cremigurt Power Mantecado 150g</v>
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>16547</v>
+        <v>618</v>
       </c>
       <c r="D25" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>787.95238095238096</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="15">
-        <v>131150</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>25</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A28</f>
+        <v>131152</v>
+      </c>
+      <c r="B26" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B28</f>
+        <v>Cremigurt Power CheesseCake Fresa 150g</v>
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>26748</v>
+        <v>777</v>
       </c>
       <c r="D26" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>1273.7142857142858</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
+        <v>388.5</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="15">
-        <v>131151</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>26</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A29</f>
+        <v>131153</v>
+      </c>
+      <c r="B27" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B29</f>
+        <v>Cremigurt Power Cookies and Cream 150g</v>
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>11113</v>
+        <v>473</v>
       </c>
       <c r="D27" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>529.19047619047615</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
+        <v>236.5</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="15">
-        <v>131152</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>27</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A30</f>
+        <v>131154</v>
+      </c>
+      <c r="B28" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B30</f>
+        <v>Cremigurt Power Piña Colada 150g</v>
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>8439</v>
+        <v>82</v>
       </c>
       <c r="D28" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>401.85714285714283</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="15">
-        <v>131153</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>28</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A31</f>
+        <v>131155</v>
+      </c>
+      <c r="B29" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B31</f>
+        <v>Cremigurt Power Dulce de Leche 150g</v>
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>1598</v>
+        <v>140</v>
       </c>
       <c r="D29" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>76.095238095238102</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="15">
-        <v>131154</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>59</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A32</f>
+        <v>131700</v>
+      </c>
+      <c r="B30" s="20" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B32</f>
+        <v>Cremigurt Power Natural 700g</v>
       </c>
       <c r="C30" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!$C$32</f>
-        <v>1514</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
+        <v>198</v>
       </c>
       <c r="D30" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!$D$32</f>
-        <v>72.095238095238102</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="15">
-        <v>131155</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>60</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A33</f>
+        <v>131701</v>
+      </c>
+      <c r="B31" s="20" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B33</f>
+        <v>Cremigurt Power Mantecado 700g</v>
       </c>
       <c r="C31" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!$C$33</f>
-        <v>2685</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
+        <v>133</v>
       </c>
       <c r="D31" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!$D$33</f>
-        <v>127.85714285714286</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
+        <v>66.5</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="15">
-        <v>131700</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>29</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A34</f>
+        <v>132150</v>
+      </c>
+      <c r="B32" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B34</f>
+        <v>Cremigurt Griego Fresa S/A 150g</v>
       </c>
       <c r="C32" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>1514</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
+        <v>797</v>
       </c>
       <c r="D32" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>72.095238095238102</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
+        <v>398.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="15">
-        <v>131701</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>30</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A35</f>
+        <v>132151</v>
+      </c>
+      <c r="B33" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B35</f>
+        <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
       </c>
       <c r="C33" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>2685</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
+        <v>654</v>
       </c>
       <c r="D33" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>127.85714285714286</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
+        <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="15">
-        <v>132150</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>31</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A36</f>
+        <v>132152</v>
+      </c>
+      <c r="B34" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B36</f>
+        <v>Cremigurt Griego Pie de Limón S/A 150g</v>
       </c>
       <c r="C34" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>3010</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
+        <v>1045</v>
       </c>
       <c r="D34" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>143.33333333333334</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
+        <v>522.5</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="15">
-        <v>132151</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>32</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A37</f>
+        <v>132153</v>
+      </c>
+      <c r="B35" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B37</f>
+        <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
       </c>
       <c r="C35" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>13696</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
+        <v>619</v>
       </c>
       <c r="D35" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>652.19047619047615</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
+        <v>309.5</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="15">
-        <v>132152</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>33</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A38</f>
+        <v>134000</v>
+      </c>
+      <c r="B36" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B38</f>
+        <v>Cremigurt Griego Natural 4 Kg</v>
       </c>
       <c r="C36" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>13210</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
+        <v>9</v>
       </c>
       <c r="D36" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>629.04761904761904</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
+        <v>4.5</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="15">
-        <v>132153</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>34</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A39</f>
+        <v>134001</v>
+      </c>
+      <c r="B37" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B39</f>
+        <v>Cremigurt Griego Dulce 4 Kg</v>
       </c>
       <c r="C37" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>17896</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
+        <v>4</v>
       </c>
       <c r="D37" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>852.19047619047615</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A40</f>
         <v>140230</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>35</v>
+      <c r="B38" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B40</f>
+        <v>Cremigurt Líquido Dulce 230g</v>
       </c>
       <c r="C38" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>12159</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
+        <v>238</v>
       </c>
       <c r="D38" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>579</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A41</f>
         <v>140231</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>36</v>
+      <c r="B39" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B41</f>
+        <v>Cremigurt Líquido Fresa 230g</v>
       </c>
       <c r="C39" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>52</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
+        <v>518</v>
       </c>
       <c r="D39" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>2.4761904761904763</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
+        <v>259</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A42</f>
         <v>140232</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>37</v>
+      <c r="B40" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B42</f>
+        <v>Cremigurt Líquido Durazno 230g</v>
       </c>
       <c r="C40" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>9</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
+        <v>815</v>
       </c>
       <c r="D40" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>0.42857142857142855</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
+        <v>407.5</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A43</f>
         <v>150360</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>38</v>
+      <c r="B41" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B43</f>
+        <v>Tevia Limon 360ml</v>
       </c>
       <c r="C41" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>2880</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
+        <v>235</v>
       </c>
       <c r="D41" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>137.14285714285714</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
+        <v>117.5</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A44</f>
         <v>150361</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>39</v>
+      <c r="B42" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B44</f>
+        <v>Tevia Durazno 360ml</v>
       </c>
       <c r="C42" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>11643</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
+        <v>460</v>
       </c>
       <c r="D42" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>554.42857142857144</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
+        <v>230</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A45</f>
         <v>150362</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>40</v>
+      <c r="B43" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B45</f>
+        <v>Tevia Blueberry 360ml</v>
       </c>
       <c r="C43" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>2789</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
+        <v>238</v>
       </c>
       <c r="D43" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>132.8095238095238</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A46</f>
         <v>150363</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>41</v>
+      <c r="B44" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B46</f>
+        <v>Tevia Tropical Punch 360ml</v>
       </c>
       <c r="C44" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>6219</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
+        <v>289</v>
       </c>
       <c r="D44" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>296.14285714285717</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
+        <v>144.5</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A47</f>
         <v>151500</v>
       </c>
-      <c r="B45" s="8" t="s">
-        <v>42</v>
+      <c r="B45" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B47</f>
+        <v>Tevia Limon 1.5L</v>
       </c>
       <c r="C45" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>11103</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
+        <v>70</v>
       </c>
       <c r="D45" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>528.71428571428567</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A48</f>
         <v>151501</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>43</v>
+      <c r="B46" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B48</f>
+        <v>Tevia Durazno 1.5 L</v>
       </c>
       <c r="C46" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>6417</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
+        <v>103</v>
       </c>
       <c r="D46" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>305.57142857142856</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
+        <v>51.5</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A49</f>
         <v>151502</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>44</v>
+      <c r="B47" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B49</f>
+        <v>Tevia Blueberry 1.5 L</v>
       </c>
       <c r="C47" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>6088</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
+        <v>28</v>
       </c>
       <c r="D47" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>289.90476190476193</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="15">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!A50</f>
         <v>151503</v>
       </c>
-      <c r="B48" s="8" t="s">
-        <v>45</v>
+      <c r="B48" s="8" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!B50</f>
+        <v>Tevia Tropical Punch 1.5 L</v>
       </c>
       <c r="C48" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>1212</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
+        <v>35</v>
       </c>
       <c r="D48" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>57.714285714285715</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
-      <c r="B49" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C49" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>2199</v>
-      </c>
-      <c r="D49" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>104.71428571428571</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="15"/>
-      <c r="B50" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C50" s="13">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>1036</v>
-      </c>
-      <c r="D50" s="12">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>49.333333333333336</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="11"/>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C49" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2086,8 +2251,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>50</v>
+      <c r="A1" s="21" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!G1</f>
+        <v>DASHBOARD</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -2097,56 +2263,63 @@
       <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>55</v>
+      <c r="A2" s="1" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!G2</f>
+        <v>TOTAL UNITS SALES GROSS</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!H2</f>
+        <v>TOTAL UNITS SALES NET</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!I2</f>
+        <v>PROMD VTA DIA</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!J2</f>
+        <v>PROMD VTA MES</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!K2</f>
+        <v>FORECAST</v>
+      </c>
+      <c r="F2" s="1" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!L2</f>
+        <v>FORECAST EFFICIENCY</v>
+      </c>
+      <c r="G2" s="1" t="str">
+        <f>'[1]VINCULO VTS BY SKU OPEN'!M2</f>
+        <v>DIF UNITS</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>579511</v>
+        <v>34173</v>
       </c>
       <c r="B3" s="3">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!$H$3</f>
-        <v>574918</v>
+        <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
+        <v>34173</v>
       </c>
       <c r="C3" s="4">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>27377.047619047618</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
+        <v>17086.5</v>
       </c>
       <c r="D3" s="5">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>574918</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
+        <v>375903</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
-        <v>649023</v>
+        <v>632000</v>
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.89289747820955501</v>
+        <v>5.4071202531645567E-2</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-69512</v>
+        <v>-597827</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2174,40 +2347,34 @@
         <f>'[1]VINCULO VTS BY SKU OPEN'!L4</f>
         <v>DIAS VENTA RESTA.</v>
       </c>
-      <c r="G4" s="11">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!M4</f>
-        <v>0</v>
-      </c>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>4593</v>
+        <v>0</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
-        <v>46237</v>
+        <v>46266</v>
       </c>
       <c r="C5" s="16">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46265</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
+        <v>46268</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="E5" s="19">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>21</v>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
+        <v>2</v>
       </c>
       <c r="F5" s="17">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="11">
-        <f>'[1]VINCULO VTS BY SKU OPEN'!M5</f>
-        <v>0</v>
-      </c>
+        <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
+        <v>20</v>
+      </c>
+      <c r="G5" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C8ECB0-D974-4B51-B309-F3C6A33B35F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76081B9A-0942-4A3F-B0B8-F9C314E622AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -293,6 +293,7 @@
       <sheetName val="INVENTARIO NACIONAL INICIO"/>
       <sheetName val="INVENTARIO NACIONAL 02-09-2026"/>
       <sheetName val="INVENTARIO NACIONAL 03-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 04-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -304,7 +305,8 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -335,25 +337,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>34173</v>
+            <v>85857</v>
           </cell>
           <cell r="H3">
-            <v>34173</v>
+            <v>85857</v>
           </cell>
           <cell r="I3">
-            <v>17086.5</v>
+            <v>21464.25</v>
           </cell>
           <cell r="J3">
-            <v>375903</v>
+            <v>472213.5</v>
           </cell>
           <cell r="K3">
             <v>632000</v>
           </cell>
           <cell r="L3">
-            <v>5.4071202531645567E-2</v>
+            <v>0.1358496835443038</v>
           </cell>
           <cell r="M3">
-            <v>-597827</v>
+            <v>-546143</v>
           </cell>
         </row>
         <row r="4">
@@ -364,10 +366,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>1501</v>
+            <v>3548</v>
           </cell>
           <cell r="D4">
-            <v>750.5</v>
+            <v>887</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -396,10 +398,10 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>135</v>
+            <v>301</v>
           </cell>
           <cell r="D5">
-            <v>67.5</v>
+            <v>75.25</v>
           </cell>
           <cell r="G5">
             <v>0</v>
@@ -408,16 +410,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46268</v>
+            <v>46272</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>2</v>
+            <v>4</v>
           </cell>
           <cell r="L5">
-            <v>20</v>
+            <v>18</v>
           </cell>
         </row>
         <row r="6">
@@ -428,10 +430,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>473</v>
+            <v>1770</v>
           </cell>
           <cell r="D6">
-            <v>236.5</v>
+            <v>442.5</v>
           </cell>
         </row>
         <row r="7">
@@ -442,10 +444,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>171</v>
+            <v>263</v>
           </cell>
           <cell r="D7">
-            <v>85.5</v>
+            <v>65.75</v>
           </cell>
         </row>
         <row r="8">
@@ -456,10 +458,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>11</v>
+            <v>14</v>
           </cell>
           <cell r="D8">
-            <v>5.5</v>
+            <v>3.5</v>
           </cell>
         </row>
         <row r="9">
@@ -470,10 +472,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>1570</v>
+            <v>4227</v>
           </cell>
           <cell r="D9">
-            <v>785</v>
+            <v>1056.75</v>
           </cell>
         </row>
         <row r="10">
@@ -484,10 +486,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>181</v>
+            <v>460</v>
           </cell>
           <cell r="D10">
-            <v>90.5</v>
+            <v>115</v>
           </cell>
         </row>
         <row r="11">
@@ -498,10 +500,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>362</v>
+            <v>985</v>
           </cell>
           <cell r="D11">
-            <v>181</v>
+            <v>246.25</v>
           </cell>
         </row>
         <row r="12">
@@ -512,10 +514,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>1139</v>
+            <v>2752</v>
           </cell>
           <cell r="D12">
-            <v>569.5</v>
+            <v>688</v>
           </cell>
         </row>
         <row r="13">
@@ -526,10 +528,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>456</v>
+            <v>1236</v>
           </cell>
           <cell r="D13">
-            <v>228</v>
+            <v>309</v>
           </cell>
         </row>
         <row r="14">
@@ -540,10 +542,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>4082</v>
+            <v>10474</v>
           </cell>
           <cell r="D14">
-            <v>2041</v>
+            <v>2618.5</v>
           </cell>
         </row>
         <row r="15">
@@ -554,10 +556,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>2584</v>
+            <v>6672</v>
           </cell>
           <cell r="D15">
-            <v>1292</v>
+            <v>1668</v>
           </cell>
         </row>
         <row r="16">
@@ -568,10 +570,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>2632</v>
+            <v>6687</v>
           </cell>
           <cell r="D16">
-            <v>1316</v>
+            <v>1671.75</v>
           </cell>
         </row>
         <row r="17">
@@ -582,10 +584,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>3184</v>
+            <v>7869</v>
           </cell>
           <cell r="D17">
-            <v>1592</v>
+            <v>1967.25</v>
           </cell>
         </row>
         <row r="18">
@@ -596,10 +598,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>1056</v>
+            <v>2341</v>
           </cell>
           <cell r="D18">
-            <v>528</v>
+            <v>585.25</v>
           </cell>
         </row>
         <row r="19">
@@ -610,10 +612,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>1366</v>
+            <v>3122</v>
           </cell>
           <cell r="D19">
-            <v>683</v>
+            <v>780.5</v>
           </cell>
         </row>
         <row r="20">
@@ -624,10 +626,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>1391</v>
+            <v>3064</v>
           </cell>
           <cell r="D20">
-            <v>695.5</v>
+            <v>766</v>
           </cell>
         </row>
         <row r="21">
@@ -638,10 +640,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>379</v>
+            <v>733</v>
           </cell>
           <cell r="D21">
-            <v>189.5</v>
+            <v>183.25</v>
           </cell>
         </row>
         <row r="22">
@@ -652,10 +654,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>199</v>
+            <v>323</v>
           </cell>
           <cell r="D22">
-            <v>99.5</v>
+            <v>80.75</v>
           </cell>
         </row>
         <row r="23">
@@ -666,10 +668,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>760</v>
+            <v>1705</v>
           </cell>
           <cell r="D23">
-            <v>380</v>
+            <v>426.25</v>
           </cell>
         </row>
         <row r="24">
@@ -680,10 +682,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>1256</v>
+            <v>2775</v>
           </cell>
           <cell r="D24">
-            <v>628</v>
+            <v>693.75</v>
           </cell>
         </row>
         <row r="25">
@@ -694,10 +696,10 @@
             <v>Griego Mykonos 700g</v>
           </cell>
           <cell r="C25">
-            <v>20</v>
+            <v>320</v>
           </cell>
           <cell r="D25">
-            <v>10</v>
+            <v>80</v>
           </cell>
         </row>
         <row r="26">
@@ -708,10 +710,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>687</v>
+            <v>1831</v>
           </cell>
           <cell r="D26">
-            <v>343.5</v>
+            <v>457.75</v>
           </cell>
         </row>
         <row r="27">
@@ -722,10 +724,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>618</v>
+            <v>1708</v>
           </cell>
           <cell r="D27">
-            <v>309</v>
+            <v>427</v>
           </cell>
         </row>
         <row r="28">
@@ -736,10 +738,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>777</v>
+            <v>1776</v>
           </cell>
           <cell r="D28">
-            <v>388.5</v>
+            <v>444</v>
           </cell>
         </row>
         <row r="29">
@@ -750,10 +752,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>473</v>
+            <v>1153</v>
           </cell>
           <cell r="D29">
-            <v>236.5</v>
+            <v>288.25</v>
           </cell>
         </row>
         <row r="30">
@@ -764,10 +766,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>82</v>
+            <v>846</v>
           </cell>
           <cell r="D30">
-            <v>41</v>
+            <v>211.5</v>
           </cell>
         </row>
         <row r="31">
@@ -778,10 +780,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>140</v>
+            <v>927</v>
           </cell>
           <cell r="D31">
-            <v>70</v>
+            <v>231.75</v>
           </cell>
         </row>
         <row r="32">
@@ -792,10 +794,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>198</v>
+            <v>407</v>
           </cell>
           <cell r="D32">
-            <v>99</v>
+            <v>101.75</v>
           </cell>
         </row>
         <row r="33">
@@ -806,10 +808,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>133</v>
+            <v>391</v>
           </cell>
           <cell r="D33">
-            <v>66.5</v>
+            <v>97.75</v>
           </cell>
         </row>
         <row r="34">
@@ -820,10 +822,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>797</v>
+            <v>2270</v>
           </cell>
           <cell r="D34">
-            <v>398.5</v>
+            <v>567.5</v>
           </cell>
         </row>
         <row r="35">
@@ -834,10 +836,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>654</v>
+            <v>1797</v>
           </cell>
           <cell r="D35">
-            <v>327</v>
+            <v>449.25</v>
           </cell>
         </row>
         <row r="36">
@@ -848,10 +850,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>1045</v>
+            <v>2393</v>
           </cell>
           <cell r="D36">
-            <v>522.5</v>
+            <v>598.25</v>
           </cell>
         </row>
         <row r="37">
@@ -862,10 +864,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>619</v>
+            <v>1322</v>
           </cell>
           <cell r="D37">
-            <v>309.5</v>
+            <v>330.5</v>
           </cell>
         </row>
         <row r="38">
@@ -876,10 +878,10 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>9</v>
+            <v>16</v>
           </cell>
           <cell r="D38">
-            <v>4.5</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="39">
@@ -890,10 +892,10 @@
             <v>Cremigurt Griego Dulce 4 Kg</v>
           </cell>
           <cell r="C39">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="D39">
-            <v>2</v>
+            <v>1.25</v>
           </cell>
         </row>
         <row r="40">
@@ -904,10 +906,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>238</v>
+            <v>354</v>
           </cell>
           <cell r="D40">
-            <v>119</v>
+            <v>88.5</v>
           </cell>
         </row>
         <row r="41">
@@ -918,10 +920,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>518</v>
+            <v>1532</v>
           </cell>
           <cell r="D41">
-            <v>259</v>
+            <v>383</v>
           </cell>
         </row>
         <row r="42">
@@ -932,10 +934,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>815</v>
+            <v>1603</v>
           </cell>
           <cell r="D42">
-            <v>407.5</v>
+            <v>400.75</v>
           </cell>
         </row>
         <row r="43">
@@ -946,10 +948,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>235</v>
+            <v>644</v>
           </cell>
           <cell r="D43">
-            <v>117.5</v>
+            <v>161</v>
           </cell>
         </row>
         <row r="44">
@@ -960,10 +962,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>460</v>
+            <v>1051</v>
           </cell>
           <cell r="D44">
-            <v>230</v>
+            <v>262.75</v>
           </cell>
         </row>
         <row r="45">
@@ -974,10 +976,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>238</v>
+            <v>794</v>
           </cell>
           <cell r="D45">
-            <v>119</v>
+            <v>198.5</v>
           </cell>
         </row>
         <row r="46">
@@ -988,10 +990,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>289</v>
+            <v>850</v>
           </cell>
           <cell r="D46">
-            <v>144.5</v>
+            <v>212.5</v>
           </cell>
         </row>
         <row r="47">
@@ -1002,10 +1004,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>70</v>
+            <v>133</v>
           </cell>
           <cell r="D47">
-            <v>35</v>
+            <v>33.25</v>
           </cell>
         </row>
         <row r="48">
@@ -1016,10 +1018,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>103</v>
+            <v>204</v>
           </cell>
           <cell r="D48">
-            <v>51.5</v>
+            <v>51</v>
           </cell>
         </row>
         <row r="49">
@@ -1030,10 +1032,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>28</v>
+            <v>83</v>
           </cell>
           <cell r="D49">
-            <v>14</v>
+            <v>20.75</v>
           </cell>
         </row>
         <row r="50">
@@ -1044,14 +1046,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>35</v>
+            <v>126</v>
           </cell>
           <cell r="D50">
-            <v>17.5</v>
+            <v>31.5</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1398,11 +1400,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>1501</v>
+        <v>3548</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>750.5</v>
+        <v>887</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1416,11 +1418,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>135</v>
+        <v>301</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>67.5</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1434,11 +1436,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>473</v>
+        <v>1770</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>236.5</v>
+        <v>442.5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1452,11 +1454,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>171</v>
+        <v>263</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>85.5</v>
+        <v>65.75</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1470,11 +1472,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1488,11 +1490,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>1570</v>
+        <v>4227</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>785</v>
+        <v>1056.75</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1506,11 +1508,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>181</v>
+        <v>460</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>90.5</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1524,11 +1526,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>362</v>
+        <v>985</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>181</v>
+        <v>246.25</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1542,11 +1544,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>1139</v>
+        <v>2752</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>569.5</v>
+        <v>688</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1560,11 +1562,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>456</v>
+        <v>1236</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>228</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1578,11 +1580,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>4082</v>
+        <v>10474</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>2041</v>
+        <v>2618.5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1596,11 +1598,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>2584</v>
+        <v>6672</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>1292</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1614,11 +1616,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>2632</v>
+        <v>6687</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>1316</v>
+        <v>1671.75</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1632,11 +1634,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>3184</v>
+        <v>7869</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>1592</v>
+        <v>1967.25</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1650,11 +1652,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>1056</v>
+        <v>2341</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>528</v>
+        <v>585.25</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1668,11 +1670,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>1366</v>
+        <v>3122</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>683</v>
+        <v>780.5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1686,11 +1688,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>1391</v>
+        <v>3064</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>695.5</v>
+        <v>766</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1704,11 +1706,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>379</v>
+        <v>733</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>189.5</v>
+        <v>183.25</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1722,11 +1724,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>199</v>
+        <v>323</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>99.5</v>
+        <v>80.75</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1740,11 +1742,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>760</v>
+        <v>1705</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>380</v>
+        <v>426.25</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1758,11 +1760,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>1256</v>
+        <v>2775</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>628</v>
+        <v>693.75</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1776,11 +1778,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>10</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1794,11 +1796,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>687</v>
+        <v>1831</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>343.5</v>
+        <v>457.75</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1812,11 +1814,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>618</v>
+        <v>1708</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>309</v>
+        <v>427</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1830,11 +1832,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>777</v>
+        <v>1776</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>388.5</v>
+        <v>444</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1848,11 +1850,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>473</v>
+        <v>1153</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>236.5</v>
+        <v>288.25</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1866,11 +1868,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>82</v>
+        <v>846</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>41</v>
+        <v>211.5</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1884,11 +1886,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>140</v>
+        <v>927</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>70</v>
+        <v>231.75</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1902,11 +1904,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>198</v>
+        <v>407</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>99</v>
+        <v>101.75</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1920,11 +1922,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>133</v>
+        <v>391</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>66.5</v>
+        <v>97.75</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1938,11 +1940,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>797</v>
+        <v>2270</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>398.5</v>
+        <v>567.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1956,11 +1958,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>654</v>
+        <v>1797</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>327</v>
+        <v>449.25</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1974,11 +1976,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>1045</v>
+        <v>2393</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>522.5</v>
+        <v>598.25</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1992,11 +1994,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>619</v>
+        <v>1322</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>309.5</v>
+        <v>330.5</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2010,11 +2012,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2028,11 +2030,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2046,11 +2048,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>238</v>
+        <v>354</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>119</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2064,11 +2066,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>518</v>
+        <v>1532</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>259</v>
+        <v>383</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2082,11 +2084,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>815</v>
+        <v>1603</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>407.5</v>
+        <v>400.75</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2100,11 +2102,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>235</v>
+        <v>644</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>117.5</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2118,11 +2120,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>460</v>
+        <v>1051</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>230</v>
+        <v>262.75</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2136,11 +2138,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>238</v>
+        <v>794</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>119</v>
+        <v>198.5</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2154,11 +2156,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>289</v>
+        <v>850</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>144.5</v>
+        <v>212.5</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2172,11 +2174,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>35</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2190,11 +2192,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>103</v>
+        <v>204</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>51.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2208,11 +2210,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>14</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2226,11 +2228,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>17.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2295,19 +2297,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>34173</v>
+        <v>85857</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>34173</v>
+        <v>85857</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>17086.5</v>
+        <v>21464.25</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>375903</v>
+        <v>472213.5</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2315,11 +2317,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>5.4071202531645567E-2</v>
+        <v>0.1358496835443038</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-597827</v>
+        <v>-546143</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2360,7 +2362,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2368,11 +2370,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76081B9A-0942-4A3F-B0B8-F9C314E622AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D25E4E-52C3-4F44-B402-40F88B8EF8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -294,6 +294,7 @@
       <sheetName val="INVENTARIO NACIONAL 02-09-2026"/>
       <sheetName val="INVENTARIO NACIONAL 03-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 04-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 08-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -306,7 +307,8 @@
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
-      <sheetData sheetId="6">
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -337,25 +339,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>85857</v>
+            <v>119681</v>
           </cell>
           <cell r="H3">
-            <v>85857</v>
+            <v>119681</v>
           </cell>
           <cell r="I3">
-            <v>21464.25</v>
+            <v>23936.2</v>
           </cell>
           <cell r="J3">
-            <v>472213.5</v>
+            <v>526596.4</v>
           </cell>
           <cell r="K3">
             <v>632000</v>
           </cell>
           <cell r="L3">
-            <v>0.1358496835443038</v>
+            <v>0.18936867088607595</v>
           </cell>
           <cell r="M3">
-            <v>-546143</v>
+            <v>-512319</v>
           </cell>
         </row>
         <row r="4">
@@ -366,10 +368,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>3548</v>
+            <v>4937</v>
           </cell>
           <cell r="D4">
-            <v>887</v>
+            <v>987.4</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -398,10 +400,10 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>301</v>
+            <v>419</v>
           </cell>
           <cell r="D5">
-            <v>75.25</v>
+            <v>83.8</v>
           </cell>
           <cell r="G5">
             <v>0</v>
@@ -410,16 +412,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46272</v>
+            <v>46273</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="L5">
-            <v>18</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="6">
@@ -430,10 +432,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>1770</v>
+            <v>2445</v>
           </cell>
           <cell r="D6">
-            <v>442.5</v>
+            <v>489</v>
           </cell>
         </row>
         <row r="7">
@@ -444,10 +446,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>263</v>
+            <v>376</v>
           </cell>
           <cell r="D7">
-            <v>65.75</v>
+            <v>75.2</v>
           </cell>
         </row>
         <row r="8">
@@ -458,10 +460,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>14</v>
+            <v>31</v>
           </cell>
           <cell r="D8">
-            <v>3.5</v>
+            <v>6.2</v>
           </cell>
         </row>
         <row r="9">
@@ -472,10 +474,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>4227</v>
+            <v>6695</v>
           </cell>
           <cell r="D9">
-            <v>1056.75</v>
+            <v>1339</v>
           </cell>
         </row>
         <row r="10">
@@ -486,10 +488,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>460</v>
+            <v>565</v>
           </cell>
           <cell r="D10">
-            <v>115</v>
+            <v>113</v>
           </cell>
         </row>
         <row r="11">
@@ -500,10 +502,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>985</v>
+            <v>1178</v>
           </cell>
           <cell r="D11">
-            <v>246.25</v>
+            <v>235.6</v>
           </cell>
         </row>
         <row r="12">
@@ -514,10 +516,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>2752</v>
+            <v>3329</v>
           </cell>
           <cell r="D12">
-            <v>688</v>
+            <v>665.8</v>
           </cell>
         </row>
         <row r="13">
@@ -528,10 +530,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>1236</v>
+            <v>1453</v>
           </cell>
           <cell r="D13">
-            <v>309</v>
+            <v>290.60000000000002</v>
           </cell>
         </row>
         <row r="14">
@@ -542,10 +544,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>10474</v>
+            <v>15518</v>
           </cell>
           <cell r="D14">
-            <v>2618.5</v>
+            <v>3103.6</v>
           </cell>
         </row>
         <row r="15">
@@ -556,10 +558,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>6672</v>
+            <v>9416</v>
           </cell>
           <cell r="D15">
-            <v>1668</v>
+            <v>1883.2</v>
           </cell>
         </row>
         <row r="16">
@@ -570,10 +572,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>6687</v>
+            <v>9988</v>
           </cell>
           <cell r="D16">
-            <v>1671.75</v>
+            <v>1997.6</v>
           </cell>
         </row>
         <row r="17">
@@ -584,10 +586,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>7869</v>
+            <v>11515</v>
           </cell>
           <cell r="D17">
-            <v>1967.25</v>
+            <v>2303</v>
           </cell>
         </row>
         <row r="18">
@@ -598,10 +600,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>2341</v>
+            <v>2893</v>
           </cell>
           <cell r="D18">
-            <v>585.25</v>
+            <v>578.6</v>
           </cell>
         </row>
         <row r="19">
@@ -612,10 +614,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>3122</v>
+            <v>3802</v>
           </cell>
           <cell r="D19">
-            <v>780.5</v>
+            <v>760.4</v>
           </cell>
         </row>
         <row r="20">
@@ -626,10 +628,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>3064</v>
+            <v>3760</v>
           </cell>
           <cell r="D20">
-            <v>766</v>
+            <v>752</v>
           </cell>
         </row>
         <row r="21">
@@ -640,10 +642,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>733</v>
+            <v>980</v>
           </cell>
           <cell r="D21">
-            <v>183.25</v>
+            <v>196</v>
           </cell>
         </row>
         <row r="22">
@@ -654,10 +656,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>323</v>
+            <v>429</v>
           </cell>
           <cell r="D22">
-            <v>80.75</v>
+            <v>85.8</v>
           </cell>
         </row>
         <row r="23">
@@ -668,10 +670,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>1705</v>
+            <v>2181</v>
           </cell>
           <cell r="D23">
-            <v>426.25</v>
+            <v>436.2</v>
           </cell>
         </row>
         <row r="24">
@@ -682,10 +684,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>2775</v>
+            <v>3482</v>
           </cell>
           <cell r="D24">
-            <v>693.75</v>
+            <v>696.4</v>
           </cell>
         </row>
         <row r="25">
@@ -699,7 +701,7 @@
             <v>320</v>
           </cell>
           <cell r="D25">
-            <v>80</v>
+            <v>64</v>
           </cell>
         </row>
         <row r="26">
@@ -710,10 +712,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>1831</v>
+            <v>3061</v>
           </cell>
           <cell r="D26">
-            <v>457.75</v>
+            <v>612.20000000000005</v>
           </cell>
         </row>
         <row r="27">
@@ -724,10 +726,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>1708</v>
+            <v>4154</v>
           </cell>
           <cell r="D27">
-            <v>427</v>
+            <v>830.8</v>
           </cell>
         </row>
         <row r="28">
@@ -738,10 +740,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>1776</v>
+            <v>2150</v>
           </cell>
           <cell r="D28">
-            <v>444</v>
+            <v>430</v>
           </cell>
         </row>
         <row r="29">
@@ -752,10 +754,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>1153</v>
+            <v>1453</v>
           </cell>
           <cell r="D29">
-            <v>288.25</v>
+            <v>290.60000000000002</v>
           </cell>
         </row>
         <row r="30">
@@ -766,10 +768,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>846</v>
+            <v>1125</v>
           </cell>
           <cell r="D30">
-            <v>211.5</v>
+            <v>225</v>
           </cell>
         </row>
         <row r="31">
@@ -780,10 +782,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>927</v>
+            <v>1402</v>
           </cell>
           <cell r="D31">
-            <v>231.75</v>
+            <v>280.39999999999998</v>
           </cell>
         </row>
         <row r="32">
@@ -794,10 +796,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>407</v>
+            <v>520</v>
           </cell>
           <cell r="D32">
-            <v>101.75</v>
+            <v>104</v>
           </cell>
         </row>
         <row r="33">
@@ -808,10 +810,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>391</v>
+            <v>496</v>
           </cell>
           <cell r="D33">
-            <v>97.75</v>
+            <v>99.2</v>
           </cell>
         </row>
         <row r="34">
@@ -822,10 +824,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>2270</v>
+            <v>3030</v>
           </cell>
           <cell r="D34">
-            <v>567.5</v>
+            <v>606</v>
           </cell>
         </row>
         <row r="35">
@@ -836,10 +838,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>1797</v>
+            <v>2378</v>
           </cell>
           <cell r="D35">
-            <v>449.25</v>
+            <v>475.6</v>
           </cell>
         </row>
         <row r="36">
@@ -850,10 +852,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>2393</v>
+            <v>3176</v>
           </cell>
           <cell r="D36">
-            <v>598.25</v>
+            <v>635.20000000000005</v>
           </cell>
         </row>
         <row r="37">
@@ -864,10 +866,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>1322</v>
+            <v>1794</v>
           </cell>
           <cell r="D37">
-            <v>330.5</v>
+            <v>358.8</v>
           </cell>
         </row>
         <row r="38">
@@ -878,7 +880,7 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>16</v>
+            <v>20</v>
           </cell>
           <cell r="D38">
             <v>4</v>
@@ -892,10 +894,10 @@
             <v>Cremigurt Griego Dulce 4 Kg</v>
           </cell>
           <cell r="C39">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="D39">
-            <v>1.25</v>
+            <v>1.2</v>
           </cell>
         </row>
         <row r="40">
@@ -906,10 +908,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>354</v>
+            <v>483</v>
           </cell>
           <cell r="D40">
-            <v>88.5</v>
+            <v>96.6</v>
           </cell>
         </row>
         <row r="41">
@@ -920,10 +922,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>1532</v>
+            <v>2040</v>
           </cell>
           <cell r="D41">
-            <v>383</v>
+            <v>408</v>
           </cell>
         </row>
         <row r="42">
@@ -934,10 +936,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>1603</v>
+            <v>1964</v>
           </cell>
           <cell r="D42">
-            <v>400.75</v>
+            <v>392.8</v>
           </cell>
         </row>
         <row r="43">
@@ -948,10 +950,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>644</v>
+            <v>703</v>
           </cell>
           <cell r="D43">
-            <v>161</v>
+            <v>140.6</v>
           </cell>
         </row>
         <row r="44">
@@ -962,10 +964,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>1051</v>
+            <v>1248</v>
           </cell>
           <cell r="D44">
-            <v>262.75</v>
+            <v>249.6</v>
           </cell>
         </row>
         <row r="45">
@@ -976,10 +978,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>794</v>
+            <v>963</v>
           </cell>
           <cell r="D45">
-            <v>198.5</v>
+            <v>192.6</v>
           </cell>
         </row>
         <row r="46">
@@ -990,10 +992,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>850</v>
+            <v>1051</v>
           </cell>
           <cell r="D46">
-            <v>212.5</v>
+            <v>210.2</v>
           </cell>
         </row>
         <row r="47">
@@ -1004,10 +1006,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>133</v>
+            <v>144</v>
           </cell>
           <cell r="D47">
-            <v>33.25</v>
+            <v>28.8</v>
           </cell>
         </row>
         <row r="48">
@@ -1018,10 +1020,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>204</v>
+            <v>346</v>
           </cell>
           <cell r="D48">
-            <v>51</v>
+            <v>69.2</v>
           </cell>
         </row>
         <row r="49">
@@ -1032,10 +1034,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>83</v>
+            <v>113</v>
           </cell>
           <cell r="D49">
-            <v>20.75</v>
+            <v>22.6</v>
           </cell>
         </row>
         <row r="50">
@@ -1046,14 +1048,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>126</v>
+            <v>149</v>
           </cell>
           <cell r="D50">
-            <v>31.5</v>
+            <v>29.8</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1400,11 +1402,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>3548</v>
+        <v>4937</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>887</v>
+        <v>987.4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1418,11 +1420,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>301</v>
+        <v>419</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>75.25</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1436,11 +1438,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>1770</v>
+        <v>2445</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>442.5</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1454,11 +1456,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>263</v>
+        <v>376</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>65.75</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1472,11 +1474,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1490,11 +1492,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>4227</v>
+        <v>6695</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1056.75</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1508,11 +1510,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>460</v>
+        <v>565</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1526,11 +1528,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>985</v>
+        <v>1178</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>246.25</v>
+        <v>235.6</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1544,11 +1546,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>2752</v>
+        <v>3329</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>688</v>
+        <v>665.8</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1562,11 +1564,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>1236</v>
+        <v>1453</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>309</v>
+        <v>290.60000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1580,11 +1582,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>10474</v>
+        <v>15518</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>2618.5</v>
+        <v>3103.6</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1598,11 +1600,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>6672</v>
+        <v>9416</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>1668</v>
+        <v>1883.2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1616,11 +1618,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>6687</v>
+        <v>9988</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>1671.75</v>
+        <v>1997.6</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1634,11 +1636,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>7869</v>
+        <v>11515</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>1967.25</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1652,11 +1654,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>2341</v>
+        <v>2893</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>585.25</v>
+        <v>578.6</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1670,11 +1672,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>3122</v>
+        <v>3802</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>780.5</v>
+        <v>760.4</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1688,11 +1690,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>3064</v>
+        <v>3760</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>766</v>
+        <v>752</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1706,11 +1708,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>733</v>
+        <v>980</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>183.25</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1724,11 +1726,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>323</v>
+        <v>429</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>80.75</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1742,11 +1744,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>1705</v>
+        <v>2181</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>426.25</v>
+        <v>436.2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1760,11 +1762,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>2775</v>
+        <v>3482</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>693.75</v>
+        <v>696.4</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1782,7 +1784,7 @@
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>80</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1796,11 +1798,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>1831</v>
+        <v>3061</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>457.75</v>
+        <v>612.20000000000005</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1814,11 +1816,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>1708</v>
+        <v>4154</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>427</v>
+        <v>830.8</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1832,11 +1834,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>1776</v>
+        <v>2150</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>444</v>
+        <v>430</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1850,11 +1852,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>1153</v>
+        <v>1453</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>288.25</v>
+        <v>290.60000000000002</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1868,11 +1870,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>846</v>
+        <v>1125</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>211.5</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1886,11 +1888,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>927</v>
+        <v>1402</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>231.75</v>
+        <v>280.39999999999998</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1904,11 +1906,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>101.75</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1922,11 +1924,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>391</v>
+        <v>496</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>97.75</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1940,11 +1942,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>2270</v>
+        <v>3030</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>567.5</v>
+        <v>606</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1958,11 +1960,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>1797</v>
+        <v>2378</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>449.25</v>
+        <v>475.6</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1976,11 +1978,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>2393</v>
+        <v>3176</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>598.25</v>
+        <v>635.20000000000005</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1994,11 +1996,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>1322</v>
+        <v>1794</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>330.5</v>
+        <v>358.8</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2012,7 +2014,7 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
@@ -2030,11 +2032,11 @@
       </c>
       <c r="C37" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C39</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2048,11 +2050,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>354</v>
+        <v>483</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>88.5</v>
+        <v>96.6</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2066,11 +2068,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>1532</v>
+        <v>2040</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>383</v>
+        <v>408</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2084,11 +2086,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>1603</v>
+        <v>1964</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>400.75</v>
+        <v>392.8</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2102,11 +2104,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>644</v>
+        <v>703</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>161</v>
+        <v>140.6</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2120,11 +2122,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>1051</v>
+        <v>1248</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>262.75</v>
+        <v>249.6</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2138,11 +2140,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>794</v>
+        <v>963</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>198.5</v>
+        <v>192.6</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2156,11 +2158,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>850</v>
+        <v>1051</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>212.5</v>
+        <v>210.2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2174,11 +2176,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>33.25</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2192,11 +2194,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>204</v>
+        <v>346</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>51</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2210,11 +2212,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>20.75</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2228,11 +2230,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>31.5</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2297,19 +2299,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>85857</v>
+        <v>119681</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>85857</v>
+        <v>119681</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>21464.25</v>
+        <v>23936.2</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>472213.5</v>
+        <v>526596.4</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2317,11 +2319,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.1358496835443038</v>
+        <v>0.18936867088607595</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-546143</v>
+        <v>-512319</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2362,7 +2364,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2370,11 +2372,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D25E4E-52C3-4F44-B402-40F88B8EF8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14266DD5-CE58-440A-B52F-F6CA8F73A951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
@@ -295,6 +295,7 @@
       <sheetName val="INVENTARIO NACIONAL 03-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 04-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 08-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 09-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -308,7 +309,8 @@
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
-      <sheetData sheetId="7">
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -339,25 +341,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>119681</v>
+            <v>147904</v>
           </cell>
           <cell r="H3">
-            <v>119681</v>
+            <v>147904</v>
           </cell>
           <cell r="I3">
-            <v>23936.2</v>
+            <v>24650.666666666668</v>
           </cell>
           <cell r="J3">
-            <v>526596.4</v>
+            <v>542314.66666666674</v>
           </cell>
           <cell r="K3">
-            <v>632000</v>
+            <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.18936867088607595</v>
+            <v>0.21973849004072257</v>
           </cell>
           <cell r="M3">
-            <v>-512319</v>
+            <v>-525187</v>
           </cell>
         </row>
         <row r="4">
@@ -368,10 +370,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>4937</v>
+            <v>6050</v>
           </cell>
           <cell r="D4">
-            <v>987.4</v>
+            <v>1008.3333333333334</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -400,10 +402,10 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>419</v>
+            <v>533</v>
           </cell>
           <cell r="D5">
-            <v>83.8</v>
+            <v>88.833333333333329</v>
           </cell>
           <cell r="G5">
             <v>0</v>
@@ -412,16 +414,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46273</v>
+            <v>46274</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>5</v>
+            <v>6</v>
           </cell>
           <cell r="L5">
-            <v>17</v>
+            <v>16</v>
           </cell>
         </row>
         <row r="6">
@@ -432,10 +434,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>2445</v>
+            <v>2579</v>
           </cell>
           <cell r="D6">
-            <v>489</v>
+            <v>429.83333333333331</v>
           </cell>
         </row>
         <row r="7">
@@ -446,10 +448,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>376</v>
+            <v>433</v>
           </cell>
           <cell r="D7">
-            <v>75.2</v>
+            <v>72.166666666666671</v>
           </cell>
         </row>
         <row r="8">
@@ -460,10 +462,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>31</v>
+            <v>53</v>
           </cell>
           <cell r="D8">
-            <v>6.2</v>
+            <v>8.8333333333333339</v>
           </cell>
         </row>
         <row r="9">
@@ -474,10 +476,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>6695</v>
+            <v>7876</v>
           </cell>
           <cell r="D9">
-            <v>1339</v>
+            <v>1312.6666666666667</v>
           </cell>
         </row>
         <row r="10">
@@ -488,10 +490,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>565</v>
+            <v>719</v>
           </cell>
           <cell r="D10">
-            <v>113</v>
+            <v>119.83333333333333</v>
           </cell>
         </row>
         <row r="11">
@@ -502,10 +504,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>1178</v>
+            <v>1440</v>
           </cell>
           <cell r="D11">
-            <v>235.6</v>
+            <v>240</v>
           </cell>
         </row>
         <row r="12">
@@ -516,10 +518,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>3329</v>
+            <v>4132</v>
           </cell>
           <cell r="D12">
-            <v>665.8</v>
+            <v>688.66666666666663</v>
           </cell>
         </row>
         <row r="13">
@@ -530,10 +532,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>1453</v>
+            <v>1812</v>
           </cell>
           <cell r="D13">
-            <v>290.60000000000002</v>
+            <v>302</v>
           </cell>
         </row>
         <row r="14">
@@ -544,10 +546,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>15518</v>
+            <v>18780</v>
           </cell>
           <cell r="D14">
-            <v>3103.6</v>
+            <v>3130</v>
           </cell>
         </row>
         <row r="15">
@@ -558,10 +560,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>9416</v>
+            <v>11587</v>
           </cell>
           <cell r="D15">
-            <v>1883.2</v>
+            <v>1931.1666666666667</v>
           </cell>
         </row>
         <row r="16">
@@ -572,10 +574,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>9988</v>
+            <v>12604</v>
           </cell>
           <cell r="D16">
-            <v>1997.6</v>
+            <v>2100.6666666666665</v>
           </cell>
         </row>
         <row r="17">
@@ -586,10 +588,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>11515</v>
+            <v>14095</v>
           </cell>
           <cell r="D17">
-            <v>2303</v>
+            <v>2349.1666666666665</v>
           </cell>
         </row>
         <row r="18">
@@ -600,10 +602,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>2893</v>
+            <v>3804</v>
           </cell>
           <cell r="D18">
-            <v>578.6</v>
+            <v>634</v>
           </cell>
         </row>
         <row r="19">
@@ -614,10 +616,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>3802</v>
+            <v>4739</v>
           </cell>
           <cell r="D19">
-            <v>760.4</v>
+            <v>789.83333333333337</v>
           </cell>
         </row>
         <row r="20">
@@ -628,10 +630,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>3760</v>
+            <v>4689</v>
           </cell>
           <cell r="D20">
-            <v>752</v>
+            <v>781.5</v>
           </cell>
         </row>
         <row r="21">
@@ -642,10 +644,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>980</v>
+            <v>1280</v>
           </cell>
           <cell r="D21">
-            <v>196</v>
+            <v>213.33333333333334</v>
           </cell>
         </row>
         <row r="22">
@@ -656,10 +658,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>429</v>
+            <v>568</v>
           </cell>
           <cell r="D22">
-            <v>85.8</v>
+            <v>94.666666666666671</v>
           </cell>
         </row>
         <row r="23">
@@ -670,10 +672,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>2181</v>
+            <v>2776</v>
           </cell>
           <cell r="D23">
-            <v>436.2</v>
+            <v>462.66666666666669</v>
           </cell>
         </row>
         <row r="24">
@@ -684,10 +686,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>3482</v>
+            <v>4550</v>
           </cell>
           <cell r="D24">
-            <v>696.4</v>
+            <v>758.33333333333337</v>
           </cell>
         </row>
         <row r="25">
@@ -698,10 +700,10 @@
             <v>Griego Mykonos 700g</v>
           </cell>
           <cell r="C25">
-            <v>320</v>
+            <v>330</v>
           </cell>
           <cell r="D25">
-            <v>64</v>
+            <v>55</v>
           </cell>
         </row>
         <row r="26">
@@ -712,10 +714,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>3061</v>
+            <v>3626</v>
           </cell>
           <cell r="D26">
-            <v>612.20000000000005</v>
+            <v>604.33333333333337</v>
           </cell>
         </row>
         <row r="27">
@@ -726,10 +728,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>4154</v>
+            <v>5273</v>
           </cell>
           <cell r="D27">
-            <v>830.8</v>
+            <v>878.83333333333337</v>
           </cell>
         </row>
         <row r="28">
@@ -740,10 +742,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>2150</v>
+            <v>2513</v>
           </cell>
           <cell r="D28">
-            <v>430</v>
+            <v>418.83333333333331</v>
           </cell>
         </row>
         <row r="29">
@@ -754,10 +756,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>1453</v>
+            <v>1813</v>
           </cell>
           <cell r="D29">
-            <v>290.60000000000002</v>
+            <v>302.16666666666669</v>
           </cell>
         </row>
         <row r="30">
@@ -768,10 +770,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>1125</v>
+            <v>1344</v>
           </cell>
           <cell r="D30">
-            <v>225</v>
+            <v>224</v>
           </cell>
         </row>
         <row r="31">
@@ -782,10 +784,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>1402</v>
+            <v>1600</v>
           </cell>
           <cell r="D31">
-            <v>280.39999999999998</v>
+            <v>266.66666666666669</v>
           </cell>
         </row>
         <row r="32">
@@ -796,10 +798,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>520</v>
+            <v>661</v>
           </cell>
           <cell r="D32">
-            <v>104</v>
+            <v>110.16666666666667</v>
           </cell>
         </row>
         <row r="33">
@@ -810,10 +812,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>496</v>
+            <v>634</v>
           </cell>
           <cell r="D33">
-            <v>99.2</v>
+            <v>105.66666666666667</v>
           </cell>
         </row>
         <row r="34">
@@ -824,10 +826,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>3030</v>
+            <v>3802</v>
           </cell>
           <cell r="D34">
-            <v>606</v>
+            <v>633.66666666666663</v>
           </cell>
         </row>
         <row r="35">
@@ -838,10 +840,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>2378</v>
+            <v>3101</v>
           </cell>
           <cell r="D35">
-            <v>475.6</v>
+            <v>516.83333333333337</v>
           </cell>
         </row>
         <row r="36">
@@ -852,10 +854,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>3176</v>
+            <v>4066</v>
           </cell>
           <cell r="D36">
-            <v>635.20000000000005</v>
+            <v>677.66666666666663</v>
           </cell>
         </row>
         <row r="37">
@@ -866,10 +868,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>1794</v>
+            <v>2344</v>
           </cell>
           <cell r="D37">
-            <v>358.8</v>
+            <v>390.66666666666669</v>
           </cell>
         </row>
         <row r="38">
@@ -880,10 +882,10 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>20</v>
+            <v>21</v>
           </cell>
           <cell r="D38">
-            <v>4</v>
+            <v>3.5</v>
           </cell>
         </row>
         <row r="39">
@@ -897,7 +899,7 @@
             <v>6</v>
           </cell>
           <cell r="D39">
-            <v>1.2</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="40">
@@ -908,10 +910,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>483</v>
+            <v>621</v>
           </cell>
           <cell r="D40">
-            <v>96.6</v>
+            <v>103.5</v>
           </cell>
         </row>
         <row r="41">
@@ -922,10 +924,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>2040</v>
+            <v>2610</v>
           </cell>
           <cell r="D41">
-            <v>408</v>
+            <v>435</v>
           </cell>
         </row>
         <row r="42">
@@ -936,10 +938,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>1964</v>
+            <v>2377</v>
           </cell>
           <cell r="D42">
-            <v>392.8</v>
+            <v>396.16666666666669</v>
           </cell>
         </row>
         <row r="43">
@@ -950,10 +952,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>703</v>
+            <v>878</v>
           </cell>
           <cell r="D43">
-            <v>140.6</v>
+            <v>146.33333333333334</v>
           </cell>
         </row>
         <row r="44">
@@ -964,10 +966,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>1248</v>
+            <v>1647</v>
           </cell>
           <cell r="D44">
-            <v>249.6</v>
+            <v>274.5</v>
           </cell>
         </row>
         <row r="45">
@@ -978,10 +980,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>963</v>
+            <v>1158</v>
           </cell>
           <cell r="D45">
-            <v>192.6</v>
+            <v>193</v>
           </cell>
         </row>
         <row r="46">
@@ -992,10 +994,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>1051</v>
+            <v>1351</v>
           </cell>
           <cell r="D46">
-            <v>210.2</v>
+            <v>225.16666666666666</v>
           </cell>
         </row>
         <row r="47">
@@ -1006,10 +1008,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>144</v>
+            <v>192</v>
           </cell>
           <cell r="D47">
-            <v>28.8</v>
+            <v>32</v>
           </cell>
         </row>
         <row r="48">
@@ -1020,10 +1022,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>346</v>
+            <v>461</v>
           </cell>
           <cell r="D48">
-            <v>69.2</v>
+            <v>76.833333333333329</v>
           </cell>
         </row>
         <row r="49">
@@ -1034,10 +1036,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>113</v>
+            <v>168</v>
           </cell>
           <cell r="D49">
-            <v>22.6</v>
+            <v>28</v>
           </cell>
         </row>
         <row r="50">
@@ -1048,14 +1050,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>149</v>
+            <v>208</v>
           </cell>
           <cell r="D50">
-            <v>29.8</v>
+            <v>34.666666666666664</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1402,11 +1404,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>4937</v>
+        <v>6050</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>987.4</v>
+        <v>1008.3333333333334</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1420,11 +1422,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>419</v>
+        <v>533</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>83.8</v>
+        <v>88.833333333333329</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1438,11 +1440,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>2445</v>
+        <v>2579</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>489</v>
+        <v>429.83333333333331</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1456,11 +1458,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>75.2</v>
+        <v>72.166666666666671</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1474,11 +1476,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>6.2</v>
+        <v>8.8333333333333339</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1492,11 +1494,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>6695</v>
+        <v>7876</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1339</v>
+        <v>1312.6666666666667</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1510,11 +1512,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>565</v>
+        <v>719</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>113</v>
+        <v>119.83333333333333</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1528,11 +1530,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>1178</v>
+        <v>1440</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>235.6</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1546,11 +1548,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>3329</v>
+        <v>4132</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>665.8</v>
+        <v>688.66666666666663</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1564,11 +1566,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>1453</v>
+        <v>1812</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>290.60000000000002</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1582,11 +1584,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>15518</v>
+        <v>18780</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3103.6</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1600,11 +1602,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>9416</v>
+        <v>11587</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>1883.2</v>
+        <v>1931.1666666666667</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1618,11 +1620,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>9988</v>
+        <v>12604</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>1997.6</v>
+        <v>2100.6666666666665</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1636,11 +1638,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>11515</v>
+        <v>14095</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2303</v>
+        <v>2349.1666666666665</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1654,11 +1656,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>2893</v>
+        <v>3804</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>578.6</v>
+        <v>634</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1672,11 +1674,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>3802</v>
+        <v>4739</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>760.4</v>
+        <v>789.83333333333337</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1690,11 +1692,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>3760</v>
+        <v>4689</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>752</v>
+        <v>781.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1708,11 +1710,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>980</v>
+        <v>1280</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>196</v>
+        <v>213.33333333333334</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1726,11 +1728,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>429</v>
+        <v>568</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>85.8</v>
+        <v>94.666666666666671</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1744,11 +1746,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>2181</v>
+        <v>2776</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>436.2</v>
+        <v>462.66666666666669</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1762,11 +1764,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>3482</v>
+        <v>4550</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>696.4</v>
+        <v>758.33333333333337</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1780,11 +1782,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1798,11 +1800,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>3061</v>
+        <v>3626</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>612.20000000000005</v>
+        <v>604.33333333333337</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1816,11 +1818,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>4154</v>
+        <v>5273</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>830.8</v>
+        <v>878.83333333333337</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1834,11 +1836,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>2150</v>
+        <v>2513</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>430</v>
+        <v>418.83333333333331</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1852,11 +1854,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>1453</v>
+        <v>1813</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>290.60000000000002</v>
+        <v>302.16666666666669</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1870,11 +1872,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>1125</v>
+        <v>1344</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1888,11 +1890,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>1402</v>
+        <v>1600</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>280.39999999999998</v>
+        <v>266.66666666666669</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1906,11 +1908,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>520</v>
+        <v>661</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>104</v>
+        <v>110.16666666666667</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1924,11 +1926,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>496</v>
+        <v>634</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>99.2</v>
+        <v>105.66666666666667</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1942,11 +1944,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>3030</v>
+        <v>3802</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>606</v>
+        <v>633.66666666666663</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1960,11 +1962,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>2378</v>
+        <v>3101</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>475.6</v>
+        <v>516.83333333333337</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1978,11 +1980,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>3176</v>
+        <v>4066</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>635.20000000000005</v>
+        <v>677.66666666666663</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1996,11 +1998,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>1794</v>
+        <v>2344</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>358.8</v>
+        <v>390.66666666666669</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2014,11 +2016,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2036,7 +2038,7 @@
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2050,11 +2052,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>483</v>
+        <v>621</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>96.6</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2068,11 +2070,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>2040</v>
+        <v>2610</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>408</v>
+        <v>435</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2086,11 +2088,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>1964</v>
+        <v>2377</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>392.8</v>
+        <v>396.16666666666669</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2104,11 +2106,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>703</v>
+        <v>878</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>140.6</v>
+        <v>146.33333333333334</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2122,11 +2124,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>1248</v>
+        <v>1647</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>249.6</v>
+        <v>274.5</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2140,11 +2142,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>963</v>
+        <v>1158</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>192.6</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2158,11 +2160,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>1051</v>
+        <v>1351</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>210.2</v>
+        <v>225.16666666666666</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2176,11 +2178,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>144</v>
+        <v>192</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>28.8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2194,11 +2196,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>346</v>
+        <v>461</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>69.2</v>
+        <v>76.833333333333329</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2212,11 +2214,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>22.6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2230,11 +2232,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>149</v>
+        <v>208</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>29.8</v>
+        <v>34.666666666666664</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2299,31 +2301,31 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>119681</v>
+        <v>147904</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>119681</v>
+        <v>147904</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>23936.2</v>
+        <v>24650.666666666668</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>526596.4</v>
+        <v>542314.66666666674</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
-        <v>632000</v>
+        <v>673091</v>
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.18936867088607595</v>
+        <v>0.21973849004072257</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-512319</v>
+        <v>-525187</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2364,7 +2366,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2372,11 +2374,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14266DD5-CE58-440A-B52F-F6CA8F73A951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4C46BB-52FF-46CB-8D41-789D0CD632A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -341,25 +341,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>147904</v>
+            <v>188094</v>
           </cell>
           <cell r="H3">
-            <v>147904</v>
+            <v>183291</v>
           </cell>
           <cell r="I3">
-            <v>24650.666666666668</v>
+            <v>26184.428571428572</v>
           </cell>
           <cell r="J3">
-            <v>542314.66666666674</v>
+            <v>576057.42857142864</v>
           </cell>
           <cell r="K3">
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.21973849004072257</v>
+            <v>0.27944809839977058</v>
           </cell>
           <cell r="M3">
-            <v>-525187</v>
+            <v>-484997</v>
           </cell>
         </row>
         <row r="4">
@@ -370,10 +370,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>6050</v>
+            <v>7805</v>
           </cell>
           <cell r="D4">
-            <v>1008.3333333333334</v>
+            <v>1115</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -402,28 +402,28 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>533</v>
+            <v>611</v>
           </cell>
           <cell r="D5">
-            <v>88.833333333333329</v>
+            <v>87.285714285714292</v>
           </cell>
           <cell r="G5">
-            <v>0</v>
+            <v>4803</v>
           </cell>
           <cell r="H5">
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46274</v>
+            <v>46275</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>6</v>
+            <v>7</v>
           </cell>
           <cell r="L5">
-            <v>16</v>
+            <v>15</v>
           </cell>
         </row>
         <row r="6">
@@ -434,10 +434,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>2579</v>
+            <v>3130</v>
           </cell>
           <cell r="D6">
-            <v>429.83333333333331</v>
+            <v>447.14285714285717</v>
           </cell>
         </row>
         <row r="7">
@@ -448,10 +448,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>433</v>
+            <v>733</v>
           </cell>
           <cell r="D7">
-            <v>72.166666666666671</v>
+            <v>104.71428571428571</v>
           </cell>
         </row>
         <row r="8">
@@ -462,10 +462,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>53</v>
+            <v>105</v>
           </cell>
           <cell r="D8">
-            <v>8.8333333333333339</v>
+            <v>15</v>
           </cell>
         </row>
         <row r="9">
@@ -476,10 +476,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>7876</v>
+            <v>9089</v>
           </cell>
           <cell r="D9">
-            <v>1312.6666666666667</v>
+            <v>1298.4285714285713</v>
           </cell>
         </row>
         <row r="10">
@@ -490,10 +490,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>719</v>
+            <v>937</v>
           </cell>
           <cell r="D10">
-            <v>119.83333333333333</v>
+            <v>133.85714285714286</v>
           </cell>
         </row>
         <row r="11">
@@ -504,10 +504,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>1440</v>
+            <v>1955</v>
           </cell>
           <cell r="D11">
-            <v>240</v>
+            <v>279.28571428571428</v>
           </cell>
         </row>
         <row r="12">
@@ -518,10 +518,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>4132</v>
+            <v>5093</v>
           </cell>
           <cell r="D12">
-            <v>688.66666666666663</v>
+            <v>727.57142857142856</v>
           </cell>
         </row>
         <row r="13">
@@ -532,10 +532,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>1812</v>
+            <v>2271</v>
           </cell>
           <cell r="D13">
-            <v>302</v>
+            <v>324.42857142857144</v>
           </cell>
         </row>
         <row r="14">
@@ -546,10 +546,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>18780</v>
+            <v>22817</v>
           </cell>
           <cell r="D14">
-            <v>3130</v>
+            <v>3259.5714285714284</v>
           </cell>
         </row>
         <row r="15">
@@ -560,10 +560,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>11587</v>
+            <v>13843</v>
           </cell>
           <cell r="D15">
-            <v>1931.1666666666667</v>
+            <v>1977.5714285714287</v>
           </cell>
         </row>
         <row r="16">
@@ -574,10 +574,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>12604</v>
+            <v>14922</v>
           </cell>
           <cell r="D16">
-            <v>2100.6666666666665</v>
+            <v>2131.7142857142858</v>
           </cell>
         </row>
         <row r="17">
@@ -588,10 +588,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>14095</v>
+            <v>17660</v>
           </cell>
           <cell r="D17">
-            <v>2349.1666666666665</v>
+            <v>2522.8571428571427</v>
           </cell>
         </row>
         <row r="18">
@@ -602,10 +602,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>3804</v>
+            <v>4814</v>
           </cell>
           <cell r="D18">
-            <v>634</v>
+            <v>687.71428571428567</v>
           </cell>
         </row>
         <row r="19">
@@ -616,10 +616,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>4739</v>
+            <v>5710</v>
           </cell>
           <cell r="D19">
-            <v>789.83333333333337</v>
+            <v>815.71428571428567</v>
           </cell>
         </row>
         <row r="20">
@@ -630,10 +630,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>4689</v>
+            <v>5628</v>
           </cell>
           <cell r="D20">
-            <v>781.5</v>
+            <v>804</v>
           </cell>
         </row>
         <row r="21">
@@ -644,10 +644,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>1280</v>
+            <v>1730</v>
           </cell>
           <cell r="D21">
-            <v>213.33333333333334</v>
+            <v>247.14285714285714</v>
           </cell>
         </row>
         <row r="22">
@@ -658,10 +658,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>568</v>
+            <v>785</v>
           </cell>
           <cell r="D22">
-            <v>94.666666666666671</v>
+            <v>112.14285714285714</v>
           </cell>
         </row>
         <row r="23">
@@ -672,10 +672,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>2776</v>
+            <v>3625</v>
           </cell>
           <cell r="D23">
-            <v>462.66666666666669</v>
+            <v>517.85714285714289</v>
           </cell>
         </row>
         <row r="24">
@@ -686,10 +686,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>4550</v>
+            <v>5865</v>
           </cell>
           <cell r="D24">
-            <v>758.33333333333337</v>
+            <v>837.85714285714289</v>
           </cell>
         </row>
         <row r="25">
@@ -700,10 +700,10 @@
             <v>Griego Mykonos 700g</v>
           </cell>
           <cell r="C25">
-            <v>330</v>
+            <v>599</v>
           </cell>
           <cell r="D25">
-            <v>55</v>
+            <v>85.571428571428569</v>
           </cell>
         </row>
         <row r="26">
@@ -714,10 +714,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>3626</v>
+            <v>4432</v>
           </cell>
           <cell r="D26">
-            <v>604.33333333333337</v>
+            <v>633.14285714285711</v>
           </cell>
         </row>
         <row r="27">
@@ -728,10 +728,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>5273</v>
+            <v>6413</v>
           </cell>
           <cell r="D27">
-            <v>878.83333333333337</v>
+            <v>916.14285714285711</v>
           </cell>
         </row>
         <row r="28">
@@ -742,10 +742,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>2513</v>
+            <v>3366</v>
           </cell>
           <cell r="D28">
-            <v>418.83333333333331</v>
+            <v>480.85714285714283</v>
           </cell>
         </row>
         <row r="29">
@@ -756,10 +756,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>1813</v>
+            <v>2303</v>
           </cell>
           <cell r="D29">
-            <v>302.16666666666669</v>
+            <v>329</v>
           </cell>
         </row>
         <row r="30">
@@ -770,10 +770,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>1344</v>
+            <v>1527</v>
           </cell>
           <cell r="D30">
-            <v>224</v>
+            <v>218.14285714285714</v>
           </cell>
         </row>
         <row r="31">
@@ -784,10 +784,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>1600</v>
+            <v>1777</v>
           </cell>
           <cell r="D31">
-            <v>266.66666666666669</v>
+            <v>253.85714285714286</v>
           </cell>
         </row>
         <row r="32">
@@ -798,10 +798,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>661</v>
+            <v>830</v>
           </cell>
           <cell r="D32">
-            <v>110.16666666666667</v>
+            <v>118.57142857142857</v>
           </cell>
         </row>
         <row r="33">
@@ -812,10 +812,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>634</v>
+            <v>833</v>
           </cell>
           <cell r="D33">
-            <v>105.66666666666667</v>
+            <v>119</v>
           </cell>
         </row>
         <row r="34">
@@ -826,10 +826,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>3802</v>
+            <v>5092</v>
           </cell>
           <cell r="D34">
-            <v>633.66666666666663</v>
+            <v>727.42857142857144</v>
           </cell>
         </row>
         <row r="35">
@@ -840,10 +840,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>3101</v>
+            <v>4057</v>
           </cell>
           <cell r="D35">
-            <v>516.83333333333337</v>
+            <v>579.57142857142856</v>
           </cell>
         </row>
         <row r="36">
@@ -854,10 +854,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>4066</v>
+            <v>5363</v>
           </cell>
           <cell r="D36">
-            <v>677.66666666666663</v>
+            <v>766.14285714285711</v>
           </cell>
         </row>
         <row r="37">
@@ -868,10 +868,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>2344</v>
+            <v>3153</v>
           </cell>
           <cell r="D37">
-            <v>390.66666666666669</v>
+            <v>450.42857142857144</v>
           </cell>
         </row>
         <row r="38">
@@ -882,10 +882,10 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>21</v>
+            <v>28</v>
           </cell>
           <cell r="D38">
-            <v>3.5</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="39">
@@ -899,7 +899,7 @@
             <v>6</v>
           </cell>
           <cell r="D39">
-            <v>1</v>
+            <v>0.8571428571428571</v>
           </cell>
         </row>
         <row r="40">
@@ -910,10 +910,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>621</v>
+            <v>928</v>
           </cell>
           <cell r="D40">
-            <v>103.5</v>
+            <v>132.57142857142858</v>
           </cell>
         </row>
         <row r="41">
@@ -924,10 +924,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>2610</v>
+            <v>3459</v>
           </cell>
           <cell r="D41">
-            <v>435</v>
+            <v>494.14285714285717</v>
           </cell>
         </row>
         <row r="42">
@@ -938,10 +938,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>2377</v>
+            <v>2978</v>
           </cell>
           <cell r="D42">
-            <v>396.16666666666669</v>
+            <v>425.42857142857144</v>
           </cell>
         </row>
         <row r="43">
@@ -952,10 +952,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>878</v>
+            <v>997</v>
           </cell>
           <cell r="D43">
-            <v>146.33333333333334</v>
+            <v>142.42857142857142</v>
           </cell>
         </row>
         <row r="44">
@@ -966,10 +966,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>1647</v>
+            <v>2003</v>
           </cell>
           <cell r="D44">
-            <v>274.5</v>
+            <v>286.14285714285717</v>
           </cell>
         </row>
         <row r="45">
@@ -980,10 +980,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>1158</v>
+            <v>1335</v>
           </cell>
           <cell r="D45">
-            <v>193</v>
+            <v>190.71428571428572</v>
           </cell>
         </row>
         <row r="46">
@@ -994,10 +994,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>1351</v>
+            <v>1528</v>
           </cell>
           <cell r="D46">
-            <v>225.16666666666666</v>
+            <v>218.28571428571428</v>
           </cell>
         </row>
         <row r="47">
@@ -1008,10 +1008,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>192</v>
+            <v>216</v>
           </cell>
           <cell r="D47">
-            <v>32</v>
+            <v>30.857142857142858</v>
           </cell>
         </row>
         <row r="48">
@@ -1022,10 +1022,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>461</v>
+            <v>521</v>
           </cell>
           <cell r="D48">
-            <v>76.833333333333329</v>
+            <v>74.428571428571431</v>
           </cell>
         </row>
         <row r="49">
@@ -1036,10 +1036,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>168</v>
+            <v>182</v>
           </cell>
           <cell r="D49">
-            <v>28</v>
+            <v>26</v>
           </cell>
         </row>
         <row r="50">
@@ -1050,10 +1050,10 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>208</v>
+            <v>237</v>
           </cell>
           <cell r="D50">
-            <v>34.666666666666664</v>
+            <v>33.857142857142854</v>
           </cell>
         </row>
       </sheetData>
@@ -1404,11 +1404,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>6050</v>
+        <v>7805</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1008.3333333333334</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1422,11 +1422,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>533</v>
+        <v>611</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>88.833333333333329</v>
+        <v>87.285714285714292</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1440,11 +1440,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>2579</v>
+        <v>3130</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>429.83333333333331</v>
+        <v>447.14285714285717</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1458,11 +1458,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>433</v>
+        <v>733</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>72.166666666666671</v>
+        <v>104.71428571428571</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>8.8333333333333339</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1494,11 +1494,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>7876</v>
+        <v>9089</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1312.6666666666667</v>
+        <v>1298.4285714285713</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1512,11 +1512,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>719</v>
+        <v>937</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>119.83333333333333</v>
+        <v>133.85714285714286</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1530,11 +1530,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>1440</v>
+        <v>1955</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>240</v>
+        <v>279.28571428571428</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1548,11 +1548,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>4132</v>
+        <v>5093</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>688.66666666666663</v>
+        <v>727.57142857142856</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1566,11 +1566,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>1812</v>
+        <v>2271</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>302</v>
+        <v>324.42857142857144</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1584,11 +1584,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>18780</v>
+        <v>22817</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3130</v>
+        <v>3259.5714285714284</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1602,11 +1602,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>11587</v>
+        <v>13843</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>1931.1666666666667</v>
+        <v>1977.5714285714287</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1620,11 +1620,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>12604</v>
+        <v>14922</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2100.6666666666665</v>
+        <v>2131.7142857142858</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1638,11 +1638,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>14095</v>
+        <v>17660</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2349.1666666666665</v>
+        <v>2522.8571428571427</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1656,11 +1656,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>3804</v>
+        <v>4814</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>634</v>
+        <v>687.71428571428567</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1674,11 +1674,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>4739</v>
+        <v>5710</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>789.83333333333337</v>
+        <v>815.71428571428567</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1692,11 +1692,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>4689</v>
+        <v>5628</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>781.5</v>
+        <v>804</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1710,11 +1710,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>1280</v>
+        <v>1730</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>213.33333333333334</v>
+        <v>247.14285714285714</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1728,11 +1728,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>568</v>
+        <v>785</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>94.666666666666671</v>
+        <v>112.14285714285714</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1746,11 +1746,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>2776</v>
+        <v>3625</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>462.66666666666669</v>
+        <v>517.85714285714289</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1764,11 +1764,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>4550</v>
+        <v>5865</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>758.33333333333337</v>
+        <v>837.85714285714289</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1782,11 +1782,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>330</v>
+        <v>599</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>55</v>
+        <v>85.571428571428569</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1800,11 +1800,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>3626</v>
+        <v>4432</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>604.33333333333337</v>
+        <v>633.14285714285711</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1818,11 +1818,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>5273</v>
+        <v>6413</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>878.83333333333337</v>
+        <v>916.14285714285711</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1836,11 +1836,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>2513</v>
+        <v>3366</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>418.83333333333331</v>
+        <v>480.85714285714283</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1854,11 +1854,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>1813</v>
+        <v>2303</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>302.16666666666669</v>
+        <v>329</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1872,11 +1872,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>1344</v>
+        <v>1527</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>224</v>
+        <v>218.14285714285714</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1890,11 +1890,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>1600</v>
+        <v>1777</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>266.66666666666669</v>
+        <v>253.85714285714286</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1908,11 +1908,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>661</v>
+        <v>830</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>110.16666666666667</v>
+        <v>118.57142857142857</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1926,11 +1926,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>634</v>
+        <v>833</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>105.66666666666667</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1944,11 +1944,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>3802</v>
+        <v>5092</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>633.66666666666663</v>
+        <v>727.42857142857144</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1962,11 +1962,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>3101</v>
+        <v>4057</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>516.83333333333337</v>
+        <v>579.57142857142856</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1980,11 +1980,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>4066</v>
+        <v>5363</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>677.66666666666663</v>
+        <v>766.14285714285711</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1998,11 +1998,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>2344</v>
+        <v>3153</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>390.66666666666669</v>
+        <v>450.42857142857144</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2016,11 +2016,11 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2052,11 +2052,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>621</v>
+        <v>928</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>103.5</v>
+        <v>132.57142857142858</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2070,11 +2070,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>2610</v>
+        <v>3459</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>435</v>
+        <v>494.14285714285717</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2088,11 +2088,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>2377</v>
+        <v>2978</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>396.16666666666669</v>
+        <v>425.42857142857144</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2106,11 +2106,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>878</v>
+        <v>997</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>146.33333333333334</v>
+        <v>142.42857142857142</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2124,11 +2124,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>1647</v>
+        <v>2003</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>274.5</v>
+        <v>286.14285714285717</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2142,11 +2142,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>1158</v>
+        <v>1335</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>193</v>
+        <v>190.71428571428572</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2160,11 +2160,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>1351</v>
+        <v>1528</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>225.16666666666666</v>
+        <v>218.28571428571428</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2178,11 +2178,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>32</v>
+        <v>30.857142857142858</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2196,11 +2196,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>461</v>
+        <v>521</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>76.833333333333329</v>
+        <v>74.428571428571431</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2214,11 +2214,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2232,11 +2232,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>34.666666666666664</v>
+        <v>33.857142857142854</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2301,19 +2301,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>147904</v>
+        <v>188094</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>147904</v>
+        <v>183291</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>24650.666666666668</v>
+        <v>26184.428571428572</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>542314.66666666674</v>
+        <v>576057.42857142864</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2321,11 +2321,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.21973849004072257</v>
+        <v>0.27944809839977058</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-525187</v>
+        <v>-484997</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2358,7 +2358,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G5</f>
-        <v>0</v>
+        <v>4803</v>
       </c>
       <c r="B5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H5</f>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2374,11 +2374,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" s="11"/>
     </row>

--- a/data/VINCULO VTS BY SKU.xlsx
+++ b/data/VINCULO VTS BY SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4C46BB-52FF-46CB-8D41-789D0CD632A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2ED708-E05D-44AF-A1F1-DB7F6136140B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{935E6DF5-EF5A-46DF-8511-A0024DAB6D46}"/>
   </bookViews>
   <sheets>
     <sheet name="file_ventas" sheetId="1" r:id="rId1"/>
@@ -296,6 +296,7 @@
       <sheetName val="INVENTARIO NACIONAL 04-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 08-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 09-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 10-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -310,7 +311,8 @@
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9">
         <row r="1">
           <cell r="G1" t="str">
             <v>DASHBOARD</v>
@@ -341,25 +343,25 @@
         </row>
         <row r="3">
           <cell r="G3">
-            <v>188094</v>
+            <v>223525</v>
           </cell>
           <cell r="H3">
-            <v>183291</v>
+            <v>218722</v>
           </cell>
           <cell r="I3">
-            <v>26184.428571428572</v>
+            <v>27340.25</v>
           </cell>
           <cell r="J3">
-            <v>576057.42857142864</v>
+            <v>601485.5</v>
           </cell>
           <cell r="K3">
             <v>673091</v>
           </cell>
           <cell r="L3">
-            <v>0.27944809839977058</v>
+            <v>0.33208734034476767</v>
           </cell>
           <cell r="M3">
-            <v>-484997</v>
+            <v>-449566</v>
           </cell>
         </row>
         <row r="4">
@@ -370,10 +372,10 @@
             <v>Cremosillo Tradicional 150g</v>
           </cell>
           <cell r="C4">
-            <v>7805</v>
+            <v>9064</v>
           </cell>
           <cell r="D4">
-            <v>1115</v>
+            <v>1133</v>
           </cell>
           <cell r="G4" t="str">
             <v>UNITS RETURN</v>
@@ -402,10 +404,10 @@
             <v>Cremosillo Coco 150g</v>
           </cell>
           <cell r="C5">
-            <v>611</v>
+            <v>677</v>
           </cell>
           <cell r="D5">
-            <v>87.285714285714292</v>
+            <v>84.625</v>
           </cell>
           <cell r="G5">
             <v>4803</v>
@@ -414,16 +416,16 @@
             <v>46266</v>
           </cell>
           <cell r="I5">
-            <v>46275</v>
+            <v>46276</v>
           </cell>
           <cell r="J5">
             <v>46295</v>
           </cell>
           <cell r="K5">
-            <v>7</v>
+            <v>8</v>
           </cell>
           <cell r="L5">
-            <v>15</v>
+            <v>14</v>
           </cell>
         </row>
         <row r="6">
@@ -434,10 +436,10 @@
             <v>Cremosillo Tradicional 230g</v>
           </cell>
           <cell r="C6">
-            <v>3130</v>
+            <v>3432</v>
           </cell>
           <cell r="D6">
-            <v>447.14285714285717</v>
+            <v>429</v>
           </cell>
         </row>
         <row r="7">
@@ -448,10 +450,10 @@
             <v>Cremosillo Tradicional 400g</v>
           </cell>
           <cell r="C7">
-            <v>733</v>
+            <v>840</v>
           </cell>
           <cell r="D7">
-            <v>104.71428571428571</v>
+            <v>105</v>
           </cell>
         </row>
         <row r="8">
@@ -462,10 +464,10 @@
             <v>Cremosillo Tradicional 1000g</v>
           </cell>
           <cell r="C8">
-            <v>105</v>
+            <v>112</v>
           </cell>
           <cell r="D8">
-            <v>15</v>
+            <v>14</v>
           </cell>
         </row>
         <row r="9">
@@ -476,10 +478,10 @@
             <v>Gelatina Saltarina Fresa 130g</v>
           </cell>
           <cell r="C9">
-            <v>9089</v>
+            <v>10701</v>
           </cell>
           <cell r="D9">
-            <v>1298.4285714285713</v>
+            <v>1337.625</v>
           </cell>
         </row>
         <row r="10">
@@ -490,10 +492,10 @@
             <v>Gelatina Saltarina Chicle 130g</v>
           </cell>
           <cell r="C10">
-            <v>937</v>
+            <v>1082</v>
           </cell>
           <cell r="D10">
-            <v>133.85714285714286</v>
+            <v>135.25</v>
           </cell>
         </row>
         <row r="11">
@@ -504,10 +506,10 @@
             <v>Gelatina Saltarina Kolita 130g</v>
           </cell>
           <cell r="C11">
-            <v>1955</v>
+            <v>2258</v>
           </cell>
           <cell r="D11">
-            <v>279.28571428571428</v>
+            <v>282.25</v>
           </cell>
         </row>
         <row r="12">
@@ -518,10 +520,10 @@
             <v>Cremigurt Natural 150g</v>
           </cell>
           <cell r="C12">
-            <v>5093</v>
+            <v>5774</v>
           </cell>
           <cell r="D12">
-            <v>727.57142857142856</v>
+            <v>721.75</v>
           </cell>
         </row>
         <row r="13">
@@ -532,10 +534,10 @@
             <v>Cremigurt Dulce 150g</v>
           </cell>
           <cell r="C13">
-            <v>2271</v>
+            <v>2607</v>
           </cell>
           <cell r="D13">
-            <v>324.42857142857144</v>
+            <v>325.875</v>
           </cell>
         </row>
         <row r="14">
@@ -546,10 +548,10 @@
             <v>Cremigurt Fresa 150g</v>
           </cell>
           <cell r="C14">
-            <v>22817</v>
+            <v>26908</v>
           </cell>
           <cell r="D14">
-            <v>3259.5714285714284</v>
+            <v>3363.5</v>
           </cell>
         </row>
         <row r="15">
@@ -560,10 +562,10 @@
             <v>Cremigurt Durazno 150g</v>
           </cell>
           <cell r="C15">
-            <v>13843</v>
+            <v>16353</v>
           </cell>
           <cell r="D15">
-            <v>1977.5714285714287</v>
+            <v>2044.125</v>
           </cell>
         </row>
         <row r="16">
@@ -574,10 +576,10 @@
             <v>Cremigurt Piña 150g</v>
           </cell>
           <cell r="C16">
-            <v>14922</v>
+            <v>17448</v>
           </cell>
           <cell r="D16">
-            <v>2131.7142857142858</v>
+            <v>2181</v>
           </cell>
         </row>
         <row r="17">
@@ -588,10 +590,10 @@
             <v>Cremigurt Griego 150g</v>
           </cell>
           <cell r="C17">
-            <v>17660</v>
+            <v>20714</v>
           </cell>
           <cell r="D17">
-            <v>2522.8571428571427</v>
+            <v>2589.25</v>
           </cell>
         </row>
         <row r="18">
@@ -602,10 +604,10 @@
             <v>Cremigurt Griego Mango 150g</v>
           </cell>
           <cell r="C18">
-            <v>4814</v>
+            <v>5529</v>
           </cell>
           <cell r="D18">
-            <v>687.71428571428567</v>
+            <v>691.125</v>
           </cell>
         </row>
         <row r="19">
@@ -616,10 +618,10 @@
             <v>Cremigurt Griego Ciruela 150g</v>
           </cell>
           <cell r="C19">
-            <v>5710</v>
+            <v>6699</v>
           </cell>
           <cell r="D19">
-            <v>815.71428571428567</v>
+            <v>837.375</v>
           </cell>
         </row>
         <row r="20">
@@ -630,10 +632,10 @@
             <v>Cremigurt Griego Mora 150g</v>
           </cell>
           <cell r="C20">
-            <v>5628</v>
+            <v>6582</v>
           </cell>
           <cell r="D20">
-            <v>804</v>
+            <v>822.75</v>
           </cell>
         </row>
         <row r="21">
@@ -644,10 +646,10 @@
             <v>Cremigurt Natural 700g</v>
           </cell>
           <cell r="C21">
-            <v>1730</v>
+            <v>2049</v>
           </cell>
           <cell r="D21">
-            <v>247.14285714285714</v>
+            <v>256.125</v>
           </cell>
         </row>
         <row r="22">
@@ -658,10 +660,10 @@
             <v>Cremigurt Dulce 700g</v>
           </cell>
           <cell r="C22">
-            <v>785</v>
+            <v>961</v>
           </cell>
           <cell r="D22">
-            <v>112.14285714285714</v>
+            <v>120.125</v>
           </cell>
         </row>
         <row r="23">
@@ -672,10 +674,10 @@
             <v>Cremigurt Griego Fresa 700g</v>
           </cell>
           <cell r="C23">
-            <v>3625</v>
+            <v>4233</v>
           </cell>
           <cell r="D23">
-            <v>517.85714285714289</v>
+            <v>529.125</v>
           </cell>
         </row>
         <row r="24">
@@ -686,10 +688,10 @@
             <v>Cremigurt Griego 700g</v>
           </cell>
           <cell r="C24">
-            <v>5865</v>
+            <v>6800</v>
           </cell>
           <cell r="D24">
-            <v>837.85714285714289</v>
+            <v>850</v>
           </cell>
         </row>
         <row r="25">
@@ -700,10 +702,10 @@
             <v>Griego Mykonos 700g</v>
           </cell>
           <cell r="C25">
-            <v>599</v>
+            <v>620</v>
           </cell>
           <cell r="D25">
-            <v>85.571428571428569</v>
+            <v>77.5</v>
           </cell>
         </row>
         <row r="26">
@@ -714,10 +716,10 @@
             <v>Cremigurt Power Natural 150g</v>
           </cell>
           <cell r="C26">
-            <v>4432</v>
+            <v>5247</v>
           </cell>
           <cell r="D26">
-            <v>633.14285714285711</v>
+            <v>655.875</v>
           </cell>
         </row>
         <row r="27">
@@ -728,10 +730,10 @@
             <v>Cremigurt Power Mantecado 150g</v>
           </cell>
           <cell r="C27">
-            <v>6413</v>
+            <v>7711</v>
           </cell>
           <cell r="D27">
-            <v>916.14285714285711</v>
+            <v>963.875</v>
           </cell>
         </row>
         <row r="28">
@@ -742,10 +744,10 @@
             <v>Cremigurt Power CheesseCake Fresa 150g</v>
           </cell>
           <cell r="C28">
-            <v>3366</v>
+            <v>4104</v>
           </cell>
           <cell r="D28">
-            <v>480.85714285714283</v>
+            <v>513</v>
           </cell>
         </row>
         <row r="29">
@@ -756,10 +758,10 @@
             <v>Cremigurt Power Cookies and Cream 150g</v>
           </cell>
           <cell r="C29">
-            <v>2303</v>
+            <v>2795</v>
           </cell>
           <cell r="D29">
-            <v>329</v>
+            <v>349.375</v>
           </cell>
         </row>
         <row r="30">
@@ -770,10 +772,10 @@
             <v>Cremigurt Power Piña Colada 150g</v>
           </cell>
           <cell r="C30">
-            <v>1527</v>
+            <v>1717</v>
           </cell>
           <cell r="D30">
-            <v>218.14285714285714</v>
+            <v>214.625</v>
           </cell>
         </row>
         <row r="31">
@@ -784,10 +786,10 @@
             <v>Cremigurt Power Dulce de Leche 150g</v>
           </cell>
           <cell r="C31">
-            <v>1777</v>
+            <v>2058</v>
           </cell>
           <cell r="D31">
-            <v>253.85714285714286</v>
+            <v>257.25</v>
           </cell>
         </row>
         <row r="32">
@@ -798,10 +800,10 @@
             <v>Cremigurt Power Natural 700g</v>
           </cell>
           <cell r="C32">
-            <v>830</v>
+            <v>1025</v>
           </cell>
           <cell r="D32">
-            <v>118.57142857142857</v>
+            <v>128.125</v>
           </cell>
         </row>
         <row r="33">
@@ -812,10 +814,10 @@
             <v>Cremigurt Power Mantecado 700g</v>
           </cell>
           <cell r="C33">
-            <v>833</v>
+            <v>1050</v>
           </cell>
           <cell r="D33">
-            <v>119</v>
+            <v>131.25</v>
           </cell>
         </row>
         <row r="34">
@@ -826,10 +828,10 @@
             <v>Cremigurt Griego Fresa S/A 150g</v>
           </cell>
           <cell r="C34">
-            <v>5092</v>
+            <v>6142</v>
           </cell>
           <cell r="D34">
-            <v>727.42857142857144</v>
+            <v>767.75</v>
           </cell>
         </row>
         <row r="35">
@@ -840,10 +842,10 @@
             <v>Cremigurt Griego Coco Vainilla S/A 150g</v>
           </cell>
           <cell r="C35">
-            <v>4057</v>
+            <v>4726</v>
           </cell>
           <cell r="D35">
-            <v>579.57142857142856</v>
+            <v>590.75</v>
           </cell>
         </row>
         <row r="36">
@@ -854,10 +856,10 @@
             <v>Cremigurt Griego Pie de Limón S/A 150g</v>
           </cell>
           <cell r="C36">
-            <v>5363</v>
+            <v>6389</v>
           </cell>
           <cell r="D36">
-            <v>766.14285714285711</v>
+            <v>798.625</v>
           </cell>
         </row>
         <row r="37">
@@ -868,10 +870,10 @@
             <v>Cremigurt Griego Caramelo Salado S/A 150g</v>
           </cell>
           <cell r="C37">
-            <v>3153</v>
+            <v>3896</v>
           </cell>
           <cell r="D37">
-            <v>450.42857142857144</v>
+            <v>487</v>
           </cell>
         </row>
         <row r="38">
@@ -882,7 +884,7 @@
             <v>Cremigurt Griego Natural 4 Kg</v>
           </cell>
           <cell r="C38">
-            <v>28</v>
+            <v>32</v>
           </cell>
           <cell r="D38">
             <v>4</v>
@@ -899,7 +901,7 @@
             <v>6</v>
           </cell>
           <cell r="D39">
-            <v>0.8571428571428571</v>
+            <v>0.75</v>
           </cell>
         </row>
         <row r="40">
@@ -910,10 +912,10 @@
             <v>Cremigurt Líquido Dulce 230g</v>
           </cell>
           <cell r="C40">
-            <v>928</v>
+            <v>1140</v>
           </cell>
           <cell r="D40">
-            <v>132.57142857142858</v>
+            <v>142.5</v>
           </cell>
         </row>
         <row r="41">
@@ -924,10 +926,10 @@
             <v>Cremigurt Líquido Fresa 230g</v>
           </cell>
           <cell r="C41">
-            <v>3459</v>
+            <v>4182</v>
           </cell>
           <cell r="D41">
-            <v>494.14285714285717</v>
+            <v>522.75</v>
           </cell>
         </row>
         <row r="42">
@@ -938,10 +940,10 @@
             <v>Cremigurt Líquido Durazno 230g</v>
           </cell>
           <cell r="C42">
-            <v>2978</v>
+            <v>3404</v>
           </cell>
           <cell r="D42">
-            <v>425.42857142857144</v>
+            <v>425.5</v>
           </cell>
         </row>
         <row r="43">
@@ -952,10 +954,10 @@
             <v>Tevia Limon 360ml</v>
           </cell>
           <cell r="C43">
-            <v>997</v>
+            <v>1477</v>
           </cell>
           <cell r="D43">
-            <v>142.42857142857142</v>
+            <v>184.625</v>
           </cell>
         </row>
         <row r="44">
@@ -966,10 +968,10 @@
             <v>Tevia Durazno 360ml</v>
           </cell>
           <cell r="C44">
-            <v>2003</v>
+            <v>3785</v>
           </cell>
           <cell r="D44">
-            <v>286.14285714285717</v>
+            <v>473.125</v>
           </cell>
         </row>
         <row r="45">
@@ -980,10 +982,10 @@
             <v>Tevia Blueberry 360ml</v>
           </cell>
           <cell r="C45">
-            <v>1335</v>
+            <v>2519</v>
           </cell>
           <cell r="D45">
-            <v>190.71428571428572</v>
+            <v>314.875</v>
           </cell>
         </row>
         <row r="46">
@@ -994,10 +996,10 @@
             <v>Tevia Tropical Punch 360ml</v>
           </cell>
           <cell r="C46">
-            <v>1528</v>
+            <v>1785</v>
           </cell>
           <cell r="D46">
-            <v>218.28571428571428</v>
+            <v>223.125</v>
           </cell>
         </row>
         <row r="47">
@@ -1008,10 +1010,10 @@
             <v>Tevia Limon 1.5L</v>
           </cell>
           <cell r="C47">
-            <v>216</v>
+            <v>241</v>
           </cell>
           <cell r="D47">
-            <v>30.857142857142858</v>
+            <v>30.125</v>
           </cell>
         </row>
         <row r="48">
@@ -1022,10 +1024,10 @@
             <v>Tevia Durazno 1.5 L</v>
           </cell>
           <cell r="C48">
-            <v>521</v>
+            <v>902</v>
           </cell>
           <cell r="D48">
-            <v>74.428571428571431</v>
+            <v>112.75</v>
           </cell>
         </row>
         <row r="49">
@@ -1036,10 +1038,10 @@
             <v>Tevia Blueberry 1.5 L</v>
           </cell>
           <cell r="C49">
-            <v>182</v>
+            <v>382</v>
           </cell>
           <cell r="D49">
-            <v>26</v>
+            <v>47.75</v>
           </cell>
         </row>
         <row r="50">
@@ -1050,14 +1052,14 @@
             <v>Tevia Tropical Punch 1.5 L</v>
           </cell>
           <cell r="C50">
-            <v>237</v>
+            <v>564</v>
           </cell>
           <cell r="D50">
-            <v>33.857142857142854</v>
+            <v>70.5</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1404,11 +1406,11 @@
       </c>
       <c r="C2" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C4</f>
-        <v>7805</v>
+        <v>9064</v>
       </c>
       <c r="D2" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D4</f>
-        <v>1115</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1422,11 +1424,11 @@
       </c>
       <c r="C3" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C5</f>
-        <v>611</v>
+        <v>677</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D5</f>
-        <v>87.285714285714292</v>
+        <v>84.625</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1440,11 +1442,11 @@
       </c>
       <c r="C4" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C6</f>
-        <v>3130</v>
+        <v>3432</v>
       </c>
       <c r="D4" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D6</f>
-        <v>447.14285714285717</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1458,11 +1460,11 @@
       </c>
       <c r="C5" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C7</f>
-        <v>733</v>
+        <v>840</v>
       </c>
       <c r="D5" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D7</f>
-        <v>104.71428571428571</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1476,11 +1478,11 @@
       </c>
       <c r="C6" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C8</f>
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D6" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D8</f>
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1494,11 +1496,11 @@
       </c>
       <c r="C7" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C9</f>
-        <v>9089</v>
+        <v>10701</v>
       </c>
       <c r="D7" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D9</f>
-        <v>1298.4285714285713</v>
+        <v>1337.625</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1512,11 +1514,11 @@
       </c>
       <c r="C8" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C10</f>
-        <v>937</v>
+        <v>1082</v>
       </c>
       <c r="D8" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D10</f>
-        <v>133.85714285714286</v>
+        <v>135.25</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1530,11 +1532,11 @@
       </c>
       <c r="C9" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C11</f>
-        <v>1955</v>
+        <v>2258</v>
       </c>
       <c r="D9" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D11</f>
-        <v>279.28571428571428</v>
+        <v>282.25</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1548,11 +1550,11 @@
       </c>
       <c r="C10" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C12</f>
-        <v>5093</v>
+        <v>5774</v>
       </c>
       <c r="D10" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D12</f>
-        <v>727.57142857142856</v>
+        <v>721.75</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1566,11 +1568,11 @@
       </c>
       <c r="C11" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C13</f>
-        <v>2271</v>
+        <v>2607</v>
       </c>
       <c r="D11" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D13</f>
-        <v>324.42857142857144</v>
+        <v>325.875</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1584,11 +1586,11 @@
       </c>
       <c r="C12" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C14</f>
-        <v>22817</v>
+        <v>26908</v>
       </c>
       <c r="D12" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D14</f>
-        <v>3259.5714285714284</v>
+        <v>3363.5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1602,11 +1604,11 @@
       </c>
       <c r="C13" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C15</f>
-        <v>13843</v>
+        <v>16353</v>
       </c>
       <c r="D13" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D15</f>
-        <v>1977.5714285714287</v>
+        <v>2044.125</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1620,11 +1622,11 @@
       </c>
       <c r="C14" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C16</f>
-        <v>14922</v>
+        <v>17448</v>
       </c>
       <c r="D14" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D16</f>
-        <v>2131.7142857142858</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1638,11 +1640,11 @@
       </c>
       <c r="C15" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C17</f>
-        <v>17660</v>
+        <v>20714</v>
       </c>
       <c r="D15" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D17</f>
-        <v>2522.8571428571427</v>
+        <v>2589.25</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1656,11 +1658,11 @@
       </c>
       <c r="C16" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C18</f>
-        <v>4814</v>
+        <v>5529</v>
       </c>
       <c r="D16" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D18</f>
-        <v>687.71428571428567</v>
+        <v>691.125</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1674,11 +1676,11 @@
       </c>
       <c r="C17" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C19</f>
-        <v>5710</v>
+        <v>6699</v>
       </c>
       <c r="D17" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D19</f>
-        <v>815.71428571428567</v>
+        <v>837.375</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1692,11 +1694,11 @@
       </c>
       <c r="C18" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C20</f>
-        <v>5628</v>
+        <v>6582</v>
       </c>
       <c r="D18" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D20</f>
-        <v>804</v>
+        <v>822.75</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1710,11 +1712,11 @@
       </c>
       <c r="C19" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C21</f>
-        <v>1730</v>
+        <v>2049</v>
       </c>
       <c r="D19" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D21</f>
-        <v>247.14285714285714</v>
+        <v>256.125</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1728,11 +1730,11 @@
       </c>
       <c r="C20" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C22</f>
-        <v>785</v>
+        <v>961</v>
       </c>
       <c r="D20" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D22</f>
-        <v>112.14285714285714</v>
+        <v>120.125</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1746,11 +1748,11 @@
       </c>
       <c r="C21" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C23</f>
-        <v>3625</v>
+        <v>4233</v>
       </c>
       <c r="D21" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D23</f>
-        <v>517.85714285714289</v>
+        <v>529.125</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1764,11 +1766,11 @@
       </c>
       <c r="C22" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C24</f>
-        <v>5865</v>
+        <v>6800</v>
       </c>
       <c r="D22" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D24</f>
-        <v>837.85714285714289</v>
+        <v>850</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1782,11 +1784,11 @@
       </c>
       <c r="C23" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C25</f>
-        <v>599</v>
+        <v>620</v>
       </c>
       <c r="D23" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D25</f>
-        <v>85.571428571428569</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1800,11 +1802,11 @@
       </c>
       <c r="C24" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C26</f>
-        <v>4432</v>
+        <v>5247</v>
       </c>
       <c r="D24" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D26</f>
-        <v>633.14285714285711</v>
+        <v>655.875</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1818,11 +1820,11 @@
       </c>
       <c r="C25" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C27</f>
-        <v>6413</v>
+        <v>7711</v>
       </c>
       <c r="D25" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D27</f>
-        <v>916.14285714285711</v>
+        <v>963.875</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1836,11 +1838,11 @@
       </c>
       <c r="C26" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C28</f>
-        <v>3366</v>
+        <v>4104</v>
       </c>
       <c r="D26" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D28</f>
-        <v>480.85714285714283</v>
+        <v>513</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1854,11 +1856,11 @@
       </c>
       <c r="C27" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C29</f>
-        <v>2303</v>
+        <v>2795</v>
       </c>
       <c r="D27" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D29</f>
-        <v>329</v>
+        <v>349.375</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1872,11 +1874,11 @@
       </c>
       <c r="C28" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C30</f>
-        <v>1527</v>
+        <v>1717</v>
       </c>
       <c r="D28" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D30</f>
-        <v>218.14285714285714</v>
+        <v>214.625</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1890,11 +1892,11 @@
       </c>
       <c r="C29" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C31</f>
-        <v>1777</v>
+        <v>2058</v>
       </c>
       <c r="D29" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D31</f>
-        <v>253.85714285714286</v>
+        <v>257.25</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1908,11 +1910,11 @@
       </c>
       <c r="C30" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C32</f>
-        <v>830</v>
+        <v>1025</v>
       </c>
       <c r="D30" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D32</f>
-        <v>118.57142857142857</v>
+        <v>128.125</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1926,11 +1928,11 @@
       </c>
       <c r="C31" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C33</f>
-        <v>833</v>
+        <v>1050</v>
       </c>
       <c r="D31" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D33</f>
-        <v>119</v>
+        <v>131.25</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1944,11 +1946,11 @@
       </c>
       <c r="C32" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C34</f>
-        <v>5092</v>
+        <v>6142</v>
       </c>
       <c r="D32" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D34</f>
-        <v>727.42857142857144</v>
+        <v>767.75</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1962,11 +1964,11 @@
       </c>
       <c r="C33" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C35</f>
-        <v>4057</v>
+        <v>4726</v>
       </c>
       <c r="D33" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D35</f>
-        <v>579.57142857142856</v>
+        <v>590.75</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1980,11 +1982,11 @@
       </c>
       <c r="C34" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C36</f>
-        <v>5363</v>
+        <v>6389</v>
       </c>
       <c r="D34" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D36</f>
-        <v>766.14285714285711</v>
+        <v>798.625</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1998,11 +2000,11 @@
       </c>
       <c r="C35" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C37</f>
-        <v>3153</v>
+        <v>3896</v>
       </c>
       <c r="D35" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D37</f>
-        <v>450.42857142857144</v>
+        <v>487</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2016,7 +2018,7 @@
       </c>
       <c r="C36" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C38</f>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D36" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D38</f>
@@ -2038,7 +2040,7 @@
       </c>
       <c r="D37" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D39</f>
-        <v>0.8571428571428571</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2052,11 +2054,11 @@
       </c>
       <c r="C38" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C40</f>
-        <v>928</v>
+        <v>1140</v>
       </c>
       <c r="D38" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D40</f>
-        <v>132.57142857142858</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2070,11 +2072,11 @@
       </c>
       <c r="C39" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C41</f>
-        <v>3459</v>
+        <v>4182</v>
       </c>
       <c r="D39" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D41</f>
-        <v>494.14285714285717</v>
+        <v>522.75</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2088,11 +2090,11 @@
       </c>
       <c r="C40" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C42</f>
-        <v>2978</v>
+        <v>3404</v>
       </c>
       <c r="D40" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D42</f>
-        <v>425.42857142857144</v>
+        <v>425.5</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2106,11 +2108,11 @@
       </c>
       <c r="C41" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C43</f>
-        <v>997</v>
+        <v>1477</v>
       </c>
       <c r="D41" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D43</f>
-        <v>142.42857142857142</v>
+        <v>184.625</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2124,11 +2126,11 @@
       </c>
       <c r="C42" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C44</f>
-        <v>2003</v>
+        <v>3785</v>
       </c>
       <c r="D42" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D44</f>
-        <v>286.14285714285717</v>
+        <v>473.125</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2142,11 +2144,11 @@
       </c>
       <c r="C43" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C45</f>
-        <v>1335</v>
+        <v>2519</v>
       </c>
       <c r="D43" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D45</f>
-        <v>190.71428571428572</v>
+        <v>314.875</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2160,11 +2162,11 @@
       </c>
       <c r="C44" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C46</f>
-        <v>1528</v>
+        <v>1785</v>
       </c>
       <c r="D44" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D46</f>
-        <v>218.28571428571428</v>
+        <v>223.125</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2178,11 +2180,11 @@
       </c>
       <c r="C45" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C47</f>
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="D45" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D47</f>
-        <v>30.857142857142858</v>
+        <v>30.125</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2196,11 +2198,11 @@
       </c>
       <c r="C46" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C48</f>
-        <v>521</v>
+        <v>902</v>
       </c>
       <c r="D46" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D48</f>
-        <v>74.428571428571431</v>
+        <v>112.75</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2214,11 +2216,11 @@
       </c>
       <c r="C47" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C49</f>
-        <v>182</v>
+        <v>382</v>
       </c>
       <c r="D47" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D49</f>
-        <v>26</v>
+        <v>47.75</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2232,11 +2234,11 @@
       </c>
       <c r="C48" s="13">
         <f>'[1]VINCULO VTS BY SKU OPEN'!C50</f>
-        <v>237</v>
+        <v>564</v>
       </c>
       <c r="D48" s="12">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!D50</f>
-        <v>33.857142857142854</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
@@ -2301,19 +2303,19 @@
     <row r="3" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!G3</f>
-        <v>188094</v>
+        <v>223525</v>
       </c>
       <c r="B3" s="3">
         <f>'[1]VINCULO VTS BY SKU OPEN'!H3</f>
-        <v>183291</v>
+        <v>218722</v>
       </c>
       <c r="C3" s="4">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I3</f>
-        <v>26184.428571428572</v>
+        <v>27340.25</v>
       </c>
       <c r="D3" s="5">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!J3</f>
-        <v>576057.42857142864</v>
+        <v>601485.5</v>
       </c>
       <c r="E3" s="4">
         <f>'[1]VINCULO VTS BY SKU OPEN'!K3</f>
@@ -2321,11 +2323,11 @@
       </c>
       <c r="F3" s="6">
         <f>'[1]VINCULO VTS BY SKU OPEN'!L3</f>
-        <v>0.27944809839977058</v>
+        <v>0.33208734034476767</v>
       </c>
       <c r="G3" s="7">
         <f>'[1]VINCULO VTS BY SKU OPEN'!M3</f>
-        <v>-484997</v>
+        <v>-449566</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2366,7 +2368,7 @@
       </c>
       <c r="C5" s="16">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!I5</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D5" s="16">
         <f>'[1]VINCULO VTS BY SKU OPEN'!J5</f>
@@ -2374,11 +2376,11 @@
       </c>
       <c r="E5" s="19">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!K5</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="17">
         <f ca="1">'[1]VINCULO VTS BY SKU OPEN'!L5</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" s="11"/>
     </row>
